--- a/research/traditional_assets/database/data/luxembourg/luxembourg_environmental_waste_services.xlsx
+++ b/research/traditional_assets/database/data/luxembourg/luxembourg_environmental_waste_services.xlsx
@@ -650,10 +650,10 @@
         <v>0.07110804280289955</v>
       </c>
       <c r="X2">
-        <v>0.1060356240412631</v>
+        <v>0.1059968978905859</v>
       </c>
       <c r="Y2">
-        <v>-0.03492758123836358</v>
+        <v>-0.03488885508768637</v>
       </c>
       <c r="Z2">
         <v>1.450911870700011</v>
@@ -662,10 +662,10 @@
         <v>0.09097186980066679</v>
       </c>
       <c r="AB2">
-        <v>0.07750531717522956</v>
+        <v>0.07748566608814586</v>
       </c>
       <c r="AC2">
-        <v>0.01346655262543724</v>
+        <v>0.01348620371252093</v>
       </c>
       <c r="AD2">
         <v>834.5</v>
@@ -787,10 +787,10 @@
         <v>0.07110804280289955</v>
       </c>
       <c r="X3">
-        <v>0.1060356240412631</v>
+        <v>0.1059968978905859</v>
       </c>
       <c r="Y3">
-        <v>-0.03492758123836358</v>
+        <v>-0.03488885508768637</v>
       </c>
       <c r="Z3">
         <v>1.450911870700011</v>
@@ -799,10 +799,10 @@
         <v>0.09097186980066679</v>
       </c>
       <c r="AB3">
-        <v>0.07750531717522956</v>
+        <v>0.07748566608814586</v>
       </c>
       <c r="AC3">
-        <v>0.01346655262543724</v>
+        <v>0.01348620371252093</v>
       </c>
       <c r="AD3">
         <v>834.5</v>
@@ -1139,49 +1139,49 @@
         <v>2.03189066059225</v>
       </c>
       <c r="F2">
-        <v>4.62565669033576</v>
+        <v>4.54044172192202</v>
       </c>
       <c r="G2">
         <v>4.44592434736281</v>
       </c>
       <c r="H2">
-        <v>2.70783164624401</v>
+        <v>2.88835375599361</v>
       </c>
       <c r="I2">
         <v>0.492562861527565</v>
       </c>
       <c r="J2">
-        <v>0.3</v>
+        <v>0.32</v>
       </c>
       <c r="K2">
         <v>859.7</v>
       </c>
       <c r="L2">
-        <v>1194.45781088635</v>
+        <v>1204.89834090614</v>
       </c>
       <c r="M2">
         <v>1598.1</v>
       </c>
       <c r="N2">
-        <v>1606.61781088635</v>
+        <v>1650.94234090614</v>
       </c>
       <c r="O2">
         <v>834.5</v>
       </c>
       <c r="P2">
-        <v>508.26</v>
+        <v>542.144</v>
       </c>
       <c r="Q2">
-        <v>0.0775053171752296</v>
+        <v>0.0774856660881459</v>
       </c>
       <c r="R2">
-        <v>0.0773372249917865</v>
+        <v>0.0764714908939057</v>
       </c>
       <c r="S2">
         <v>0.04811346</v>
       </c>
       <c r="T2">
-        <v>0.04345974</v>
+        <v>0.04150818</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -1194,16 +1194,16 @@
         </is>
       </c>
       <c r="W2">
-        <v>0.106035624041263</v>
+        <v>0.105996897890586</v>
       </c>
       <c r="X2">
-        <v>0.0918561471311236</v>
+        <v>0.09292481366750829</v>
       </c>
       <c r="Y2">
         <v>1.39022858869713</v>
       </c>
       <c r="Z2">
-        <v>1.06296852478972</v>
+        <v>1.08833287915724</v>
       </c>
       <c r="AA2">
         <v>834.5</v>
@@ -1236,7 +1236,7 @@
         <v>859.7</v>
       </c>
       <c r="AK2">
-        <v>0.043327855959079</v>
+        <v>0.04329999999999999</v>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
@@ -1424,13 +1424,13 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0.08064651958730899</v>
+        <v>0.08062411637343692</v>
       </c>
       <c r="C2">
-        <v>1550.1409767691</v>
+        <v>1550.174596824246</v>
       </c>
       <c r="D2">
-        <v>1454.040976769101</v>
+        <v>1454.074596824246</v>
       </c>
       <c r="E2">
         <v>-834.5</v>
@@ -1475,19 +1475,19 @@
         <v>0</v>
       </c>
       <c r="S2">
-        <v>0.08064651958730899</v>
+        <v>0.08062411637343692</v>
       </c>
       <c r="T2">
         <v>0.8042521102410373</v>
       </c>
       <c r="U2">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V2">
         <v>0.2494</v>
       </c>
       <c r="W2">
-        <v>0.03880602</v>
+        <v>0.03775518</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -1506,13 +1506,13 @@
         <v>0.01</v>
       </c>
       <c r="B3">
-        <v>0.08048967256745823</v>
+        <v>0.08045681682720156</v>
       </c>
       <c r="C3">
-        <v>1539.773325186591</v>
+        <v>1540.251880258555</v>
       </c>
       <c r="D3">
-        <v>1460.615325186591</v>
+        <v>1461.093880258555</v>
       </c>
       <c r="E3">
         <v>-817.558</v>
@@ -1539,37 +1539,37 @@
         <v>136.125</v>
       </c>
       <c r="M3">
-        <v>0.8759014000000002</v>
+        <v>0.8521826000000001</v>
       </c>
       <c r="N3">
-        <v>135.2490986</v>
+        <v>135.2728174</v>
       </c>
       <c r="O3">
-        <v>33.73112519084</v>
+        <v>33.73704065955999</v>
       </c>
       <c r="P3">
-        <v>101.51797340916</v>
+        <v>101.53577674044</v>
       </c>
       <c r="Q3">
-        <v>200.01797340916</v>
+        <v>200.03577674044</v>
       </c>
       <c r="R3">
         <v>0.0101010101010101</v>
       </c>
       <c r="S3">
-        <v>0.08091071956308912</v>
+        <v>0.08088814649212278</v>
       </c>
       <c r="T3">
         <v>0.8103498035132284</v>
       </c>
       <c r="U3">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V3">
         <v>0.2494</v>
       </c>
       <c r="W3">
-        <v>0.03880602</v>
+        <v>0.03775518</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>155.4113282613773</v>
+        <v>159.7368920698451</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1588,13 +1588,13 @@
         <v>0.02</v>
       </c>
       <c r="B4">
-        <v>0.08033282554760748</v>
+        <v>0.0802895172809662</v>
       </c>
       <c r="C4">
-        <v>1529.46539457625</v>
+        <v>1530.397261075839</v>
       </c>
       <c r="D4">
-        <v>1467.249394576251</v>
+        <v>1468.181261075839</v>
       </c>
       <c r="E4">
         <v>-800.616</v>
@@ -1621,37 +1621,37 @@
         <v>136.125</v>
       </c>
       <c r="M4">
-        <v>1.7518028</v>
+        <v>1.7043652</v>
       </c>
       <c r="N4">
-        <v>134.3731972</v>
+        <v>134.4206348</v>
       </c>
       <c r="O4">
-        <v>33.51267538167999</v>
+        <v>33.52450631911999</v>
       </c>
       <c r="P4">
-        <v>100.86052181832</v>
+        <v>100.89612848088</v>
       </c>
       <c r="Q4">
-        <v>199.36052181832</v>
+        <v>199.39612848088</v>
       </c>
       <c r="R4">
         <v>0.02040816326530612</v>
       </c>
       <c r="S4">
-        <v>0.08118031137510968</v>
+        <v>0.08115756498057776</v>
       </c>
       <c r="T4">
         <v>0.8165719395052602</v>
       </c>
       <c r="U4">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V4">
         <v>0.2494</v>
       </c>
       <c r="W4">
-        <v>0.03880602</v>
+        <v>0.03775518</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>77.70566413068865</v>
+        <v>79.86844603492253</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1670,13 +1670,13 @@
         <v>0.03</v>
       </c>
       <c r="B5">
-        <v>0.08017597852775674</v>
+        <v>0.08012221773473084</v>
       </c>
       <c r="C5">
-        <v>1519.218002403378</v>
+        <v>1520.61173507375</v>
       </c>
       <c r="D5">
-        <v>1473.944002403379</v>
+        <v>1475.33773507375</v>
       </c>
       <c r="E5">
         <v>-783.674</v>
@@ -1703,37 +1703,37 @@
         <v>136.125</v>
       </c>
       <c r="M5">
-        <v>2.627704200000001</v>
+        <v>2.5565478</v>
       </c>
       <c r="N5">
-        <v>133.4972958</v>
+        <v>133.5684522</v>
       </c>
       <c r="O5">
-        <v>33.29422557251999</v>
+        <v>33.31197197867999</v>
       </c>
       <c r="P5">
-        <v>100.20307022748</v>
+        <v>100.25648022132</v>
       </c>
       <c r="Q5">
-        <v>198.70307022748</v>
+        <v>198.75648022132</v>
       </c>
       <c r="R5">
         <v>0.03092783505154639</v>
       </c>
       <c r="S5">
-        <v>0.08145546178119252</v>
+        <v>0.08143253848941324</v>
       </c>
       <c r="T5">
         <v>0.8229223669610451</v>
       </c>
       <c r="U5">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V5">
         <v>0.2494</v>
       </c>
       <c r="W5">
-        <v>0.03880602</v>
+        <v>0.03775518</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>51.80377608712576</v>
+        <v>53.24563068994836</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1752,13 +1752,13 @@
         <v>0.04</v>
       </c>
       <c r="B6">
-        <v>0.08001913150790599</v>
+        <v>0.0799549181884955</v>
       </c>
       <c r="C6">
-        <v>1509.031981121028</v>
+        <v>1510.896317560628</v>
       </c>
       <c r="D6">
-        <v>1480.699981121028</v>
+        <v>1482.564317560628</v>
       </c>
       <c r="E6">
         <v>-766.732</v>
@@ -1785,37 +1785,37 @@
         <v>136.125</v>
       </c>
       <c r="M6">
-        <v>3.503605600000001</v>
+        <v>3.4087304</v>
       </c>
       <c r="N6">
-        <v>132.6213944</v>
+        <v>132.7162696</v>
       </c>
       <c r="O6">
-        <v>33.07577576335999</v>
+        <v>33.09943763824</v>
       </c>
       <c r="P6">
-        <v>99.54561863663997</v>
+        <v>99.61683196175997</v>
       </c>
       <c r="Q6">
-        <v>198.04561863664</v>
+        <v>198.11683196176</v>
       </c>
       <c r="R6">
         <v>0.04166666666666667</v>
       </c>
       <c r="S6">
-        <v>0.08173634448740208</v>
+        <v>0.08171324061301614</v>
       </c>
       <c r="T6">
         <v>0.8294050949888256</v>
       </c>
       <c r="U6">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V6">
         <v>0.2494</v>
       </c>
       <c r="W6">
-        <v>0.03880602</v>
+        <v>0.03775518</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>38.85283206534432</v>
+        <v>39.93422301746127</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1834,13 +1834,13 @@
         <v>0.05</v>
       </c>
       <c r="B7">
-        <v>0.07986228448805524</v>
+        <v>0.07978761864226015</v>
       </c>
       <c r="C7">
-        <v>1498.908178515079</v>
+        <v>1501.252043835696</v>
       </c>
       <c r="D7">
-        <v>1487.518178515079</v>
+        <v>1489.862043835696</v>
       </c>
       <c r="E7">
         <v>-749.79</v>
@@ -1867,37 +1867,37 @@
         <v>136.125</v>
       </c>
       <c r="M7">
-        <v>4.379507000000001</v>
+        <v>4.260913</v>
       </c>
       <c r="N7">
-        <v>131.745493</v>
+        <v>131.864087</v>
       </c>
       <c r="O7">
-        <v>32.8573259542</v>
+        <v>32.8869032978</v>
       </c>
       <c r="P7">
-        <v>98.88816704579997</v>
+        <v>98.97718370219999</v>
       </c>
       <c r="Q7">
-        <v>197.3881670458</v>
+        <v>197.4771837022</v>
       </c>
       <c r="R7">
         <v>0.05263157894736843</v>
       </c>
       <c r="S7">
-        <v>0.08202314051374236</v>
+        <v>0.08199985225501069</v>
       </c>
       <c r="T7">
         <v>0.8360243015014016</v>
       </c>
       <c r="U7">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V7">
         <v>0.2494</v>
       </c>
       <c r="W7">
-        <v>0.03880602</v>
+        <v>0.03775518</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>31.08226565227546</v>
+        <v>31.94737841396902</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1916,13 +1916,13 @@
         <v>0.06</v>
       </c>
       <c r="B8">
-        <v>0.07970543746820449</v>
+        <v>0.07962031909602479</v>
       </c>
       <c r="C8">
-        <v>1488.847458058889</v>
+        <v>1491.679969683506</v>
       </c>
       <c r="D8">
-        <v>1494.399458058889</v>
+        <v>1497.231969683506</v>
       </c>
       <c r="E8">
         <v>-732.848</v>
@@ -1949,37 +1949,37 @@
         <v>136.125</v>
       </c>
       <c r="M8">
-        <v>5.255408400000001</v>
+        <v>5.1130956</v>
       </c>
       <c r="N8">
-        <v>130.8695916</v>
+        <v>131.0119044</v>
       </c>
       <c r="O8">
-        <v>32.63887614503999</v>
+        <v>32.67436895736</v>
       </c>
       <c r="P8">
-        <v>98.23071545495998</v>
+        <v>98.33753544263996</v>
       </c>
       <c r="Q8">
-        <v>196.73071545496</v>
+        <v>196.83753544264</v>
       </c>
       <c r="R8">
         <v>0.06382978723404255</v>
       </c>
       <c r="S8">
-        <v>0.08231603858319628</v>
+        <v>0.08229256201704765</v>
       </c>
       <c r="T8">
         <v>0.842784342195096</v>
       </c>
       <c r="U8">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V8">
         <v>0.2494</v>
       </c>
       <c r="W8">
-        <v>0.03880602</v>
+        <v>0.03775518</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>25.90188804356288</v>
+        <v>26.62281534497418</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1998,13 +1998,13 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="B9">
-        <v>0.07954859044835375</v>
+        <v>0.07945301954978945</v>
       </c>
       <c r="C9">
-        <v>1478.850699277832</v>
+        <v>1482.181171883134</v>
       </c>
       <c r="D9">
-        <v>1501.344699277832</v>
+        <v>1504.675171883134</v>
       </c>
       <c r="E9">
         <v>-715.9059999999999</v>
@@ -2031,37 +2031,37 @@
         <v>136.125</v>
       </c>
       <c r="M9">
-        <v>6.131309800000001</v>
+        <v>5.965278200000001</v>
       </c>
       <c r="N9">
-        <v>129.9936902</v>
+        <v>130.1597218</v>
       </c>
       <c r="O9">
-        <v>32.42042633587999</v>
+        <v>32.46183461691999</v>
       </c>
       <c r="P9">
-        <v>97.57326386411998</v>
+        <v>97.69788718307998</v>
       </c>
       <c r="Q9">
-        <v>196.07326386412</v>
+        <v>196.19788718308</v>
       </c>
       <c r="R9">
         <v>0.07526881720430109</v>
       </c>
       <c r="S9">
-        <v>0.08261523553586425</v>
+        <v>0.08259156661267683</v>
       </c>
       <c r="T9">
         <v>0.84968976010801</v>
       </c>
       <c r="U9">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V9">
         <v>0.2494</v>
       </c>
       <c r="W9">
-        <v>0.03880602</v>
+        <v>0.03775518</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>22.2016183230539</v>
+        <v>22.81955600997787</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2080,13 +2080,13 @@
         <v>0.08</v>
       </c>
       <c r="B10">
-        <v>0.07939174342850301</v>
+        <v>0.07928572000355411</v>
       </c>
       <c r="C10">
-        <v>1468.918798124045</v>
+        <v>1472.756748732636</v>
       </c>
       <c r="D10">
-        <v>1508.354798124045</v>
+        <v>1512.192748732636</v>
       </c>
       <c r="E10">
         <v>-698.9639999999999</v>
@@ -2113,37 +2113,37 @@
         <v>136.125</v>
       </c>
       <c r="M10">
-        <v>7.007211200000001</v>
+        <v>6.817460800000001</v>
       </c>
       <c r="N10">
-        <v>129.1177888</v>
+        <v>129.3075392</v>
       </c>
       <c r="O10">
-        <v>32.20197652672</v>
+        <v>32.24930027648</v>
       </c>
       <c r="P10">
-        <v>96.91581227327998</v>
+        <v>97.05823892351998</v>
       </c>
       <c r="Q10">
-        <v>195.41581227328</v>
+        <v>195.55823892352</v>
       </c>
       <c r="R10">
         <v>0.08695652173913043</v>
       </c>
       <c r="S10">
-        <v>0.08292093677011196</v>
+        <v>0.08289707130821097</v>
       </c>
       <c r="T10">
         <v>0.8567452958016393</v>
       </c>
       <c r="U10">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V10">
         <v>0.2494</v>
       </c>
       <c r="W10">
-        <v>0.03880602</v>
+        <v>0.03775518</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>19.42641603267216</v>
+        <v>19.96711150873064</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2162,13 +2162,13 @@
         <v>0.09</v>
       </c>
       <c r="B11">
-        <v>0.07923489640865226</v>
+        <v>0.07911842045731875</v>
       </c>
       <c r="C11">
-        <v>1459.052667361734</v>
+        <v>1463.407820589312</v>
       </c>
       <c r="D11">
-        <v>1515.430667361735</v>
+        <v>1519.785820589312</v>
       </c>
       <c r="E11">
         <v>-682.0219999999999</v>
@@ -2195,37 +2195,37 @@
         <v>136.125</v>
       </c>
       <c r="M11">
-        <v>7.883112600000002</v>
+        <v>7.669643400000001</v>
       </c>
       <c r="N11">
-        <v>128.2418874</v>
+        <v>128.4553566</v>
       </c>
       <c r="O11">
-        <v>31.98352671755999</v>
+        <v>32.03676593603999</v>
       </c>
       <c r="P11">
-        <v>96.25836068243997</v>
+        <v>96.41859066395998</v>
       </c>
       <c r="Q11">
-        <v>194.75836068244</v>
+        <v>194.91859066396</v>
       </c>
       <c r="R11">
         <v>0.0989010989010989</v>
       </c>
       <c r="S11">
-        <v>0.08323335671280468</v>
+        <v>0.08320929039265795</v>
       </c>
       <c r="T11">
         <v>0.8639558982138099</v>
       </c>
       <c r="U11">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V11">
         <v>0.2494</v>
       </c>
       <c r="W11">
-        <v>0.03880602</v>
+        <v>0.03775518</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>17.26792536237526</v>
+        <v>17.74854356331612</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2244,13 +2244,13 @@
         <v>0.1</v>
       </c>
       <c r="B12">
-        <v>0.0790780493888015</v>
+        <v>0.0789511209110834</v>
       </c>
       <c r="C12">
-        <v>1449.253236963369</v>
+        <v>1454.135530426318</v>
       </c>
       <c r="D12">
-        <v>1522.573236963369</v>
+        <v>1527.455530426318</v>
       </c>
       <c r="E12">
         <v>-665.0799999999999</v>
@@ -2277,37 +2277,37 @@
         <v>136.125</v>
       </c>
       <c r="M12">
-        <v>8.759014000000002</v>
+        <v>8.521826000000001</v>
       </c>
       <c r="N12">
-        <v>127.365986</v>
+        <v>127.603174</v>
       </c>
       <c r="O12">
-        <v>31.76507690839999</v>
+        <v>31.82423159559999</v>
       </c>
       <c r="P12">
-        <v>95.60090909159997</v>
+        <v>95.77894240439997</v>
       </c>
       <c r="Q12">
-        <v>194.1009090916</v>
+        <v>194.2789424044</v>
       </c>
       <c r="R12">
         <v>0.1111111111111111</v>
       </c>
       <c r="S12">
-        <v>0.08355271932089056</v>
+        <v>0.08352844767898154</v>
       </c>
       <c r="T12">
         <v>0.8713267362351397</v>
       </c>
       <c r="U12">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V12">
         <v>0.2494</v>
       </c>
       <c r="W12">
-        <v>0.03880602</v>
+        <v>0.03775518</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>15.54113282613773</v>
+        <v>15.97368920698451</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2326,13 +2326,13 @@
         <v>0.11</v>
       </c>
       <c r="B13">
-        <v>0.07892120236895074</v>
+        <v>0.07878382136484804</v>
       </c>
       <c r="C13">
-        <v>1439.521454517128</v>
+        <v>1444.941044406228</v>
       </c>
       <c r="D13">
-        <v>1529.783454517128</v>
+        <v>1535.203044406228</v>
       </c>
       <c r="E13">
         <v>-648.138</v>
@@ -2359,37 +2359,37 @@
         <v>136.125</v>
       </c>
       <c r="M13">
-        <v>9.634915400000002</v>
+        <v>9.3740086</v>
       </c>
       <c r="N13">
-        <v>126.4900846</v>
+        <v>126.7509914</v>
       </c>
       <c r="O13">
-        <v>31.54662709923999</v>
+        <v>31.61169725516</v>
       </c>
       <c r="P13">
-        <v>94.94345750075998</v>
+        <v>95.13929414483998</v>
       </c>
       <c r="Q13">
-        <v>193.44345750076</v>
+        <v>193.63929414484</v>
       </c>
       <c r="R13">
         <v>0.1235955056179775</v>
       </c>
       <c r="S13">
-        <v>0.0838792586167986</v>
+        <v>0.0838547770391551</v>
       </c>
       <c r="T13">
         <v>0.8788632110659378</v>
       </c>
       <c r="U13">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V13">
         <v>0.2494</v>
       </c>
       <c r="W13">
-        <v>0.03880602</v>
+        <v>0.03775518</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>14.12830256921612</v>
+        <v>14.52153564271319</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2408,13 +2408,13 @@
         <v>0.12</v>
       </c>
       <c r="B14">
-        <v>0.07876435534910001</v>
+        <v>0.07861652181861267</v>
       </c>
       <c r="C14">
-        <v>1429.858285645993</v>
+        <v>1435.825552472133</v>
       </c>
       <c r="D14">
-        <v>1537.062285645993</v>
+        <v>1543.029552472133</v>
       </c>
       <c r="E14">
         <v>-631.196</v>
@@ -2441,37 +2441,37 @@
         <v>136.125</v>
       </c>
       <c r="M14">
-        <v>10.5108168</v>
+        <v>10.2261912</v>
       </c>
       <c r="N14">
-        <v>125.6141832</v>
+        <v>125.8988088</v>
       </c>
       <c r="O14">
-        <v>31.32817729008</v>
+        <v>31.39916291471999</v>
       </c>
       <c r="P14">
-        <v>94.28600590991998</v>
+        <v>94.49964588527997</v>
       </c>
       <c r="Q14">
-        <v>192.78600590992</v>
+        <v>192.99964588528</v>
       </c>
       <c r="R14">
         <v>0.1363636363636364</v>
       </c>
       <c r="S14">
-        <v>0.08421321926034092</v>
+        <v>0.08418852297569623</v>
       </c>
       <c r="T14">
         <v>0.8865709694156175</v>
       </c>
       <c r="U14">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V14">
         <v>0.2494</v>
       </c>
       <c r="W14">
-        <v>0.03880602</v>
+        <v>0.03775518</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>12.95094402178144</v>
+        <v>13.31140767248709</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2490,13 +2490,13 @@
         <v>0.13</v>
       </c>
       <c r="B15">
-        <v>0.07871484412924926</v>
+        <v>0.07859558927237732</v>
       </c>
       <c r="C15">
-        <v>1415.228367952993</v>
+        <v>1419.868426906965</v>
       </c>
       <c r="D15">
-        <v>1539.374367952993</v>
+        <v>1544.014426906966</v>
       </c>
       <c r="E15">
         <v>-614.254</v>
@@ -2523,37 +2523,37 @@
         <v>136.125</v>
       </c>
       <c r="M15">
-        <v>11.6289888</v>
+        <v>11.4087428</v>
       </c>
       <c r="N15">
-        <v>124.4960112</v>
+        <v>124.7162572</v>
       </c>
       <c r="O15">
-        <v>31.04930519328</v>
+        <v>31.10423454567999</v>
       </c>
       <c r="P15">
-        <v>93.44670600671998</v>
+        <v>93.61202265431999</v>
       </c>
       <c r="Q15">
-        <v>191.94670600672</v>
+        <v>192.11202265432</v>
       </c>
       <c r="R15">
         <v>0.1494252873563219</v>
       </c>
       <c r="S15">
-        <v>0.08455485716005662</v>
+        <v>0.08452994123261762</v>
       </c>
       <c r="T15">
         <v>0.8944559176124165</v>
       </c>
       <c r="U15">
-        <v>0.05280000000000001</v>
+        <v>0.05180000000000001</v>
       </c>
       <c r="V15">
         <v>0.2494</v>
       </c>
       <c r="W15">
-        <v>0.03963168</v>
+        <v>0.03888108</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2561,7 +2561,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>11.705660942764</v>
+        <v>11.93163895324206</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2572,13 +2572,13 @@
         <v>0.14</v>
       </c>
       <c r="B16">
-        <v>0.07856625370939851</v>
+        <v>0.07843954872614199</v>
       </c>
       <c r="C16">
-        <v>1405.267217386384</v>
+        <v>1410.307927692754</v>
       </c>
       <c r="D16">
-        <v>1546.355217386384</v>
+        <v>1551.395927692754</v>
       </c>
       <c r="E16">
         <v>-597.312</v>
@@ -2605,37 +2605,37 @@
         <v>136.125</v>
       </c>
       <c r="M16">
-        <v>12.5235264</v>
+        <v>12.2863384</v>
       </c>
       <c r="N16">
-        <v>123.6014736</v>
+        <v>123.8386616</v>
       </c>
       <c r="O16">
-        <v>30.82620751583999</v>
+        <v>30.88536220303999</v>
       </c>
       <c r="P16">
-        <v>92.77526608415997</v>
+        <v>92.95329939695998</v>
       </c>
       <c r="Q16">
-        <v>191.27526608416</v>
+        <v>191.45329939696</v>
       </c>
       <c r="R16">
         <v>0.1627906976744186</v>
       </c>
       <c r="S16">
-        <v>0.08490444012720758</v>
+        <v>0.08487929944900231</v>
       </c>
       <c r="T16">
         <v>0.9025242366975131</v>
       </c>
       <c r="U16">
-        <v>0.05280000000000001</v>
+        <v>0.05180000000000001</v>
       </c>
       <c r="V16">
         <v>0.2494</v>
       </c>
       <c r="W16">
-        <v>0.03963168</v>
+        <v>0.03888108</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>10.86954230399514</v>
+        <v>11.07937902801049</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2654,13 +2654,13 @@
         <v>0.15</v>
       </c>
       <c r="B17">
-        <v>0.07841766328954775</v>
+        <v>0.07828350817990663</v>
       </c>
       <c r="C17">
-        <v>1395.369669619218</v>
+        <v>1400.818345290131</v>
       </c>
       <c r="D17">
-        <v>1553.399669619218</v>
+        <v>1558.848345290131</v>
       </c>
       <c r="E17">
         <v>-580.37</v>
@@ -2687,37 +2687,37 @@
         <v>136.125</v>
       </c>
       <c r="M17">
-        <v>13.418064</v>
+        <v>13.163934</v>
       </c>
       <c r="N17">
-        <v>122.706936</v>
+        <v>122.961066</v>
       </c>
       <c r="O17">
-        <v>30.60310983839999</v>
+        <v>30.6664898604</v>
       </c>
       <c r="P17">
-        <v>92.10382616159998</v>
+        <v>92.29457613959998</v>
       </c>
       <c r="Q17">
-        <v>190.6038261616</v>
+        <v>190.7945761396</v>
       </c>
       <c r="R17">
         <v>0.1764705882352941</v>
       </c>
       <c r="S17">
-        <v>0.08526224857593853</v>
+        <v>0.08523687785871369</v>
       </c>
       <c r="T17">
         <v>0.9107823985846119</v>
       </c>
       <c r="U17">
-        <v>0.05280000000000001</v>
+        <v>0.05180000000000001</v>
       </c>
       <c r="V17">
         <v>0.2494</v>
       </c>
       <c r="W17">
-        <v>0.03963168</v>
+        <v>0.03888108</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>10.14490615039546</v>
+        <v>10.34075375947646</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2736,13 +2736,13 @@
         <v>0.16</v>
       </c>
       <c r="B18">
-        <v>0.07853328406969701</v>
+        <v>0.07833163083367127</v>
       </c>
       <c r="C18">
-        <v>1372.940738295659</v>
+        <v>1381.570407429976</v>
       </c>
       <c r="D18">
-        <v>1547.912738295659</v>
+        <v>1556.542407429976</v>
       </c>
       <c r="E18">
         <v>-563.428</v>
@@ -2769,37 +2769,37 @@
         <v>136.125</v>
       </c>
       <c r="M18">
-        <v>14.90896</v>
+        <v>14.502352</v>
       </c>
       <c r="N18">
-        <v>121.21604</v>
+        <v>121.622648</v>
       </c>
       <c r="O18">
-        <v>30.23128037599999</v>
+        <v>30.33268841119999</v>
       </c>
       <c r="P18">
-        <v>90.98475962399996</v>
+        <v>91.28995958879997</v>
       </c>
       <c r="Q18">
-        <v>189.484759624</v>
+        <v>189.7899595888</v>
       </c>
       <c r="R18">
         <v>0.1904761904761905</v>
       </c>
       <c r="S18">
-        <v>0.08562857627344882</v>
+        <v>0.08560297004008485</v>
       </c>
       <c r="T18">
         <v>0.9192371833737844</v>
       </c>
       <c r="U18">
-        <v>0.05500000000000001</v>
+        <v>0.05350000000000001</v>
       </c>
       <c r="V18">
         <v>0.2494</v>
       </c>
       <c r="W18">
-        <v>0.041283</v>
+        <v>0.0401571</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>9.130415535355917</v>
+        <v>9.38640849429113</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2818,13 +2818,13 @@
         <v>0.17</v>
       </c>
       <c r="B19">
-        <v>0.07840120684984626</v>
+        <v>0.07818835048743593</v>
       </c>
       <c r="C19">
-        <v>1362.269794823942</v>
+        <v>1371.514276321418</v>
       </c>
       <c r="D19">
-        <v>1554.183794823942</v>
+        <v>1563.428276321418</v>
       </c>
       <c r="E19">
         <v>-546.486</v>
@@ -2851,37 +2851,37 @@
         <v>136.125</v>
       </c>
       <c r="M19">
-        <v>15.84077</v>
+        <v>15.408749</v>
       </c>
       <c r="N19">
-        <v>120.28423</v>
+        <v>120.716251</v>
       </c>
       <c r="O19">
-        <v>29.99888696199999</v>
+        <v>30.1066329994</v>
       </c>
       <c r="P19">
-        <v>90.28534303799998</v>
+        <v>90.60961800059998</v>
       </c>
       <c r="Q19">
-        <v>188.785343038</v>
+        <v>189.1096180006</v>
       </c>
       <c r="R19">
         <v>0.2048192771084338</v>
       </c>
       <c r="S19">
-        <v>0.08600373114439309</v>
+        <v>0.08597788371980233</v>
       </c>
       <c r="T19">
         <v>0.9278956979169131</v>
       </c>
       <c r="U19">
-        <v>0.05500000000000001</v>
+        <v>0.05350000000000001</v>
       </c>
       <c r="V19">
         <v>0.2494</v>
       </c>
       <c r="W19">
-        <v>0.041283</v>
+        <v>0.0401571</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>8.593332268570276</v>
+        <v>8.834266818156358</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2900,13 +2900,13 @@
         <v>0.18</v>
       </c>
       <c r="B20">
-        <v>0.07826912962999551</v>
+        <v>0.07804507014120057</v>
       </c>
       <c r="C20">
-        <v>1351.649869887137</v>
+        <v>1361.519339663645</v>
       </c>
       <c r="D20">
-        <v>1560.505869887137</v>
+        <v>1570.375339663645</v>
       </c>
       <c r="E20">
         <v>-529.544</v>
@@ -2933,37 +2933,37 @@
         <v>136.125</v>
       </c>
       <c r="M20">
-        <v>16.77258</v>
+        <v>16.315146</v>
       </c>
       <c r="N20">
-        <v>119.35242</v>
+        <v>119.809854</v>
       </c>
       <c r="O20">
-        <v>29.76649354799999</v>
+        <v>29.88057758759999</v>
       </c>
       <c r="P20">
-        <v>89.58592645199997</v>
+        <v>89.92927641239999</v>
       </c>
       <c r="Q20">
-        <v>188.085926452</v>
+        <v>188.4292764124</v>
       </c>
       <c r="R20">
         <v>0.2195121951219512</v>
       </c>
       <c r="S20">
-        <v>0.08638803613414087</v>
+        <v>0.08636194163561045</v>
       </c>
       <c r="T20">
         <v>0.9367653957415812</v>
       </c>
       <c r="U20">
-        <v>0.05500000000000001</v>
+        <v>0.05350000000000001</v>
       </c>
       <c r="V20">
         <v>0.2494</v>
       </c>
       <c r="W20">
-        <v>0.041283</v>
+        <v>0.0401571</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>8.11592492031637</v>
+        <v>8.343474217147671</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2982,13 +2982,13 @@
         <v>0.19</v>
       </c>
       <c r="B21">
-        <v>0.07835097341014477</v>
+        <v>0.07790178979496522</v>
       </c>
       <c r="C21">
-        <v>1330.784248380418</v>
+        <v>1351.58641684668</v>
       </c>
       <c r="D21">
-        <v>1556.582248380418</v>
+        <v>1577.38441684668</v>
       </c>
       <c r="E21">
         <v>-512.602</v>
@@ -3015,45 +3015,45 @@
         <v>136.125</v>
       </c>
       <c r="M21">
-        <v>18.187237</v>
+        <v>17.221543</v>
       </c>
       <c r="N21">
-        <v>117.937763</v>
+        <v>118.903457</v>
       </c>
       <c r="O21">
-        <v>29.41367809219999</v>
+        <v>29.65452217579999</v>
       </c>
       <c r="P21">
-        <v>88.52408490779997</v>
+        <v>89.24893482419998</v>
       </c>
       <c r="Q21">
-        <v>187.0240849078</v>
+        <v>187.7489348242</v>
       </c>
       <c r="R21">
         <v>0.2345679012345679</v>
       </c>
       <c r="S21">
-        <v>0.08678183013598119</v>
+        <v>0.08675548246292003</v>
       </c>
       <c r="T21">
         <v>0.9458540984508091</v>
       </c>
       <c r="U21">
-        <v>0.05650000000000001</v>
+        <v>0.05350000000000001</v>
       </c>
       <c r="V21">
         <v>0.2494</v>
       </c>
       <c r="W21">
-        <v>0.0424089</v>
+        <v>0.0401571</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y21">
-        <v>7.484644314031864</v>
+        <v>7.90434399519253</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3064,13 +3064,13 @@
         <v>0.2</v>
       </c>
       <c r="B22">
-        <v>0.07823015519029401</v>
+        <v>0.07787860544872988</v>
       </c>
       <c r="C22">
-        <v>1319.641280028497</v>
+        <v>1335.784448526824</v>
       </c>
       <c r="D22">
-        <v>1562.381280028497</v>
+        <v>1578.524448526824</v>
       </c>
       <c r="E22">
         <v>-495.66</v>
@@ -3097,37 +3097,37 @@
         <v>136.125</v>
       </c>
       <c r="M22">
-        <v>19.14446000000001</v>
+        <v>18.39901200000001</v>
       </c>
       <c r="N22">
-        <v>116.98054</v>
+        <v>117.725988</v>
       </c>
       <c r="O22">
-        <v>29.17494667599999</v>
+        <v>29.36086140719999</v>
       </c>
       <c r="P22">
-        <v>87.80559332399997</v>
+        <v>88.36512659279998</v>
       </c>
       <c r="Q22">
-        <v>186.305593324</v>
+        <v>186.8651265928</v>
       </c>
       <c r="R22">
         <v>0.25</v>
       </c>
       <c r="S22">
-        <v>0.08718546898786753</v>
+        <v>0.08715886181091234</v>
       </c>
       <c r="T22">
         <v>0.955170018727768</v>
       </c>
       <c r="U22">
-        <v>0.05650000000000001</v>
+        <v>0.05430000000000001</v>
       </c>
       <c r="V22">
         <v>0.2494</v>
       </c>
       <c r="W22">
-        <v>0.0424089</v>
+        <v>0.04075758</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>7.11041209833027</v>
+        <v>7.398495093106082</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3146,13 +3146,13 @@
         <v>0.21</v>
       </c>
       <c r="B23">
-        <v>0.07810933697044327</v>
+        <v>0.07774132990249452</v>
       </c>
       <c r="C23">
-        <v>1308.541681720424</v>
+        <v>1325.626536934504</v>
       </c>
       <c r="D23">
-        <v>1568.223681720424</v>
+        <v>1585.308536934504</v>
       </c>
       <c r="E23">
         <v>-478.718</v>
@@ -3179,37 +3179,37 @@
         <v>136.125</v>
       </c>
       <c r="M23">
-        <v>20.101683</v>
+        <v>19.3189626</v>
       </c>
       <c r="N23">
-        <v>116.023317</v>
+        <v>116.8060374</v>
       </c>
       <c r="O23">
-        <v>28.93621525979999</v>
+        <v>29.13142572755999</v>
       </c>
       <c r="P23">
-        <v>87.08710174019997</v>
+        <v>87.67461167243997</v>
       </c>
       <c r="Q23">
-        <v>185.5871017402</v>
+        <v>186.17461167244</v>
       </c>
       <c r="R23">
         <v>0.2658227848101266</v>
       </c>
       <c r="S23">
-        <v>0.08759932654486489</v>
+        <v>0.08757245329429686</v>
       </c>
       <c r="T23">
         <v>0.9647217850876876</v>
       </c>
       <c r="U23">
-        <v>0.05650000000000001</v>
+        <v>0.05430000000000001</v>
       </c>
       <c r="V23">
         <v>0.2494</v>
       </c>
       <c r="W23">
-        <v>0.0424089</v>
+        <v>0.04075758</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>6.771821046028831</v>
+        <v>7.046185802958175</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3228,13 +3228,13 @@
         <v>0.22</v>
       </c>
       <c r="B24">
-        <v>0.07798851875059253</v>
+        <v>0.07760405435625918</v>
       </c>
       <c r="C24">
-        <v>1297.48594181898</v>
+        <v>1315.527189538523</v>
       </c>
       <c r="D24">
-        <v>1574.10994181898</v>
+        <v>1592.151189538523</v>
       </c>
       <c r="E24">
         <v>-461.776</v>
@@ -3261,37 +3261,37 @@
         <v>136.125</v>
       </c>
       <c r="M24">
-        <v>21.058906</v>
+        <v>20.2389132</v>
       </c>
       <c r="N24">
-        <v>115.066094</v>
+        <v>115.8860868</v>
       </c>
       <c r="O24">
-        <v>28.69748384359999</v>
+        <v>28.90199004791999</v>
       </c>
       <c r="P24">
-        <v>86.36861015639997</v>
+        <v>86.98409675207998</v>
       </c>
       <c r="Q24">
-        <v>184.8686101564</v>
+        <v>185.48409675208</v>
       </c>
       <c r="R24">
         <v>0.282051282051282</v>
       </c>
       <c r="S24">
-        <v>0.08802379583409298</v>
+        <v>0.08799664968751175</v>
       </c>
       <c r="T24">
         <v>0.9745184685337591</v>
       </c>
       <c r="U24">
-        <v>0.05650000000000001</v>
+        <v>0.05430000000000001</v>
       </c>
       <c r="V24">
         <v>0.2494</v>
       </c>
       <c r="W24">
-        <v>0.0424089</v>
+        <v>0.04075758</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>6.464010998482065</v>
+        <v>6.72590463009644</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3310,13 +3310,13 @@
         <v>0.23</v>
       </c>
       <c r="B25">
-        <v>0.07786770053074178</v>
+        <v>0.07746677881002381</v>
       </c>
       <c r="C25">
-        <v>1286.474556046764</v>
+        <v>1305.487167966591</v>
       </c>
       <c r="D25">
-        <v>1580.040556046764</v>
+        <v>1599.053167966591</v>
       </c>
       <c r="E25">
         <v>-444.8339999999999</v>
@@ -3343,37 +3343,37 @@
         <v>136.125</v>
       </c>
       <c r="M25">
-        <v>22.01612900000001</v>
+        <v>21.15886380000001</v>
       </c>
       <c r="N25">
-        <v>114.108871</v>
+        <v>114.9661362</v>
       </c>
       <c r="O25">
-        <v>28.45875242739999</v>
+        <v>28.67255436827999</v>
       </c>
       <c r="P25">
-        <v>85.65011857259998</v>
+        <v>86.29358183171998</v>
       </c>
       <c r="Q25">
-        <v>184.1501185726</v>
+        <v>184.79358183172</v>
       </c>
       <c r="R25">
         <v>0.2987012987012987</v>
       </c>
       <c r="S25">
-        <v>0.08845929029966465</v>
+        <v>0.0884318641688621</v>
       </c>
       <c r="T25">
         <v>0.9845696112901181</v>
       </c>
       <c r="U25">
-        <v>0.05650000000000001</v>
+        <v>0.05430000000000001</v>
       </c>
       <c r="V25">
         <v>0.2494</v>
       </c>
       <c r="W25">
-        <v>0.0424089</v>
+        <v>0.04075758</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>6.182967042026323</v>
+        <v>6.433473994005289</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3392,13 +3392,13 @@
         <v>0.24</v>
       </c>
       <c r="B26">
-        <v>0.07799908391089103</v>
+        <v>0.07732950326378847</v>
       </c>
       <c r="C26">
-        <v>1263.085445017121</v>
+        <v>1295.507247110542</v>
       </c>
       <c r="D26">
-        <v>1573.593445017121</v>
+        <v>1606.015247110543</v>
       </c>
       <c r="E26">
         <v>-427.892</v>
@@ -3425,45 +3425,45 @@
         <v>136.125</v>
       </c>
       <c r="M26">
-        <v>23.5426032</v>
+        <v>22.0788144</v>
       </c>
       <c r="N26">
-        <v>112.5823968</v>
+        <v>114.0461856</v>
       </c>
       <c r="O26">
-        <v>28.07804976191999</v>
+        <v>28.44311868863999</v>
       </c>
       <c r="P26">
-        <v>84.50434703807997</v>
+        <v>85.60306691135997</v>
       </c>
       <c r="Q26">
-        <v>183.00434703808</v>
+        <v>184.10306691136</v>
       </c>
       <c r="R26">
         <v>0.3157894736842105</v>
       </c>
       <c r="S26">
-        <v>0.08890624514590924</v>
+        <v>0.08887853166287957</v>
       </c>
       <c r="T26">
         <v>0.9948852578032233</v>
       </c>
       <c r="U26">
-        <v>0.05790000000000001</v>
+        <v>0.05430000000000001</v>
       </c>
       <c r="V26">
         <v>0.2494</v>
       </c>
       <c r="W26">
-        <v>0.04345974</v>
+        <v>0.04075758</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y26">
-        <v>5.782070862919695</v>
+        <v>6.165412577588404</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3474,13 +3474,13 @@
         <v>0.25</v>
       </c>
       <c r="B27">
-        <v>0.07788877409104028</v>
+        <v>0.07737987771755311</v>
       </c>
       <c r="C27">
-        <v>1251.552900951638</v>
+        <v>1276.003421458953</v>
       </c>
       <c r="D27">
-        <v>1579.002900951638</v>
+        <v>1603.453421458953</v>
       </c>
       <c r="E27">
         <v>-410.95</v>
@@ -3507,37 +3507,37 @@
         <v>136.125</v>
       </c>
       <c r="M27">
-        <v>24.523545</v>
+        <v>23.422315</v>
       </c>
       <c r="N27">
-        <v>111.601455</v>
+        <v>112.702685</v>
       </c>
       <c r="O27">
-        <v>27.83340287699999</v>
+        <v>28.10804963899999</v>
       </c>
       <c r="P27">
-        <v>83.76805212299998</v>
+        <v>84.59463536099997</v>
       </c>
       <c r="Q27">
-        <v>182.268052123</v>
+        <v>183.094635361</v>
       </c>
       <c r="R27">
         <v>0.3333333333333333</v>
       </c>
       <c r="S27">
-        <v>0.0893651187880537</v>
+        <v>0.08933711029007083</v>
       </c>
       <c r="T27">
         <v>1.005475988223345</v>
       </c>
       <c r="U27">
-        <v>0.05790000000000001</v>
+        <v>0.05530000000000001</v>
       </c>
       <c r="V27">
         <v>0.2494</v>
       </c>
       <c r="W27">
-        <v>0.04345974</v>
+        <v>0.04150818000000001</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3545,7 +3545,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>5.550788028402907</v>
+        <v>5.811765404060186</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3556,13 +3556,13 @@
         <v>0.26</v>
       </c>
       <c r="B28">
-        <v>0.07777846427118952</v>
+        <v>0.07725010817131775</v>
       </c>
       <c r="C28">
-        <v>1240.057676758965</v>
+        <v>1265.677596569665</v>
       </c>
       <c r="D28">
-        <v>1584.449676758965</v>
+        <v>1610.069596569665</v>
       </c>
       <c r="E28">
         <v>-394.008</v>
@@ -3589,37 +3589,37 @@
         <v>136.125</v>
       </c>
       <c r="M28">
-        <v>25.50448680000001</v>
+        <v>24.3592076</v>
       </c>
       <c r="N28">
-        <v>110.6205132</v>
+        <v>111.7657924</v>
       </c>
       <c r="O28">
-        <v>27.58875599207999</v>
+        <v>27.87438862455999</v>
       </c>
       <c r="P28">
-        <v>83.03175720791997</v>
+        <v>83.89140377543997</v>
       </c>
       <c r="Q28">
-        <v>181.53175720792</v>
+        <v>182.39140377544</v>
       </c>
       <c r="R28">
         <v>0.3513513513513514</v>
       </c>
       <c r="S28">
-        <v>0.08983639442052638</v>
+        <v>0.08980808293421319</v>
       </c>
       <c r="T28">
         <v>1.016352954600767</v>
       </c>
       <c r="U28">
-        <v>0.05790000000000001</v>
+        <v>0.05530000000000001</v>
       </c>
       <c r="V28">
         <v>0.2494</v>
       </c>
       <c r="W28">
-        <v>0.04345974</v>
+        <v>0.04150818000000001</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3627,7 +3627,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>5.33729618115664</v>
+        <v>5.588235965442486</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3638,13 +3638,13 @@
         <v>0.27</v>
       </c>
       <c r="B29">
-        <v>0.07766815445133879</v>
+        <v>0.07712033862508241</v>
       </c>
       <c r="C29">
-        <v>1228.600159981008</v>
+        <v>1255.406597271645</v>
       </c>
       <c r="D29">
-        <v>1589.934159981008</v>
+        <v>1616.740597271645</v>
       </c>
       <c r="E29">
         <v>-377.066</v>
@@ -3671,37 +3671,37 @@
         <v>136.125</v>
       </c>
       <c r="M29">
-        <v>26.48542860000001</v>
+        <v>25.29610020000001</v>
       </c>
       <c r="N29">
-        <v>109.6395714</v>
+        <v>110.8288998</v>
       </c>
       <c r="O29">
-        <v>27.34410910715999</v>
+        <v>27.64072761011999</v>
       </c>
       <c r="P29">
-        <v>82.29546229283997</v>
+        <v>83.18817218987996</v>
       </c>
       <c r="Q29">
-        <v>180.79546229284</v>
+        <v>181.68817218988</v>
       </c>
       <c r="R29">
         <v>0.3698630136986302</v>
       </c>
       <c r="S29">
-        <v>0.09032058171416271</v>
+        <v>0.09029195893846906</v>
       </c>
       <c r="T29">
         <v>1.027527920057022</v>
       </c>
       <c r="U29">
-        <v>0.05790000000000001</v>
+        <v>0.05530000000000001</v>
       </c>
       <c r="V29">
         <v>0.2494</v>
       </c>
       <c r="W29">
-        <v>0.04345974</v>
+        <v>0.04150818000000001</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>5.139618544817505</v>
+        <v>5.38126426301869</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3720,13 +3720,13 @@
         <v>0.28</v>
       </c>
       <c r="B30">
-        <v>0.07755784463148804</v>
+        <v>0.07699056907884706</v>
       </c>
       <c r="C30">
-        <v>1217.180743544131</v>
+        <v>1245.191107876752</v>
       </c>
       <c r="D30">
-        <v>1595.456743544131</v>
+        <v>1623.467107876752</v>
       </c>
       <c r="E30">
         <v>-360.124</v>
@@ -3753,37 +3753,37 @@
         <v>136.125</v>
       </c>
       <c r="M30">
-        <v>27.46637040000001</v>
+        <v>26.23299280000001</v>
       </c>
       <c r="N30">
-        <v>108.6586296</v>
+        <v>109.8920072</v>
       </c>
       <c r="O30">
-        <v>27.09946222223999</v>
+        <v>27.40706659567999</v>
       </c>
       <c r="P30">
-        <v>81.55916737775998</v>
+        <v>82.48494060431997</v>
       </c>
       <c r="Q30">
-        <v>180.05916737776</v>
+        <v>180.98494060432</v>
       </c>
       <c r="R30">
         <v>0.388888888888889</v>
       </c>
       <c r="S30">
-        <v>0.09081821865484449</v>
+        <v>0.09078927594284314</v>
       </c>
       <c r="T30">
         <v>1.039013301220396</v>
       </c>
       <c r="U30">
-        <v>0.05790000000000001</v>
+        <v>0.05530000000000001</v>
       </c>
       <c r="V30">
         <v>0.2494</v>
       </c>
       <c r="W30">
-        <v>0.04345974</v>
+        <v>0.04150818000000001</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>4.956060739645451</v>
+        <v>5.189076253625165</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3802,13 +3802,13 @@
         <v>0.29</v>
       </c>
       <c r="B31">
-        <v>0.07744753481163727</v>
+        <v>0.07686079953261171</v>
       </c>
       <c r="C31">
-        <v>1205.799825852991</v>
+        <v>1235.031824132848</v>
       </c>
       <c r="D31">
-        <v>1601.017825852991</v>
+        <v>1630.249824132848</v>
       </c>
       <c r="E31">
         <v>-343.182</v>
@@ -3835,37 +3835,37 @@
         <v>136.125</v>
       </c>
       <c r="M31">
-        <v>28.4473122</v>
+        <v>27.1698854</v>
       </c>
       <c r="N31">
-        <v>107.6776878</v>
+        <v>108.9551146</v>
       </c>
       <c r="O31">
-        <v>26.85481533731999</v>
+        <v>27.17340558123999</v>
       </c>
       <c r="P31">
-        <v>80.82287246267998</v>
+        <v>81.78170901875998</v>
       </c>
       <c r="Q31">
-        <v>179.32287246268</v>
+        <v>180.28170901876</v>
       </c>
       <c r="R31">
         <v>0.4084507042253521</v>
       </c>
       <c r="S31">
-        <v>0.09132987353751729</v>
+        <v>0.09130060187691791</v>
       </c>
       <c r="T31">
         <v>1.050822214247527</v>
       </c>
       <c r="U31">
-        <v>0.05790000000000001</v>
+        <v>0.05530000000000001</v>
       </c>
       <c r="V31">
         <v>0.2494</v>
       </c>
       <c r="W31">
-        <v>0.04345974</v>
+        <v>0.04150818000000001</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>4.785162093450782</v>
+        <v>5.010142589707058</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3884,13 +3884,13 @@
         <v>0.3</v>
       </c>
       <c r="B32">
-        <v>0.07733722499178652</v>
+        <v>0.07673102998637636</v>
       </c>
       <c r="C32">
-        <v>1194.45781088635</v>
+        <v>1224.929453463691</v>
       </c>
       <c r="D32">
-        <v>1606.61781088635</v>
+        <v>1637.089453463691</v>
       </c>
       <c r="E32">
         <v>-326.24</v>
@@ -3917,37 +3917,37 @@
         <v>136.125</v>
       </c>
       <c r="M32">
-        <v>29.428254</v>
+        <v>28.10677800000001</v>
       </c>
       <c r="N32">
-        <v>106.696746</v>
+        <v>108.018222</v>
       </c>
       <c r="O32">
-        <v>26.61016845239999</v>
+        <v>26.93974456679999</v>
       </c>
       <c r="P32">
-        <v>80.08657754759997</v>
+        <v>81.07847743319998</v>
       </c>
       <c r="Q32">
-        <v>178.5865775476</v>
+        <v>179.5784774332</v>
       </c>
       <c r="R32">
         <v>0.4285714285714286</v>
       </c>
       <c r="S32">
-        <v>0.09185614713112361</v>
+        <v>0.09182653712339481</v>
       </c>
       <c r="T32">
         <v>1.062968524789718</v>
       </c>
       <c r="U32">
-        <v>0.05790000000000001</v>
+        <v>0.05530000000000001</v>
       </c>
       <c r="V32">
         <v>0.2494</v>
       </c>
       <c r="W32">
-        <v>0.04345974</v>
+        <v>0.04150818000000001</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>4.625656690335756</v>
+        <v>4.843137836716821</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3966,13 +3966,13 @@
         <v>0.31</v>
       </c>
       <c r="B33">
-        <v>0.07783189877193579</v>
+        <v>0.076601260440141</v>
       </c>
       <c r="C33">
-        <v>1152.704552851825</v>
+        <v>1214.884715214895</v>
       </c>
       <c r="D33">
-        <v>1581.806552851825</v>
+        <v>1643.986715214895</v>
       </c>
       <c r="E33">
         <v>-309.298</v>
@@ -3999,45 +3999,45 @@
         <v>136.125</v>
       </c>
       <c r="M33">
-        <v>31.774721</v>
+        <v>29.04367060000001</v>
       </c>
       <c r="N33">
-        <v>104.350279</v>
+        <v>107.0813294</v>
       </c>
       <c r="O33">
-        <v>26.02495958259999</v>
+        <v>26.70608355235999</v>
       </c>
       <c r="P33">
-        <v>78.32531941739998</v>
+        <v>80.37524584763997</v>
       </c>
       <c r="Q33">
-        <v>176.8253194174</v>
+        <v>178.87524584764</v>
       </c>
       <c r="R33">
         <v>0.4492753623188406</v>
       </c>
       <c r="S33">
-        <v>0.092397675031791</v>
+        <v>0.09236771686976958</v>
       </c>
       <c r="T33">
         <v>1.075466902304147</v>
       </c>
       <c r="U33">
-        <v>0.06050000000000001</v>
+        <v>0.05530000000000001</v>
       </c>
       <c r="V33">
         <v>0.2494</v>
       </c>
       <c r="W33">
-        <v>0.0454113</v>
+        <v>0.04150818000000001</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y33">
-        <v>4.284065940342952</v>
+        <v>4.686907583919504</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4048,13 +4048,13 @@
         <v>0.32</v>
       </c>
       <c r="B34">
-        <v>0.07774110455208504</v>
+        <v>0.07647149089390566</v>
       </c>
       <c r="C34">
-        <v>1140.25891870814</v>
+        <v>1204.898340906138</v>
       </c>
       <c r="D34">
-        <v>1586.30291870814</v>
+        <v>1650.942340906138</v>
       </c>
       <c r="E34">
         <v>-292.356</v>
@@ -4081,45 +4081,45 @@
         <v>136.125</v>
       </c>
       <c r="M34">
-        <v>32.79971200000001</v>
+        <v>29.98056320000001</v>
       </c>
       <c r="N34">
-        <v>103.325288</v>
+        <v>106.1444368</v>
       </c>
       <c r="O34">
-        <v>25.76932682719999</v>
+        <v>26.47242253791999</v>
       </c>
       <c r="P34">
-        <v>77.55596117279998</v>
+        <v>79.67201426207997</v>
       </c>
       <c r="Q34">
-        <v>176.0559611728</v>
+        <v>178.17201426208</v>
       </c>
       <c r="R34">
         <v>0.4705882352941177</v>
       </c>
       <c r="S34">
-        <v>0.09295513022365447</v>
+        <v>0.09292481366750832</v>
       </c>
       <c r="T34">
         <v>1.088332879157236</v>
       </c>
       <c r="U34">
-        <v>0.06050000000000001</v>
+        <v>0.05530000000000001</v>
       </c>
       <c r="V34">
         <v>0.2494</v>
       </c>
       <c r="W34">
-        <v>0.0454113</v>
+        <v>0.04150818000000001</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y34">
-        <v>4.150188879707235</v>
+        <v>4.54044172192202</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4130,13 +4130,13 @@
         <v>0.33</v>
       </c>
       <c r="B35">
-        <v>0.07765031033223428</v>
+        <v>0.0769609663476703</v>
       </c>
       <c r="C35">
-        <v>1127.83891973258</v>
+        <v>1162.023391894282</v>
       </c>
       <c r="D35">
-        <v>1590.82491973258</v>
+        <v>1625.009391894282</v>
       </c>
       <c r="E35">
         <v>-275.414</v>
@@ -4163,37 +4163,37 @@
         <v>136.125</v>
       </c>
       <c r="M35">
-        <v>33.82470300000001</v>
+        <v>32.3151708</v>
       </c>
       <c r="N35">
-        <v>102.300297</v>
+        <v>103.8098292</v>
       </c>
       <c r="O35">
-        <v>25.51369407179999</v>
+        <v>25.89017140247999</v>
       </c>
       <c r="P35">
-        <v>76.78660292819998</v>
+        <v>77.91965779751997</v>
       </c>
       <c r="Q35">
-        <v>175.2866029282</v>
+        <v>176.41965779752</v>
       </c>
       <c r="R35">
         <v>0.4925373134328359</v>
       </c>
       <c r="S35">
-        <v>0.0935292258690064</v>
+        <v>0.09349854022040344</v>
       </c>
       <c r="T35">
         <v>1.101582915020865</v>
       </c>
       <c r="U35">
-        <v>0.06050000000000001</v>
+        <v>0.0578</v>
       </c>
       <c r="V35">
         <v>0.2494</v>
       </c>
       <c r="W35">
-        <v>0.0454113</v>
+        <v>0.04338468</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>4.024425580322167</v>
+        <v>4.212417778710919</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4212,13 +4212,13 @@
         <v>0.34</v>
       </c>
       <c r="B36">
-        <v>0.07824856691238352</v>
+        <v>0.07684996180143494</v>
       </c>
       <c r="C36">
-        <v>1081.566765378916</v>
+        <v>1150.890849288432</v>
       </c>
       <c r="D36">
-        <v>1561.494765378916</v>
+        <v>1630.818849288432</v>
       </c>
       <c r="E36">
         <v>-258.472</v>
@@ -4245,45 +4245,45 @@
         <v>136.125</v>
       </c>
       <c r="M36">
-        <v>36.40496960000001</v>
+        <v>33.2944184</v>
       </c>
       <c r="N36">
-        <v>99.72003039999996</v>
+        <v>102.8305816</v>
       </c>
       <c r="O36">
-        <v>24.87017558175999</v>
+        <v>25.64594705103999</v>
       </c>
       <c r="P36">
-        <v>74.84985481823996</v>
+        <v>77.18463454895996</v>
       </c>
       <c r="Q36">
-        <v>173.34985481824</v>
+        <v>175.68463454896</v>
       </c>
       <c r="R36">
         <v>0.5151515151515152</v>
       </c>
       <c r="S36">
-        <v>0.09412071835209626</v>
+        <v>0.09408965242641659</v>
       </c>
       <c r="T36">
         <v>1.115234467122785</v>
       </c>
       <c r="U36">
-        <v>0.06320000000000001</v>
+        <v>0.0578</v>
       </c>
       <c r="V36">
         <v>0.2494</v>
       </c>
       <c r="W36">
-        <v>0.04743792</v>
+        <v>0.04338468</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y36">
-        <v>3.739187300406369</v>
+        <v>4.088523138160598</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4294,13 +4294,13 @@
         <v>0.35</v>
       </c>
       <c r="B37">
-        <v>0.07817803889253278</v>
+        <v>0.07765844225519959</v>
       </c>
       <c r="C37">
-        <v>1068.026118196331</v>
+        <v>1092.563110691452</v>
       </c>
       <c r="D37">
-        <v>1564.896118196331</v>
+        <v>1589.433110691453</v>
       </c>
       <c r="E37">
         <v>-241.53</v>
@@ -4327,37 +4327,37 @@
         <v>136.125</v>
       </c>
       <c r="M37">
-        <v>37.47570400000001</v>
+        <v>36.34906100000001</v>
       </c>
       <c r="N37">
-        <v>98.64929599999996</v>
+        <v>99.77593899999997</v>
       </c>
       <c r="O37">
-        <v>24.60313442239999</v>
+        <v>24.88411918659999</v>
       </c>
       <c r="P37">
-        <v>74.04616157759997</v>
+        <v>74.89181981339998</v>
       </c>
       <c r="Q37">
-        <v>172.5461615776</v>
+        <v>173.3918198134</v>
       </c>
       <c r="R37">
         <v>0.5384615384615385</v>
       </c>
       <c r="S37">
-        <v>0.0947304106038966</v>
+        <v>0.09469895270030708</v>
       </c>
       <c r="T37">
         <v>1.129306066981688</v>
       </c>
       <c r="U37">
-        <v>0.06320000000000001</v>
+        <v>0.06130000000000001</v>
       </c>
       <c r="V37">
         <v>0.2494</v>
       </c>
       <c r="W37">
-        <v>0.04743792</v>
+        <v>0.04601178</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4365,7 +4365,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>3.632353377537616</v>
+        <v>3.744938555634214</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4376,13 +4376,13 @@
         <v>0.36</v>
       </c>
       <c r="B38">
-        <v>0.07810751087268204</v>
+        <v>0.07757370870896424</v>
       </c>
       <c r="C38">
-        <v>1054.500321472511</v>
+        <v>1079.859781889907</v>
       </c>
       <c r="D38">
-        <v>1568.312321472511</v>
+        <v>1593.671781889907</v>
       </c>
       <c r="E38">
         <v>-224.588</v>
@@ -4409,37 +4409,37 @@
         <v>136.125</v>
       </c>
       <c r="M38">
-        <v>38.54643840000001</v>
+        <v>37.38760560000001</v>
       </c>
       <c r="N38">
-        <v>97.57856159999997</v>
+        <v>98.73739439999997</v>
       </c>
       <c r="O38">
-        <v>24.33609326304</v>
+        <v>24.62510616335999</v>
       </c>
       <c r="P38">
-        <v>73.24246833695997</v>
+        <v>74.11228823663998</v>
       </c>
       <c r="Q38">
-        <v>171.74246833696</v>
+        <v>172.61228823664</v>
       </c>
       <c r="R38">
         <v>0.5625</v>
       </c>
       <c r="S38">
-        <v>0.09535915573856568</v>
+        <v>0.09532729360775663</v>
       </c>
       <c r="T38">
         <v>1.143817404336181</v>
       </c>
       <c r="U38">
-        <v>0.06320000000000001</v>
+        <v>0.06130000000000001</v>
       </c>
       <c r="V38">
         <v>0.2494</v>
       </c>
       <c r="W38">
-        <v>0.04743792</v>
+        <v>0.04601178</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>3.531454672606016</v>
+        <v>3.640912484644375</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4458,13 +4458,13 @@
         <v>0.37</v>
       </c>
       <c r="B39">
-        <v>0.0793422762528313</v>
+        <v>0.0774889751627289</v>
       </c>
       <c r="C39">
-        <v>979.82527601015</v>
+        <v>1067.179120760012</v>
       </c>
       <c r="D39">
-        <v>1510.57927601015</v>
+        <v>1597.933120760012</v>
       </c>
       <c r="E39">
         <v>-207.646</v>
@@ -4491,45 +4491,45 @@
         <v>136.125</v>
       </c>
       <c r="M39">
-        <v>42.56338660000002</v>
+        <v>38.42615020000001</v>
       </c>
       <c r="N39">
-        <v>93.56161339999996</v>
+        <v>97.69884979999996</v>
       </c>
       <c r="O39">
-        <v>23.33426638195999</v>
+        <v>24.36609314011999</v>
       </c>
       <c r="P39">
-        <v>70.22734701803996</v>
+        <v>73.33275665987998</v>
       </c>
       <c r="Q39">
-        <v>168.7273470180399</v>
+        <v>171.83275665988</v>
       </c>
       <c r="R39">
         <v>0.5873015873015873</v>
       </c>
       <c r="S39">
-        <v>0.09600786103624015</v>
+        <v>0.09597558184560143</v>
       </c>
       <c r="T39">
         <v>1.158789419067008</v>
       </c>
       <c r="U39">
-        <v>0.06790000000000002</v>
+        <v>0.06130000000000001</v>
       </c>
       <c r="V39">
         <v>0.2494</v>
       </c>
       <c r="W39">
-        <v>0.05096574000000001</v>
+        <v>0.04601178</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y39">
-        <v>3.19817126581746</v>
+        <v>3.542509444518851</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4540,13 +4540,13 @@
         <v>0.38</v>
       </c>
       <c r="B40">
-        <v>0.07930702643298054</v>
+        <v>0.07820288001649355</v>
       </c>
       <c r="C40">
-        <v>964.4724247057572</v>
+        <v>1015.031231335332</v>
       </c>
       <c r="D40">
-        <v>1512.168424705757</v>
+        <v>1562.727231335332</v>
       </c>
       <c r="E40">
         <v>-190.704</v>
@@ -4573,37 +4573,37 @@
         <v>136.125</v>
       </c>
       <c r="M40">
-        <v>43.71374840000001</v>
+        <v>41.2673236</v>
       </c>
       <c r="N40">
-        <v>92.41125159999996</v>
+        <v>94.85767639999997</v>
       </c>
       <c r="O40">
-        <v>23.04736614903999</v>
+        <v>23.65750449415999</v>
       </c>
       <c r="P40">
-        <v>69.36388545095997</v>
+        <v>71.20017190583998</v>
       </c>
       <c r="Q40">
-        <v>167.86388545096</v>
+        <v>169.70017190584</v>
       </c>
       <c r="R40">
         <v>0.6129032258064516</v>
       </c>
       <c r="S40">
-        <v>0.09667749231125894</v>
+        <v>0.09664478260724765</v>
       </c>
       <c r="T40">
         <v>1.174244402014957</v>
       </c>
       <c r="U40">
-        <v>0.06790000000000002</v>
+        <v>0.0641</v>
       </c>
       <c r="V40">
         <v>0.2494</v>
       </c>
       <c r="W40">
-        <v>0.05096574000000001</v>
+        <v>0.04811346</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>3.114008864085422</v>
+        <v>3.298614693781595</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4622,13 +4622,13 @@
         <v>0.39</v>
       </c>
       <c r="B41">
-        <v>0.0792717766131298</v>
+        <v>0.07813916327025819</v>
       </c>
       <c r="C41">
-        <v>949.1229205320456</v>
+        <v>1001.168219298067</v>
       </c>
       <c r="D41">
-        <v>1513.760920532046</v>
+        <v>1565.806219298068</v>
       </c>
       <c r="E41">
         <v>-173.7619999999999</v>
@@ -4655,37 +4655,37 @@
         <v>136.125</v>
       </c>
       <c r="M41">
-        <v>44.86411020000001</v>
+        <v>42.35330580000001</v>
       </c>
       <c r="N41">
-        <v>91.26088979999996</v>
+        <v>93.77169419999996</v>
       </c>
       <c r="O41">
-        <v>22.76046591611999</v>
+        <v>23.38666053347999</v>
       </c>
       <c r="P41">
-        <v>68.50042388387996</v>
+        <v>70.38503366651997</v>
       </c>
       <c r="Q41">
-        <v>167.00042388388</v>
+        <v>168.88503366652</v>
       </c>
       <c r="R41">
         <v>0.639344262295082</v>
       </c>
       <c r="S41">
-        <v>0.09736907871004885</v>
+        <v>0.09733592437747245</v>
       </c>
       <c r="T41">
         <v>1.190206105715299</v>
       </c>
       <c r="U41">
-        <v>0.06790000000000002</v>
+        <v>0.0641</v>
       </c>
       <c r="V41">
         <v>0.2494</v>
       </c>
       <c r="W41">
-        <v>0.05096574000000001</v>
+        <v>0.04811346</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>3.034162482955026</v>
+        <v>3.214034829838476</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4704,13 +4704,13 @@
         <v>0.4</v>
       </c>
       <c r="B42">
-        <v>0.08202875879327905</v>
+        <v>0.07807544652402285</v>
       </c>
       <c r="C42">
-        <v>816.9848160580659</v>
+        <v>987.3173640620748</v>
       </c>
       <c r="D42">
-        <v>1398.564816058066</v>
+        <v>1568.897364062075</v>
       </c>
       <c r="E42">
         <v>-156.8199999999999</v>
@@ -4737,45 +4737,45 @@
         <v>136.125</v>
       </c>
       <c r="M42">
-        <v>52.31689600000001</v>
+        <v>43.439288</v>
       </c>
       <c r="N42">
-        <v>83.80810399999996</v>
+        <v>92.68571199999997</v>
       </c>
       <c r="O42">
-        <v>20.90174113759999</v>
+        <v>23.11581657279999</v>
       </c>
       <c r="P42">
-        <v>62.90636286239997</v>
+        <v>69.56989542719998</v>
       </c>
       <c r="Q42">
-        <v>161.4063628624</v>
+        <v>168.0698954272</v>
       </c>
       <c r="R42">
         <v>0.6666666666666667</v>
       </c>
       <c r="S42">
-        <v>0.09808371798879841</v>
+        <v>0.09805010420670474</v>
       </c>
       <c r="T42">
         <v>1.206699866205652</v>
       </c>
       <c r="U42">
-        <v>0.0772</v>
+        <v>0.0641</v>
       </c>
       <c r="V42">
         <v>0.2494</v>
       </c>
       <c r="W42">
-        <v>0.05794632</v>
+        <v>0.04811346</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y42">
-        <v>2.601931888313862</v>
+        <v>3.133683959092514</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4786,13 +4786,13 @@
         <v>0.41</v>
       </c>
       <c r="B43">
-        <v>0.08206331477342829</v>
+        <v>0.07801172977778748</v>
       </c>
       <c r="C43">
-        <v>798.7100979013533</v>
+        <v>973.4787377680163</v>
       </c>
       <c r="D43">
-        <v>1397.232097901353</v>
+        <v>1572.000737768017</v>
       </c>
       <c r="E43">
         <v>-139.8779999999999</v>
@@ -4819,45 +4819,45 @@
         <v>136.125</v>
       </c>
       <c r="M43">
-        <v>53.62481840000001</v>
+        <v>44.52527020000001</v>
       </c>
       <c r="N43">
-        <v>82.50018159999996</v>
+        <v>91.59972979999996</v>
       </c>
       <c r="O43">
-        <v>20.57554529103999</v>
+        <v>22.84497261211999</v>
       </c>
       <c r="P43">
-        <v>61.92463630895998</v>
+        <v>68.75475718787997</v>
       </c>
       <c r="Q43">
-        <v>160.42463630896</v>
+        <v>167.25475718788</v>
       </c>
       <c r="R43">
         <v>0.6949152542372882</v>
       </c>
       <c r="S43">
-        <v>0.09882258232784458</v>
+        <v>0.09878849352167371</v>
       </c>
       <c r="T43">
         <v>1.223752737221102</v>
       </c>
       <c r="U43">
-        <v>0.0772</v>
+        <v>0.0641</v>
       </c>
       <c r="V43">
         <v>0.2494</v>
       </c>
       <c r="W43">
-        <v>0.05794632</v>
+        <v>0.04811346</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y43">
-        <v>2.538470134940353</v>
+        <v>3.057252643017087</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4868,13 +4868,13 @@
         <v>0.42</v>
       </c>
       <c r="B44">
-        <v>0.08357955515357755</v>
+        <v>0.08040697863155215</v>
       </c>
       <c r="C44">
-        <v>725.6917434110311</v>
+        <v>847.73403050645</v>
       </c>
       <c r="D44">
-        <v>1341.155743411031</v>
+        <v>1463.19803050645</v>
       </c>
       <c r="E44">
         <v>-122.936</v>
@@ -4901,45 +4901,45 @@
         <v>136.125</v>
       </c>
       <c r="M44">
-        <v>58.2770916</v>
+        <v>51.1614516</v>
       </c>
       <c r="N44">
-        <v>77.84790839999997</v>
+        <v>84.96354839999998</v>
       </c>
       <c r="O44">
-        <v>19.41526835495999</v>
+        <v>21.18990897095999</v>
       </c>
       <c r="P44">
-        <v>58.43264004503997</v>
+        <v>63.77363942903999</v>
       </c>
       <c r="Q44">
-        <v>156.93264004504</v>
+        <v>162.27363942904</v>
       </c>
       <c r="R44">
         <v>0.7241379310344827</v>
       </c>
       <c r="S44">
-        <v>0.09958692474754749</v>
+        <v>0.09955234453715886</v>
       </c>
       <c r="T44">
         <v>1.241393638271567</v>
       </c>
       <c r="U44">
-        <v>0.0819</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V44">
         <v>0.2494</v>
       </c>
       <c r="W44">
-        <v>0.06147414</v>
+        <v>0.05396814</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y44">
-        <v>2.335823498782839</v>
+        <v>2.660694639086432</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4950,13 +4950,13 @@
         <v>0.43</v>
       </c>
       <c r="B45">
-        <v>0.0836493893337268</v>
+        <v>0.08040180868531679</v>
       </c>
       <c r="C45">
-        <v>706.2752381827498</v>
+        <v>831.0106507299819</v>
       </c>
       <c r="D45">
-        <v>1338.68123818275</v>
+        <v>1463.416650729982</v>
       </c>
       <c r="E45">
         <v>-105.994</v>
@@ -4983,45 +4983,45 @@
         <v>136.125</v>
       </c>
       <c r="M45">
-        <v>59.6646414</v>
+        <v>52.3795814</v>
       </c>
       <c r="N45">
-        <v>76.46035859999998</v>
+        <v>83.74541859999997</v>
       </c>
       <c r="O45">
-        <v>19.06921343483999</v>
+        <v>20.88610739883999</v>
       </c>
       <c r="P45">
-        <v>57.39114516515998</v>
+        <v>62.85931120115997</v>
       </c>
       <c r="Q45">
-        <v>155.89114516516</v>
+        <v>161.35931120116</v>
       </c>
       <c r="R45">
         <v>0.7543859649122806</v>
       </c>
       <c r="S45">
-        <v>0.1003780861995207</v>
+        <v>0.100342997342661</v>
       </c>
       <c r="T45">
         <v>1.259653518306259</v>
       </c>
       <c r="U45">
-        <v>0.0819</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V45">
         <v>0.2494</v>
       </c>
       <c r="W45">
-        <v>0.06147414</v>
+        <v>0.05396814</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y45">
-        <v>2.281502022066959</v>
+        <v>2.598818019572794</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5032,13 +5032,13 @@
         <v>0.44</v>
       </c>
       <c r="B46">
-        <v>0.08371922351387605</v>
+        <v>0.08039663873908143</v>
       </c>
       <c r="C46">
-        <v>686.8678473311819</v>
+        <v>814.2873362925094</v>
       </c>
       <c r="D46">
-        <v>1336.215847331182</v>
+        <v>1463.635336292509</v>
       </c>
       <c r="E46">
         <v>-89.05200000000002</v>
@@ -5065,45 +5065,45 @@
         <v>136.125</v>
       </c>
       <c r="M46">
-        <v>61.0521912</v>
+        <v>53.5977112</v>
       </c>
       <c r="N46">
-        <v>75.07280879999998</v>
+        <v>82.52728879999998</v>
       </c>
       <c r="O46">
-        <v>18.72315851471999</v>
+        <v>20.58230582672</v>
       </c>
       <c r="P46">
-        <v>56.34965028527998</v>
+        <v>61.94498297327998</v>
       </c>
       <c r="Q46">
-        <v>154.84965028528</v>
+        <v>160.44498297328</v>
       </c>
       <c r="R46">
         <v>0.7857142857142857</v>
       </c>
       <c r="S46">
-        <v>0.1011975034176358</v>
+        <v>0.1011618877483597</v>
       </c>
       <c r="T46">
         <v>1.278565536913619</v>
       </c>
       <c r="U46">
-        <v>0.0819</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V46">
         <v>0.2494</v>
       </c>
       <c r="W46">
-        <v>0.06147414</v>
+        <v>0.05396814</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y46">
-        <v>2.229649703383619</v>
+        <v>2.539753973673413</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5114,13 +5114,13 @@
         <v>0.45</v>
       </c>
       <c r="B47">
-        <v>0.08378905769402531</v>
+        <v>0.08170877179284609</v>
       </c>
       <c r="C47">
-        <v>667.4695205922457</v>
+        <v>743.8630196461357</v>
       </c>
       <c r="D47">
-        <v>1333.759520592246</v>
+        <v>1410.153019646136</v>
       </c>
       <c r="E47">
         <v>-72.11000000000001</v>
@@ -5147,37 +5147,37 @@
         <v>136.125</v>
       </c>
       <c r="M47">
-        <v>62.439741</v>
+        <v>57.789162</v>
       </c>
       <c r="N47">
-        <v>73.68525899999997</v>
+        <v>78.33583799999997</v>
       </c>
       <c r="O47">
-        <v>18.37710359459999</v>
+        <v>19.53695799719999</v>
       </c>
       <c r="P47">
-        <v>55.30815540539998</v>
+        <v>58.79888000279998</v>
       </c>
       <c r="Q47">
-        <v>153.8081554054</v>
+        <v>157.2988800028</v>
       </c>
       <c r="R47">
         <v>0.8181818181818181</v>
       </c>
       <c r="S47">
-        <v>0.1020467176255005</v>
+        <v>0.1020105559869929</v>
       </c>
       <c r="T47">
         <v>1.298165265288519</v>
       </c>
       <c r="U47">
-        <v>0.0819</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V47">
         <v>0.2494</v>
       </c>
       <c r="W47">
-        <v>0.06147414</v>
+        <v>0.05689548</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>2.180101932197316</v>
+        <v>2.355545491384698</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5196,13 +5196,13 @@
         <v>0.46</v>
       </c>
       <c r="B48">
-        <v>0.08385889187417456</v>
+        <v>0.08173287524661074</v>
       </c>
       <c r="C48">
-        <v>648.0802080707788</v>
+        <v>725.9751015174902</v>
       </c>
       <c r="D48">
-        <v>1331.312208070779</v>
+        <v>1409.20710151749</v>
       </c>
       <c r="E48">
         <v>-55.16799999999989</v>
@@ -5229,37 +5229,37 @@
         <v>136.125</v>
       </c>
       <c r="M48">
-        <v>63.82729080000001</v>
+        <v>59.07336560000001</v>
       </c>
       <c r="N48">
-        <v>72.29770919999996</v>
+        <v>77.05163439999995</v>
       </c>
       <c r="O48">
-        <v>18.03104867447999</v>
+        <v>19.21667761935999</v>
       </c>
       <c r="P48">
-        <v>54.26666052551997</v>
+        <v>57.83495678063997</v>
       </c>
       <c r="Q48">
-        <v>152.76666052552</v>
+        <v>156.33495678064</v>
       </c>
       <c r="R48">
         <v>0.8518518518518519</v>
       </c>
       <c r="S48">
-        <v>0.1029273842114344</v>
+        <v>0.1028906563826125</v>
       </c>
       <c r="T48">
         <v>1.318490909529156</v>
       </c>
       <c r="U48">
-        <v>0.0819</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V48">
         <v>0.2494</v>
       </c>
       <c r="W48">
-        <v>0.06147414</v>
+        <v>0.05689548</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5267,7 +5267,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>2.132708411932157</v>
+        <v>2.304337980702423</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5278,13 +5278,13 @@
         <v>0.47</v>
       </c>
       <c r="B49">
-        <v>0.0839287260543238</v>
+        <v>0.08175697870037538</v>
       </c>
       <c r="C49">
-        <v>628.6998602371575</v>
+        <v>708.088451565133</v>
       </c>
       <c r="D49">
-        <v>1328.873860237158</v>
+        <v>1408.262451565133</v>
       </c>
       <c r="E49">
         <v>-38.22599999999989</v>
@@ -5311,37 +5311,37 @@
         <v>136.125</v>
       </c>
       <c r="M49">
-        <v>65.21484060000002</v>
+        <v>60.35756920000001</v>
       </c>
       <c r="N49">
-        <v>70.91015939999996</v>
+        <v>75.76743079999996</v>
       </c>
       <c r="O49">
-        <v>17.68499375435999</v>
+        <v>18.89639724151999</v>
       </c>
       <c r="P49">
-        <v>53.22516564563996</v>
+        <v>56.87103355847997</v>
       </c>
       <c r="Q49">
-        <v>151.7251656456399</v>
+        <v>155.37103355848</v>
       </c>
       <c r="R49">
         <v>0.8867924528301887</v>
       </c>
       <c r="S49">
-        <v>0.1038412834987242</v>
+        <v>0.1038039681139158</v>
       </c>
       <c r="T49">
         <v>1.339583559212836</v>
       </c>
       <c r="U49">
-        <v>0.0819</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V49">
         <v>0.2494</v>
       </c>
       <c r="W49">
-        <v>0.06147414</v>
+        <v>0.05689548</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5349,7 +5349,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>2.087331637210196</v>
+        <v>2.255309513027902</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5360,13 +5360,13 @@
         <v>0.48</v>
       </c>
       <c r="B50">
-        <v>0.08399856023447305</v>
+        <v>0.08178108215414003</v>
       </c>
       <c r="C50">
-        <v>609.3284279239555</v>
+        <v>690.2030672404377</v>
       </c>
       <c r="D50">
-        <v>1326.444427923956</v>
+        <v>1407.319067240438</v>
       </c>
       <c r="E50">
         <v>-21.28399999999999</v>
@@ -5393,37 +5393,37 @@
         <v>136.125</v>
       </c>
       <c r="M50">
-        <v>66.6023904</v>
+        <v>61.64177280000001</v>
       </c>
       <c r="N50">
-        <v>69.52260959999997</v>
+        <v>74.48322719999996</v>
       </c>
       <c r="O50">
-        <v>17.33893883423999</v>
+        <v>18.57611686367999</v>
       </c>
       <c r="P50">
-        <v>52.18367076575997</v>
+        <v>55.90711033631997</v>
       </c>
       <c r="Q50">
-        <v>150.68367076576</v>
+        <v>154.40711033632</v>
       </c>
       <c r="R50">
         <v>0.923076923076923</v>
       </c>
       <c r="S50">
-        <v>0.104790332758602</v>
+        <v>0.1047524072195</v>
       </c>
       <c r="T50">
         <v>1.361487464653581</v>
       </c>
       <c r="U50">
-        <v>0.0819</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V50">
         <v>0.2494</v>
       </c>
       <c r="W50">
-        <v>0.06147414</v>
+        <v>0.05689548</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5431,7 +5431,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>2.043845561434984</v>
+        <v>2.208323898173155</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5442,13 +5442,13 @@
         <v>0.49</v>
       </c>
       <c r="B51">
-        <v>0.0840683944146223</v>
+        <v>0.08180518560790467</v>
       </c>
       <c r="C51">
-        <v>589.96586232264</v>
+        <v>672.3189460016046</v>
       </c>
       <c r="D51">
-        <v>1324.02386232264</v>
+        <v>1406.376946001605</v>
       </c>
       <c r="E51">
         <v>-4.341999999999985</v>
@@ -5475,37 +5475,37 @@
         <v>136.125</v>
       </c>
       <c r="M51">
-        <v>67.98994020000001</v>
+        <v>62.9259764</v>
       </c>
       <c r="N51">
-        <v>68.13505979999996</v>
+        <v>73.19902359999998</v>
       </c>
       <c r="O51">
-        <v>16.99288391411999</v>
+        <v>18.25583648584</v>
       </c>
       <c r="P51">
-        <v>51.14217588587997</v>
+        <v>54.94318711415998</v>
       </c>
       <c r="Q51">
-        <v>149.64217588588</v>
+        <v>153.44318711416</v>
       </c>
       <c r="R51">
         <v>0.9607843137254901</v>
       </c>
       <c r="S51">
-        <v>0.1057765996365143</v>
+        <v>0.1057380400154994</v>
       </c>
       <c r="T51">
         <v>1.384250346778277</v>
       </c>
       <c r="U51">
-        <v>0.0819</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V51">
         <v>0.2494</v>
       </c>
       <c r="W51">
-        <v>0.06147414</v>
+        <v>0.05689548</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>2.002134427528147</v>
+        <v>2.163256063516561</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5524,13 +5524,13 @@
         <v>0.5</v>
       </c>
       <c r="B52">
-        <v>0.09025561859477155</v>
+        <v>0.08182928906166932</v>
       </c>
       <c r="C52">
-        <v>388.7494620329832</v>
+        <v>654.4360853136349</v>
       </c>
       <c r="D52">
-        <v>1139.749462032983</v>
+        <v>1405.436085313635</v>
       </c>
       <c r="E52">
         <v>12.60000000000002</v>
@@ -5557,45 +5557,45 @@
         <v>136.125</v>
       </c>
       <c r="M52">
-        <v>83.18522000000002</v>
+        <v>64.21018000000001</v>
       </c>
       <c r="N52">
-        <v>52.93977999999996</v>
+        <v>71.91481999999996</v>
       </c>
       <c r="O52">
-        <v>13.20318113199999</v>
+        <v>17.93555610799999</v>
       </c>
       <c r="P52">
-        <v>39.73659886799997</v>
+        <v>53.97926389199997</v>
       </c>
       <c r="Q52">
-        <v>138.236598868</v>
+        <v>152.479263892</v>
       </c>
       <c r="R52">
         <v>1</v>
       </c>
       <c r="S52">
-        <v>0.1068023171895431</v>
+        <v>0.1067630981233386</v>
       </c>
       <c r="T52">
         <v>1.40792374418796</v>
       </c>
       <c r="U52">
-        <v>0.09820000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V52">
         <v>0.2494</v>
       </c>
       <c r="W52">
-        <v>0.07370892</v>
+        <v>0.05689548</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y52">
-        <v>1.636408486988433</v>
+        <v>2.119990942246229</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5606,13 +5606,13 @@
         <v>0.51</v>
       </c>
       <c r="B53">
-        <v>0.0904478005749208</v>
+        <v>0.08185339251543397</v>
       </c>
       <c r="C53">
-        <v>366.9015247714157</v>
+        <v>636.5544826483095</v>
       </c>
       <c r="D53">
-        <v>1134.843524771416</v>
+        <v>1404.49648264831</v>
       </c>
       <c r="E53">
         <v>29.54200000000003</v>
@@ -5639,45 +5639,45 @@
         <v>136.125</v>
       </c>
       <c r="M53">
-        <v>84.84892440000002</v>
+        <v>65.49438360000001</v>
       </c>
       <c r="N53">
-        <v>51.27607559999996</v>
+        <v>70.63061639999997</v>
       </c>
       <c r="O53">
-        <v>12.78825325463999</v>
+        <v>17.61527573015999</v>
       </c>
       <c r="P53">
-        <v>38.48782234535997</v>
+        <v>53.01534066983997</v>
       </c>
       <c r="Q53">
-        <v>136.98782234536</v>
+        <v>151.51534066984</v>
       </c>
       <c r="R53">
         <v>1.040816326530612</v>
       </c>
       <c r="S53">
-        <v>0.1078699007651445</v>
+        <v>0.1078299953376204</v>
       </c>
       <c r="T53">
         <v>1.432563402716406</v>
       </c>
       <c r="U53">
-        <v>0.09820000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V53">
         <v>0.2494</v>
       </c>
       <c r="W53">
-        <v>0.07370892</v>
+        <v>0.05689548</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y53">
-        <v>1.604322046067091</v>
+        <v>2.078422492398263</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5688,13 +5688,13 @@
         <v>0.52</v>
       </c>
       <c r="B54">
-        <v>0.09063998255507005</v>
+        <v>0.08187749596919862</v>
       </c>
       <c r="C54">
-        <v>345.0956407259149</v>
+        <v>618.674135484165</v>
       </c>
       <c r="D54">
-        <v>1129.979640725915</v>
+        <v>1403.558135484165</v>
       </c>
       <c r="E54">
         <v>46.48400000000004</v>
@@ -5721,45 +5721,45 @@
         <v>136.125</v>
       </c>
       <c r="M54">
-        <v>86.51262880000002</v>
+        <v>66.7785872</v>
       </c>
       <c r="N54">
-        <v>49.61237119999996</v>
+        <v>69.34641279999997</v>
       </c>
       <c r="O54">
-        <v>12.37332537727999</v>
+        <v>17.29499535231999</v>
       </c>
       <c r="P54">
-        <v>37.23904582271997</v>
+        <v>52.05141744767997</v>
       </c>
       <c r="Q54">
-        <v>135.73904582272</v>
+        <v>150.55141744768</v>
       </c>
       <c r="R54">
         <v>1.083333333333333</v>
       </c>
       <c r="S54">
-        <v>0.1089819669897293</v>
+        <v>0.1089413466024971</v>
       </c>
       <c r="T54">
         <v>1.458229713683537</v>
       </c>
       <c r="U54">
-        <v>0.09820000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V54">
         <v>0.2494</v>
       </c>
       <c r="W54">
-        <v>0.07370892</v>
+        <v>0.05689548</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y54">
-        <v>1.57346969902734</v>
+        <v>2.038452829082912</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5770,13 +5770,13 @@
         <v>0.53</v>
       </c>
       <c r="B55">
-        <v>0.09083216453521931</v>
+        <v>0.08755061502296327</v>
       </c>
       <c r="C55">
-        <v>323.3312714899611</v>
+        <v>411.0151269538209</v>
       </c>
       <c r="D55">
-        <v>1125.157271489961</v>
+        <v>1212.841126953821</v>
       </c>
       <c r="E55">
         <v>63.42600000000004</v>
@@ -5803,37 +5803,37 @@
         <v>136.125</v>
       </c>
       <c r="M55">
-        <v>88.17633320000002</v>
+        <v>80.81334000000001</v>
       </c>
       <c r="N55">
-        <v>47.94866679999996</v>
+        <v>55.31165999999996</v>
       </c>
       <c r="O55">
-        <v>11.95839749991999</v>
+        <v>13.79472800399999</v>
       </c>
       <c r="P55">
-        <v>35.99026930007997</v>
+        <v>41.51693199599997</v>
       </c>
       <c r="Q55">
-        <v>134.49026930008</v>
+        <v>140.016931996</v>
       </c>
       <c r="R55">
         <v>1.127659574468085</v>
       </c>
       <c r="S55">
-        <v>0.1101413551813177</v>
+        <v>0.1100999894105602</v>
       </c>
       <c r="T55">
         <v>1.484988208096078</v>
       </c>
       <c r="U55">
-        <v>0.09820000000000001</v>
+        <v>0.09000000000000001</v>
       </c>
       <c r="V55">
         <v>0.2494</v>
       </c>
       <c r="W55">
-        <v>0.07370892</v>
+        <v>0.067554</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5841,7 +5841,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>1.543781591498522</v>
+        <v>1.684437247612832</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5852,13 +5852,13 @@
         <v>0.54</v>
       </c>
       <c r="B56">
-        <v>0.09102434651536856</v>
+        <v>0.08768130367672791</v>
       </c>
       <c r="C56">
-        <v>301.6078878089214</v>
+        <v>390.2885128134529</v>
       </c>
       <c r="D56">
-        <v>1120.375887808922</v>
+        <v>1209.056512813453</v>
       </c>
       <c r="E56">
         <v>80.36800000000005</v>
@@ -5885,37 +5885,37 @@
         <v>136.125</v>
       </c>
       <c r="M56">
-        <v>89.84003760000002</v>
+        <v>82.33812000000002</v>
       </c>
       <c r="N56">
-        <v>46.28496239999996</v>
+        <v>53.78687999999995</v>
       </c>
       <c r="O56">
-        <v>11.54346962255999</v>
+        <v>13.41444787199999</v>
       </c>
       <c r="P56">
-        <v>34.74149277743997</v>
+        <v>40.37243212799996</v>
       </c>
       <c r="Q56">
-        <v>133.24149277744</v>
+        <v>138.872432128</v>
       </c>
       <c r="R56">
         <v>1.173913043478261</v>
       </c>
       <c r="S56">
-        <v>0.111351151555149</v>
+        <v>0.1113090079928868</v>
       </c>
       <c r="T56">
         <v>1.512910115309164</v>
       </c>
       <c r="U56">
-        <v>0.09820000000000001</v>
+        <v>0.09000000000000001</v>
       </c>
       <c r="V56">
         <v>0.2494</v>
       </c>
       <c r="W56">
-        <v>0.07370892</v>
+        <v>0.067554</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5923,7 +5923,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>1.515193043507808</v>
+        <v>1.653243965249631</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5934,13 +5934,13 @@
         <v>0.55</v>
       </c>
       <c r="B57">
-        <v>0.1211296040608346</v>
+        <v>0.08781199233049257</v>
       </c>
       <c r="C57">
-        <v>-163.0890827731452</v>
+        <v>369.5854446226855</v>
       </c>
       <c r="D57">
-        <v>672.6209172268549</v>
+        <v>1205.295444622686</v>
       </c>
       <c r="E57">
         <v>97.31000000000006</v>
@@ -5967,45 +5967,45 @@
         <v>136.125</v>
       </c>
       <c r="M57">
-        <v>152.444116</v>
+        <v>83.86290000000001</v>
       </c>
       <c r="N57">
-        <v>-16.31911600000007</v>
+        <v>52.26209999999996</v>
       </c>
       <c r="O57">
-        <v>-4.069987530400017</v>
+        <v>13.03416773999999</v>
       </c>
       <c r="P57">
-        <v>-12.24912846960005</v>
+        <v>39.22793225999997</v>
       </c>
       <c r="Q57">
-        <v>86.25087153039995</v>
+        <v>137.72793226</v>
       </c>
       <c r="R57">
         <v>1.222222222222223</v>
       </c>
       <c r="S57">
-        <v>0.113751799210202</v>
+        <v>0.1125717607344279</v>
       </c>
       <c r="T57">
-        <v>1.568316680021717</v>
+        <v>1.542072996176165</v>
       </c>
       <c r="U57">
-        <v>0.1636</v>
+        <v>0.09000000000000001</v>
       </c>
       <c r="V57">
-        <v>0.2227017735469697</v>
+        <v>0.2494</v>
       </c>
       <c r="W57">
-        <v>0.1271659898477158</v>
+        <v>0.067554</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y57">
-        <v>0.8929501746069356</v>
+        <v>1.623184984063274</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6016,13 +6016,13 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1223076040608345</v>
+        <v>0.08794268098425723</v>
       </c>
       <c r="C58">
-        <v>-190.3875362292382</v>
+        <v>348.90570332651</v>
       </c>
       <c r="D58">
-        <v>662.2644637707618</v>
+        <v>1201.55770332651</v>
       </c>
       <c r="E58">
         <v>114.2520000000001</v>
@@ -6049,45 +6049,45 @@
         <v>136.125</v>
       </c>
       <c r="M58">
-        <v>155.2158272</v>
+        <v>85.38768000000002</v>
       </c>
       <c r="N58">
-        <v>-19.09082720000006</v>
+        <v>50.73731999999995</v>
       </c>
       <c r="O58">
-        <v>-4.761252303680016</v>
+        <v>12.65388760799999</v>
       </c>
       <c r="P58">
-        <v>-14.32957489632005</v>
+        <v>38.08343239199996</v>
       </c>
       <c r="Q58">
-        <v>84.17042510367995</v>
+        <v>136.583432392</v>
       </c>
       <c r="R58">
         <v>1.272727272727273</v>
       </c>
       <c r="S58">
-        <v>0.1152961582831611</v>
+        <v>0.1138919113278573</v>
       </c>
       <c r="T58">
-        <v>1.603960240931302</v>
+        <v>1.572561462537121</v>
       </c>
       <c r="U58">
-        <v>0.1636</v>
+        <v>0.09000000000000001</v>
       </c>
       <c r="V58">
-        <v>0.2187249561622024</v>
+        <v>0.2494</v>
       </c>
       <c r="W58">
-        <v>0.1278165971718637</v>
+        <v>0.067554</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y58">
-        <v>0.8770046357746688</v>
+        <v>1.594199537919287</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6098,13 +6098,13 @@
         <v>0.5700000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1234856040608345</v>
+        <v>0.08807336963802187</v>
       </c>
       <c r="C59">
-        <v>-217.3719056972162</v>
+        <v>328.2490725787627</v>
       </c>
       <c r="D59">
-        <v>652.2220943027839</v>
+        <v>1197.843072578763</v>
       </c>
       <c r="E59">
         <v>131.1940000000002</v>
@@ -6131,45 +6131,45 @@
         <v>136.125</v>
       </c>
       <c r="M59">
-        <v>157.9875384000001</v>
+        <v>86.91246000000002</v>
       </c>
       <c r="N59">
-        <v>-21.86253840000009</v>
+        <v>49.21253999999995</v>
       </c>
       <c r="O59">
-        <v>-5.452517076960023</v>
+        <v>12.27360747599999</v>
       </c>
       <c r="P59">
-        <v>-16.41002132304007</v>
+        <v>36.93893252399996</v>
       </c>
       <c r="Q59">
-        <v>82.08997867695993</v>
+        <v>135.438932524</v>
       </c>
       <c r="R59">
         <v>1.325581395348838</v>
       </c>
       <c r="S59">
-        <v>0.1169123480106765</v>
+        <v>0.1152734642744695</v>
       </c>
       <c r="T59">
-        <v>1.641261641883192</v>
+        <v>1.604467997100911</v>
       </c>
       <c r="U59">
-        <v>0.1636</v>
+        <v>0.09000000000000001</v>
       </c>
       <c r="V59">
-        <v>0.2148876762295322</v>
+        <v>0.2494</v>
       </c>
       <c r="W59">
-        <v>0.1284443761688485</v>
+        <v>0.067554</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y59">
-        <v>0.8616185895330079</v>
+        <v>1.566231124973334</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6180,13 +6180,13 @@
         <v>0.58</v>
       </c>
       <c r="B60">
-        <v>0.1246636040608345</v>
+        <v>0.08820405829178651</v>
       </c>
       <c r="C60">
-        <v>-244.0562657660764</v>
+        <v>307.6153387003819</v>
       </c>
       <c r="D60">
-        <v>642.4797342339235</v>
+        <v>1194.151338700382</v>
       </c>
       <c r="E60">
         <v>148.136</v>
@@ -6213,45 +6213,45 @@
         <v>136.125</v>
       </c>
       <c r="M60">
-        <v>160.7592496</v>
+        <v>88.43724</v>
       </c>
       <c r="N60">
-        <v>-24.63424960000003</v>
+        <v>47.68775999999997</v>
       </c>
       <c r="O60">
-        <v>-6.143781850240009</v>
+        <v>11.89332734399999</v>
       </c>
       <c r="P60">
-        <v>-18.49046774976002</v>
+        <v>35.79443265599998</v>
       </c>
       <c r="Q60">
-        <v>80.00953225023997</v>
+        <v>134.294432656</v>
       </c>
       <c r="R60">
         <v>1.380952380952381</v>
       </c>
       <c r="S60">
-        <v>0.1186054991537878</v>
+        <v>0.1167208054566345</v>
       </c>
       <c r="T60">
-        <v>1.680339300023268</v>
+        <v>1.637893890453454</v>
       </c>
       <c r="U60">
-        <v>0.1636</v>
+        <v>0.09000000000000001</v>
       </c>
       <c r="V60">
-        <v>0.2111827162945403</v>
+        <v>0.2494</v>
       </c>
       <c r="W60">
-        <v>0.1290505076142132</v>
+        <v>0.067554</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y60">
-        <v>0.8467630966100252</v>
+        <v>1.539227140060001</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6262,13 +6262,13 @@
         <v>0.59</v>
       </c>
       <c r="B61">
-        <v>0.1258416040608346</v>
+        <v>0.08833474694555116</v>
       </c>
       <c r="C61">
-        <v>-270.4538624624187</v>
+        <v>287.0042906384347</v>
       </c>
       <c r="D61">
-        <v>633.0241375375813</v>
+        <v>1190.482290638435</v>
       </c>
       <c r="E61">
         <v>165.078</v>
@@ -6295,45 +6295,45 @@
         <v>136.125</v>
       </c>
       <c r="M61">
-        <v>163.5309608</v>
+        <v>89.96202000000001</v>
       </c>
       <c r="N61">
-        <v>-27.40596080000006</v>
+        <v>46.16297999999996</v>
       </c>
       <c r="O61">
-        <v>-6.835046623520015</v>
+        <v>11.51304721199999</v>
       </c>
       <c r="P61">
-        <v>-20.57091417648004</v>
+        <v>34.64993278799997</v>
       </c>
       <c r="Q61">
-        <v>77.92908582351996</v>
+        <v>133.149932788</v>
       </c>
       <c r="R61">
         <v>1.439024390243902</v>
       </c>
       <c r="S61">
-        <v>0.1203812430355875</v>
+        <v>0.1182387486476857</v>
       </c>
       <c r="T61">
-        <v>1.721323185389689</v>
+        <v>1.672950315189048</v>
       </c>
       <c r="U61">
-        <v>0.1636</v>
+        <v>0.09000000000000001</v>
       </c>
       <c r="V61">
-        <v>0.2076033482217514</v>
+        <v>0.2494</v>
       </c>
       <c r="W61">
-        <v>0.1296360922309215</v>
+        <v>0.067554</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y61">
-        <v>0.8324111797183298</v>
+        <v>1.513138544465764</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6344,13 +6344,13 @@
         <v>0.6</v>
       </c>
       <c r="B62">
-        <v>0.1270196040608345</v>
+        <v>0.1164317989693688</v>
       </c>
       <c r="C62">
-        <v>-296.5771733373243</v>
+        <v>-203.5068855906414</v>
       </c>
       <c r="D62">
-        <v>623.8428266626756</v>
+        <v>716.9131144093585</v>
       </c>
       <c r="E62">
         <v>182.02</v>
@@ -6377,37 +6377,37 @@
         <v>136.125</v>
       </c>
       <c r="M62">
-        <v>166.302672</v>
+        <v>149.225136</v>
       </c>
       <c r="N62">
-        <v>-30.17767200000006</v>
+        <v>-13.10013600000005</v>
       </c>
       <c r="O62">
-        <v>-7.526311396800015</v>
+        <v>-3.267173918400012</v>
       </c>
       <c r="P62">
-        <v>-22.65136060320004</v>
+        <v>-9.832962081600037</v>
       </c>
       <c r="Q62">
-        <v>75.84863939679995</v>
+        <v>88.66703791839996</v>
       </c>
       <c r="R62">
         <v>1.5</v>
       </c>
       <c r="S62">
-        <v>0.1222457741114772</v>
+        <v>0.1209762613828128</v>
       </c>
       <c r="T62">
-        <v>1.764356265024432</v>
+        <v>1.736172318309764</v>
       </c>
       <c r="U62">
-        <v>0.1636</v>
+        <v>0.1468</v>
       </c>
       <c r="V62">
-        <v>0.2041432924180556</v>
+        <v>0.2275057400517295</v>
       </c>
       <c r="W62">
-        <v>0.1302021573604061</v>
+        <v>0.1134021573604061</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.8185376600563576</v>
+        <v>0.912212269654088</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6426,13 +6426,13 @@
         <v>0.61</v>
       </c>
       <c r="B63">
-        <v>0.1281976040608346</v>
+        <v>0.1174417989693688</v>
       </c>
       <c r="C63">
-        <v>-322.4379623990313</v>
+        <v>-230.5558658168507</v>
       </c>
       <c r="D63">
-        <v>614.9240376009686</v>
+        <v>706.8061341831493</v>
       </c>
       <c r="E63">
         <v>198.962</v>
@@ -6459,37 +6459,37 @@
         <v>136.125</v>
       </c>
       <c r="M63">
-        <v>169.0743832</v>
+        <v>151.7122216</v>
       </c>
       <c r="N63">
-        <v>-32.94938320000006</v>
+        <v>-15.58722160000005</v>
       </c>
       <c r="O63">
-        <v>-8.217576170080015</v>
+        <v>-3.887453067040012</v>
       </c>
       <c r="P63">
-        <v>-24.73180702992004</v>
+        <v>-11.69976853296004</v>
       </c>
       <c r="Q63">
-        <v>73.76819297007995</v>
+        <v>86.80023146703996</v>
       </c>
       <c r="R63">
         <v>1.564102564102564</v>
       </c>
       <c r="S63">
-        <v>0.1242059221656177</v>
+        <v>0.1229038578285259</v>
       </c>
       <c r="T63">
-        <v>1.809596169255828</v>
+        <v>1.780689557240784</v>
       </c>
       <c r="U63">
-        <v>0.1636</v>
+        <v>0.1468</v>
       </c>
       <c r="V63">
-        <v>0.2007966810669399</v>
+        <v>0.2237761377557995</v>
       </c>
       <c r="W63">
-        <v>0.1307496629774486</v>
+        <v>0.1139496629774486</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6497,7 +6497,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.8051190098914993</v>
+        <v>0.8972579701515619</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6508,13 +6508,13 @@
         <v>0.62</v>
       </c>
       <c r="B64">
-        <v>0.1627720440933178</v>
+        <v>0.1184517989693688</v>
       </c>
       <c r="C64">
-        <v>-521.1383853398655</v>
+        <v>-257.3238330420523</v>
       </c>
       <c r="D64">
-        <v>433.1656146601345</v>
+        <v>696.9801669579476</v>
       </c>
       <c r="E64">
         <v>215.904</v>
@@ -6541,45 +6541,45 @@
         <v>136.125</v>
       </c>
       <c r="M64">
-        <v>226.6771832</v>
+        <v>154.1993072</v>
       </c>
       <c r="N64">
-        <v>-90.55218320000006</v>
+        <v>-18.07430720000005</v>
       </c>
       <c r="O64">
-        <v>-22.58371449008002</v>
+        <v>-4.507732215680012</v>
       </c>
       <c r="P64">
-        <v>-67.96846870992005</v>
+        <v>-13.56657498432004</v>
       </c>
       <c r="Q64">
-        <v>30.53153129007995</v>
+        <v>84.93342501567996</v>
       </c>
       <c r="R64">
         <v>1.631578947368421</v>
       </c>
       <c r="S64">
-        <v>0.1289861833607214</v>
+        <v>0.1249329067187503</v>
       </c>
       <c r="T64">
-        <v>1.91992383466393</v>
+        <v>1.827549808747121</v>
       </c>
       <c r="U64">
-        <v>0.2158</v>
+        <v>0.1468</v>
       </c>
       <c r="V64">
-        <v>0.1497705879380276</v>
+        <v>0.2201668452113512</v>
       </c>
       <c r="W64">
-        <v>0.1834795071229737</v>
+        <v>0.1144795071229737</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y64">
-        <v>0.6005236084122998</v>
+        <v>0.8827860674071819</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6590,13 +6590,13 @@
         <v>0.63</v>
       </c>
       <c r="B65">
-        <v>0.1644720440933178</v>
+        <v>0.1194617989693688</v>
       </c>
       <c r="C65">
-        <v>-544.2855666068468</v>
+        <v>-283.8223464380972</v>
       </c>
       <c r="D65">
-        <v>426.9604333931532</v>
+        <v>687.4236535619028</v>
       </c>
       <c r="E65">
         <v>232.846</v>
@@ -6623,45 +6623,45 @@
         <v>136.125</v>
       </c>
       <c r="M65">
-        <v>230.3332668</v>
+        <v>156.6863928</v>
       </c>
       <c r="N65">
-        <v>-94.20826680000005</v>
+        <v>-20.56139280000005</v>
       </c>
       <c r="O65">
-        <v>-23.49554173992001</v>
+        <v>-5.128011364320012</v>
       </c>
       <c r="P65">
-        <v>-70.71272506008003</v>
+        <v>-15.43338143568004</v>
       </c>
       <c r="Q65">
-        <v>27.78727493991997</v>
+        <v>83.06661856431997</v>
       </c>
       <c r="R65">
         <v>1.702702702702703</v>
       </c>
       <c r="S65">
-        <v>0.1312344585866868</v>
+        <v>0.1270716339273652</v>
       </c>
       <c r="T65">
-        <v>1.971813668033226</v>
+        <v>1.876943046821367</v>
       </c>
       <c r="U65">
-        <v>0.2158</v>
+        <v>0.1468</v>
       </c>
       <c r="V65">
-        <v>0.1473932770183764</v>
+        <v>0.2166721333825996</v>
       </c>
       <c r="W65">
-        <v>0.1839925308194344</v>
+        <v>0.1149925308194344</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y65">
-        <v>0.5909914876438507</v>
+        <v>0.8687735901467505</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6672,13 +6672,13 @@
         <v>0.64</v>
       </c>
       <c r="B66">
-        <v>0.1661720440933178</v>
+        <v>0.1204717989693688</v>
       </c>
       <c r="C66">
-        <v>-567.2574778062086</v>
+        <v>-310.0623397860589</v>
       </c>
       <c r="D66">
-        <v>420.9305221937914</v>
+        <v>678.125660213941</v>
       </c>
       <c r="E66">
         <v>249.788</v>
@@ -6705,45 +6705,45 @@
         <v>136.125</v>
       </c>
       <c r="M66">
-        <v>233.9893504</v>
+        <v>159.1734784</v>
       </c>
       <c r="N66">
-        <v>-97.86435040000006</v>
+        <v>-23.04847840000005</v>
       </c>
       <c r="O66">
-        <v>-24.40736898976002</v>
+        <v>-5.748290512960013</v>
       </c>
       <c r="P66">
-        <v>-73.45698141024005</v>
+        <v>-17.30018788704004</v>
       </c>
       <c r="Q66">
-        <v>25.04301858975995</v>
+        <v>81.19981211295996</v>
       </c>
       <c r="R66">
         <v>1.777777777777778</v>
       </c>
       <c r="S66">
-        <v>0.1336076379918726</v>
+        <v>0.1293291793142365</v>
       </c>
       <c r="T66">
-        <v>2.026586269923038</v>
+        <v>1.929080353677517</v>
       </c>
       <c r="U66">
-        <v>0.2158</v>
+        <v>0.1468</v>
       </c>
       <c r="V66">
-        <v>0.1450902570649642</v>
+        <v>0.2132866312984965</v>
       </c>
       <c r="W66">
-        <v>0.1844895225253807</v>
+        <v>0.1154895225253807</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y66">
-        <v>0.5817572456494154</v>
+        <v>0.8551990028007075</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6754,13 +6754,13 @@
         <v>0.65</v>
       </c>
       <c r="B67">
-        <v>0.1678720440933178</v>
+        <v>0.1214817989693688</v>
       </c>
       <c r="C67">
-        <v>-590.0614414772881</v>
+        <v>-336.0541632065259</v>
       </c>
       <c r="D67">
-        <v>415.068558522712</v>
+        <v>669.0758367934741</v>
       </c>
       <c r="E67">
         <v>266.73</v>
@@ -6787,45 +6787,45 @@
         <v>136.125</v>
       </c>
       <c r="M67">
-        <v>237.645434</v>
+        <v>161.660564</v>
       </c>
       <c r="N67">
-        <v>-101.5204340000001</v>
+        <v>-25.53556400000005</v>
       </c>
       <c r="O67">
-        <v>-25.31919623960001</v>
+        <v>-6.368569661600013</v>
       </c>
       <c r="P67">
-        <v>-76.20123776040003</v>
+        <v>-19.16699433840004</v>
       </c>
       <c r="Q67">
-        <v>22.29876223959997</v>
+        <v>79.33300566159997</v>
       </c>
       <c r="R67">
         <v>1.857142857142857</v>
       </c>
       <c r="S67">
-        <v>0.1361164276487832</v>
+        <v>0.1317157272946432</v>
       </c>
       <c r="T67">
-        <v>2.084488734777982</v>
+        <v>1.98419693521116</v>
       </c>
       <c r="U67">
-        <v>0.2158</v>
+        <v>0.1468</v>
       </c>
       <c r="V67">
-        <v>0.1428580992639648</v>
+        <v>0.2100052985092888</v>
       </c>
       <c r="W67">
-        <v>0.1849712221788364</v>
+        <v>0.1159712221788364</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y67">
-        <v>0.572807134177886</v>
+        <v>0.842042095065312</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6836,13 +6836,13 @@
         <v>0.66</v>
       </c>
       <c r="B68">
-        <v>0.1695720440933178</v>
+        <v>0.1224917989693688</v>
       </c>
       <c r="C68">
-        <v>-612.7043778612475</v>
+        <v>-361.8076215924654</v>
       </c>
       <c r="D68">
-        <v>409.3676221387526</v>
+        <v>660.2643784075347</v>
       </c>
       <c r="E68">
         <v>283.672</v>
@@ -6869,45 +6869,45 @@
         <v>136.125</v>
       </c>
       <c r="M68">
-        <v>241.3015176</v>
+        <v>164.1476496</v>
       </c>
       <c r="N68">
-        <v>-105.1765176000001</v>
+        <v>-28.02264960000005</v>
       </c>
       <c r="O68">
-        <v>-26.23102348944002</v>
+        <v>-6.988848810240013</v>
       </c>
       <c r="P68">
-        <v>-78.94549411056005</v>
+        <v>-21.03380078976004</v>
       </c>
       <c r="Q68">
-        <v>19.55450588943995</v>
+        <v>77.46619921023996</v>
       </c>
       <c r="R68">
         <v>1.941176470588236</v>
       </c>
       <c r="S68">
-        <v>0.1387727931678651</v>
+        <v>0.134242660450368</v>
       </c>
       <c r="T68">
-        <v>2.145797226977334</v>
+        <v>2.042555668599723</v>
       </c>
       <c r="U68">
-        <v>0.2158</v>
+        <v>0.1468</v>
       </c>
       <c r="V68">
-        <v>0.1406935826084501</v>
+        <v>0.2068234000470269</v>
       </c>
       <c r="W68">
-        <v>0.1854383248730965</v>
+        <v>0.1164383248730965</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y68">
-        <v>0.5641282382054937</v>
+        <v>0.8292838815037163</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6918,13 +6918,13 @@
         <v>0.67</v>
       </c>
       <c r="B69">
-        <v>0.1712720440933178</v>
+        <v>0.1235017989693688</v>
       </c>
       <c r="C69">
-        <v>-635.1928321544308</v>
+        <v>-387.3320100446874</v>
       </c>
       <c r="D69">
-        <v>403.8211678455692</v>
+        <v>651.6819899553126</v>
       </c>
       <c r="E69">
         <v>300.614</v>
@@ -6951,45 +6951,45 @@
         <v>136.125</v>
       </c>
       <c r="M69">
-        <v>244.9576012</v>
+        <v>166.6347352</v>
       </c>
       <c r="N69">
-        <v>-108.8326012000001</v>
+        <v>-30.50973520000005</v>
       </c>
       <c r="O69">
-        <v>-27.14285073928001</v>
+        <v>-7.609127958880013</v>
       </c>
       <c r="P69">
-        <v>-81.68975046072003</v>
+        <v>-22.90060724112004</v>
       </c>
       <c r="Q69">
-        <v>16.81024953927997</v>
+        <v>75.59939275887996</v>
       </c>
       <c r="R69">
         <v>2.030303030303031</v>
       </c>
       <c r="S69">
-        <v>0.1415901505365883</v>
+        <v>0.1369227410700761</v>
       </c>
       <c r="T69">
-        <v>2.210821385370587</v>
+        <v>2.104451294920927</v>
       </c>
       <c r="U69">
-        <v>0.2158</v>
+        <v>0.1468</v>
       </c>
       <c r="V69">
-        <v>0.1385936783904136</v>
+        <v>0.2037364836284145</v>
       </c>
       <c r="W69">
-        <v>0.1858914842033488</v>
+        <v>0.1168914842033488</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y69">
-        <v>0.5557084137546655</v>
+        <v>0.8169065101379892</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7000,13 +7000,13 @@
         <v>0.68</v>
       </c>
       <c r="B70">
-        <v>0.1729720440933178</v>
+        <v>0.1245117989693688</v>
       </c>
       <c r="C70">
-        <v>-657.5329995758314</v>
+        <v>-412.6361465791481</v>
       </c>
       <c r="D70">
-        <v>398.4230004241687</v>
+        <v>643.3198534208519</v>
       </c>
       <c r="E70">
         <v>317.556</v>
@@ -7033,45 +7033,45 @@
         <v>136.125</v>
       </c>
       <c r="M70">
-        <v>248.6136848</v>
+        <v>169.1218208</v>
       </c>
       <c r="N70">
-        <v>-112.4886848000001</v>
+        <v>-32.99682080000005</v>
       </c>
       <c r="O70">
-        <v>-28.05467798912002</v>
+        <v>-8.229407107520013</v>
       </c>
       <c r="P70">
-        <v>-84.43400681088005</v>
+        <v>-24.76741369248004</v>
       </c>
       <c r="Q70">
-        <v>14.06599318911995</v>
+        <v>73.73258630751997</v>
       </c>
       <c r="R70">
         <v>2.125</v>
       </c>
       <c r="S70">
-        <v>0.1445835927408566</v>
+        <v>0.139770326728516</v>
       </c>
       <c r="T70">
-        <v>2.279909553663417</v>
+        <v>2.170215397887206</v>
       </c>
       <c r="U70">
-        <v>0.2158</v>
+        <v>0.1468</v>
       </c>
       <c r="V70">
-        <v>0.1365555360611428</v>
+        <v>0.2007403588691731</v>
       </c>
       <c r="W70">
-        <v>0.1863313153180054</v>
+        <v>0.1173313153180054</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y70">
-        <v>0.5475362311994498</v>
+        <v>0.8048931791065482</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7082,13 +7082,13 @@
         <v>0.6900000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1746720440933178</v>
+        <v>0.164060160713875</v>
       </c>
       <c r="C71">
-        <v>-679.7307484505108</v>
+        <v>-644.7160774506179</v>
       </c>
       <c r="D71">
-        <v>393.1672515494893</v>
+        <v>428.1819225493821</v>
       </c>
       <c r="E71">
         <v>334.498</v>
@@ -7115,37 +7115,37 @@
         <v>136.125</v>
       </c>
       <c r="M71">
-        <v>252.2697684</v>
+        <v>234.7347984</v>
       </c>
       <c r="N71">
-        <v>-116.1447684000001</v>
+        <v>-98.60979840000005</v>
       </c>
       <c r="O71">
-        <v>-28.96650523896002</v>
+        <v>-24.59328372096001</v>
       </c>
       <c r="P71">
-        <v>-87.17826316104004</v>
+        <v>-74.01651467904003</v>
       </c>
       <c r="Q71">
-        <v>11.32173683895996</v>
+        <v>24.48348532095997</v>
       </c>
       <c r="R71">
         <v>2.225806451612904</v>
       </c>
       <c r="S71">
-        <v>0.1477701602486262</v>
+        <v>0.1469253751536493</v>
       </c>
       <c r="T71">
-        <v>2.353455023136431</v>
+        <v>2.33545901047689</v>
       </c>
       <c r="U71">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V71">
-        <v>0.1345764703211262</v>
+        <v>0.1446294935024853</v>
       </c>
       <c r="W71">
-        <v>0.186758397704701</v>
+        <v>0.171758397704701</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.5396009235009072</v>
+        <v>0.5799097574277677</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7164,13 +7164,13 @@
         <v>0.7000000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1763720440933178</v>
+        <v>0.165610160713875</v>
       </c>
       <c r="C72">
-        <v>-701.7916414897931</v>
+        <v>-667.1975239883495</v>
       </c>
       <c r="D72">
-        <v>388.048358510207</v>
+        <v>422.6424760116506</v>
       </c>
       <c r="E72">
         <v>351.4400000000001</v>
@@ -7197,37 +7197,37 @@
         <v>136.125</v>
       </c>
       <c r="M72">
-        <v>255.925852</v>
+        <v>238.136752</v>
       </c>
       <c r="N72">
-        <v>-119.8008520000001</v>
+        <v>-102.0117520000001</v>
       </c>
       <c r="O72">
-        <v>-29.87833248880002</v>
+        <v>-25.44173094880001</v>
       </c>
       <c r="P72">
-        <v>-89.92251951120005</v>
+        <v>-76.57002105120004</v>
       </c>
       <c r="Q72">
-        <v>8.577480488799949</v>
+        <v>21.92997894879996</v>
       </c>
       <c r="R72">
         <v>2.333333333333334</v>
       </c>
       <c r="S72">
-        <v>0.1511691655902471</v>
+        <v>0.1502962209921043</v>
       </c>
       <c r="T72">
-        <v>2.431903523907645</v>
+        <v>2.413307644159453</v>
       </c>
       <c r="U72">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V72">
-        <v>0.1326539493165387</v>
+        <v>0.1425633578810212</v>
       </c>
       <c r="W72">
-        <v>0.187173277737491</v>
+        <v>0.172173277737491</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7235,7 +7235,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.5318923388794655</v>
+        <v>0.5716253323216567</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7246,13 +7246,13 @@
         <v>0.71</v>
       </c>
       <c r="B73">
-        <v>0.1780720440933178</v>
+        <v>0.1671601607138749</v>
       </c>
       <c r="C73">
-        <v>-723.7209554304618</v>
+        <v>-689.5374719966958</v>
       </c>
       <c r="D73">
-        <v>383.0610445695383</v>
+        <v>417.2445280033043</v>
       </c>
       <c r="E73">
         <v>368.3820000000001</v>
@@ -7279,37 +7279,37 @@
         <v>136.125</v>
       </c>
       <c r="M73">
-        <v>259.5819356000001</v>
+        <v>241.5387056</v>
       </c>
       <c r="N73">
-        <v>-123.4569356000001</v>
+        <v>-105.4137056</v>
       </c>
       <c r="O73">
-        <v>-30.79015973864002</v>
+        <v>-26.29017817664001</v>
       </c>
       <c r="P73">
-        <v>-92.66677586136007</v>
+        <v>-79.12352742336003</v>
       </c>
       <c r="Q73">
-        <v>5.833224138639935</v>
+        <v>19.37647257663997</v>
       </c>
       <c r="R73">
         <v>2.448275862068965</v>
       </c>
       <c r="S73">
-        <v>0.1548025850933591</v>
+        <v>0.1538995389573492</v>
       </c>
       <c r="T73">
-        <v>2.515762266111357</v>
+        <v>2.496525149130468</v>
       </c>
       <c r="U73">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V73">
-        <v>0.1307855838332072</v>
+        <v>0.1405554232629787</v>
       </c>
       <c r="W73">
-        <v>0.1875764710087939</v>
+        <v>0.1725764710087939</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.524400897486797</v>
+        <v>0.5635742713030418</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7328,13 +7328,13 @@
         <v>0.72</v>
       </c>
       <c r="B74">
-        <v>0.1797720440933178</v>
+        <v>0.1687101607138749</v>
       </c>
       <c r="C74">
-        <v>-745.5236991787218</v>
+        <v>-711.7412747203181</v>
       </c>
       <c r="D74">
-        <v>378.2003008212783</v>
+        <v>411.982725279682</v>
       </c>
       <c r="E74">
         <v>385.3240000000001</v>
@@ -7361,37 +7361,37 @@
         <v>136.125</v>
       </c>
       <c r="M74">
-        <v>263.2380192000001</v>
+        <v>244.9406592</v>
       </c>
       <c r="N74">
-        <v>-127.1130192000001</v>
+        <v>-108.8156592000001</v>
       </c>
       <c r="O74">
-        <v>-31.70198698848002</v>
+        <v>-27.13862540448002</v>
       </c>
       <c r="P74">
-        <v>-95.41103221152005</v>
+        <v>-81.67703379552003</v>
       </c>
       <c r="Q74">
-        <v>3.088967788479948</v>
+        <v>16.82296620447997</v>
       </c>
       <c r="R74">
         <v>2.571428571428571</v>
       </c>
       <c r="S74">
-        <v>0.158695534560979</v>
+        <v>0.1577602367772546</v>
       </c>
       <c r="T74">
-        <v>2.605610918472477</v>
+        <v>2.585686761599413</v>
       </c>
       <c r="U74">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V74">
-        <v>0.1289691173910793</v>
+        <v>0.1386032646065484</v>
       </c>
       <c r="W74">
-        <v>0.1879684644670051</v>
+        <v>0.1729684644670051</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.5171175516883693</v>
+        <v>0.5557468508682775</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7410,13 +7410,13 @@
         <v>0.73</v>
       </c>
       <c r="B75">
-        <v>0.1814720440933178</v>
+        <v>0.1702601607138749</v>
       </c>
       <c r="C75">
-        <v>-767.2046305900739</v>
+        <v>-733.8140187312594</v>
       </c>
       <c r="D75">
-        <v>373.4613694099262</v>
+        <v>406.8519812687407</v>
       </c>
       <c r="E75">
         <v>402.2660000000001</v>
@@ -7443,37 +7443,37 @@
         <v>136.125</v>
       </c>
       <c r="M75">
-        <v>266.8941028</v>
+        <v>248.3426128</v>
       </c>
       <c r="N75">
-        <v>-130.7691028000001</v>
+        <v>-112.2176128</v>
       </c>
       <c r="O75">
-        <v>-32.61381423832002</v>
+        <v>-27.98707263232001</v>
       </c>
       <c r="P75">
-        <v>-98.15528856168005</v>
+        <v>-84.23054016768003</v>
       </c>
       <c r="Q75">
-        <v>0.3447114383199477</v>
+        <v>14.26945983231997</v>
       </c>
       <c r="R75">
         <v>2.703703703703703</v>
       </c>
       <c r="S75">
-        <v>0.1628768506558301</v>
+        <v>0.1619069122134492</v>
       </c>
       <c r="T75">
-        <v>2.70211502656405</v>
+        <v>2.681452937954946</v>
       </c>
       <c r="U75">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V75">
-        <v>0.1272024171528454</v>
+        <v>0.1367045897489244</v>
       </c>
       <c r="W75">
-        <v>0.188349718378416</v>
+        <v>0.173349718378416</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.5100337496104465</v>
+        <v>0.548133880308438</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7492,13 +7492,13 @@
         <v>0.74</v>
       </c>
       <c r="B76">
-        <v>0.1831720440933178</v>
+        <v>0.1718101607138749</v>
       </c>
       <c r="C76">
-        <v>-788.7682720032685</v>
+        <v>-755.7605403301047</v>
       </c>
       <c r="D76">
-        <v>368.8397279967316</v>
+        <v>401.8474596698953</v>
       </c>
       <c r="E76">
         <v>419.2080000000001</v>
@@ -7525,37 +7525,37 @@
         <v>136.125</v>
       </c>
       <c r="M76">
-        <v>270.5501864</v>
+        <v>251.7445664</v>
       </c>
       <c r="N76">
-        <v>-134.4251864000001</v>
+        <v>-115.6195664000001</v>
       </c>
       <c r="O76">
-        <v>-33.52564148816002</v>
+        <v>-28.83551986016002</v>
       </c>
       <c r="P76">
-        <v>-100.89954491184</v>
+        <v>-86.78404653984003</v>
       </c>
       <c r="Q76">
-        <v>-2.399544911840039</v>
+        <v>11.71595346015997</v>
       </c>
       <c r="R76">
         <v>2.846153846153846</v>
       </c>
       <c r="S76">
-        <v>0.1673798064502851</v>
+        <v>0.1663725626831972</v>
       </c>
       <c r="T76">
-        <v>2.806042527585744</v>
+        <v>2.784585743260906</v>
       </c>
       <c r="U76">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V76">
-        <v>0.1254834655696988</v>
+        <v>0.134857230427993</v>
       </c>
       <c r="W76">
-        <v>0.188720668130059</v>
+        <v>0.173720668130059</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.5031414016427378</v>
+        <v>0.5407266657096753</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7574,13 +7574,13 @@
         <v>0.75</v>
       </c>
       <c r="B77">
-        <v>0.2077669712589282</v>
+        <v>0.1733601607138749</v>
       </c>
       <c r="C77">
-        <v>-861.7191371154084</v>
+        <v>-777.5854407513848</v>
       </c>
       <c r="D77">
-        <v>312.8308628845916</v>
+        <v>396.9645592486153</v>
       </c>
       <c r="E77">
         <v>436.1500000000001</v>
@@ -7607,45 +7607,45 @@
         <v>136.125</v>
       </c>
       <c r="M77">
-        <v>312.32577</v>
+        <v>255.14652</v>
       </c>
       <c r="N77">
-        <v>-176.2007700000001</v>
+        <v>-119.0215200000001</v>
       </c>
       <c r="O77">
-        <v>-43.94447203800001</v>
+        <v>-29.68396708800002</v>
       </c>
       <c r="P77">
-        <v>-132.256297962</v>
+        <v>-89.33755291200005</v>
       </c>
       <c r="Q77">
-        <v>-33.75629796200005</v>
+        <v>9.162447087999951</v>
       </c>
       <c r="R77">
         <v>3</v>
       </c>
       <c r="S77">
-        <v>0.1738227073707383</v>
+        <v>0.1711954651905251</v>
       </c>
       <c r="T77">
-        <v>2.954743652481889</v>
+        <v>2.895969172991343</v>
       </c>
       <c r="U77">
-        <v>0.2458</v>
+        <v>0.2008</v>
       </c>
       <c r="V77">
-        <v>0.1086992437415587</v>
+        <v>0.1330591340222864</v>
       </c>
       <c r="W77">
-        <v>0.2190817258883249</v>
+        <v>0.1740817258883249</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y77">
-        <v>0.435842998161823</v>
+        <v>0.5335169768335463</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7656,13 +7656,13 @@
         <v>0.76</v>
       </c>
       <c r="B78">
-        <v>0.2097669712589283</v>
+        <v>0.1749101607138749</v>
       </c>
       <c r="C78">
-        <v>-882.4769161162977</v>
+        <v>-799.2931002737126</v>
       </c>
       <c r="D78">
-        <v>309.0150838837023</v>
+        <v>392.1988997262874</v>
       </c>
       <c r="E78">
         <v>453.0920000000001</v>
@@ -7689,45 +7689,45 @@
         <v>136.125</v>
       </c>
       <c r="M78">
-        <v>316.4901136</v>
+        <v>258.5484736</v>
       </c>
       <c r="N78">
-        <v>-180.3651136000001</v>
+        <v>-122.4234736000001</v>
       </c>
       <c r="O78">
-        <v>-44.98305933184002</v>
+        <v>-30.53241431584001</v>
       </c>
       <c r="P78">
-        <v>-135.38205426816</v>
+        <v>-91.89105928416004</v>
       </c>
       <c r="Q78">
-        <v>-36.88205426816003</v>
+        <v>6.608940715839964</v>
       </c>
       <c r="R78">
         <v>3.166666666666667</v>
       </c>
       <c r="S78">
-        <v>0.1791569868445191</v>
+        <v>0.1764202762401303</v>
       </c>
       <c r="T78">
-        <v>3.077857971335301</v>
+        <v>3.016634555199315</v>
       </c>
       <c r="U78">
-        <v>0.2458</v>
+        <v>0.2008</v>
       </c>
       <c r="V78">
-        <v>0.1072689905344329</v>
+        <v>0.1313083559430459</v>
       </c>
       <c r="W78">
-        <v>0.2194332821266364</v>
+        <v>0.1744332821266364</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y78">
-        <v>0.4301082218702201</v>
+        <v>0.5264970166120523</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7738,13 +7738,13 @@
         <v>0.77</v>
       </c>
       <c r="B79">
-        <v>0.2117669712589282</v>
+        <v>0.1764601607138749</v>
       </c>
       <c r="C79">
-        <v>-903.1427303371596</v>
+        <v>-820.8876913256015</v>
       </c>
       <c r="D79">
-        <v>305.2912696628405</v>
+        <v>387.5463086743986</v>
       </c>
       <c r="E79">
         <v>470.0340000000001</v>
@@ -7771,45 +7771,45 @@
         <v>136.125</v>
       </c>
       <c r="M79">
-        <v>320.6544572</v>
+        <v>261.9504272</v>
       </c>
       <c r="N79">
-        <v>-184.5294572000001</v>
+        <v>-125.8254272000001</v>
       </c>
       <c r="O79">
-        <v>-46.02164662568001</v>
+        <v>-31.38086154368002</v>
       </c>
       <c r="P79">
-        <v>-138.50781057432</v>
+        <v>-94.44456565632005</v>
       </c>
       <c r="Q79">
-        <v>-40.00781057432005</v>
+        <v>4.055434343679948</v>
       </c>
       <c r="R79">
         <v>3.347826086956522</v>
       </c>
       <c r="S79">
-        <v>0.1849551167073242</v>
+        <v>0.1820994186853534</v>
       </c>
       <c r="T79">
-        <v>3.211677883132488</v>
+        <v>3.147792579338416</v>
       </c>
       <c r="U79">
-        <v>0.2458</v>
+        <v>0.2008</v>
       </c>
       <c r="V79">
-        <v>0.1058758867612584</v>
+        <v>0.1296030526191102</v>
       </c>
       <c r="W79">
-        <v>0.2197757070340827</v>
+        <v>0.1747757070340827</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y79">
-        <v>0.4245224008069705</v>
+        <v>0.519659393019688</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7820,13 +7820,13 @@
         <v>0.78</v>
       </c>
       <c r="B80">
-        <v>0.2137669712589282</v>
+        <v>0.178010160713875</v>
       </c>
       <c r="C80">
-        <v>-923.7198648802741</v>
+        <v>-842.3731906693876</v>
       </c>
       <c r="D80">
-        <v>301.656135119726</v>
+        <v>383.0028093306125</v>
       </c>
       <c r="E80">
         <v>486.9760000000001</v>
@@ -7853,45 +7853,45 @@
         <v>136.125</v>
       </c>
       <c r="M80">
-        <v>324.8188008000001</v>
+        <v>265.3523808</v>
       </c>
       <c r="N80">
-        <v>-188.6938008000001</v>
+        <v>-129.2273808000001</v>
       </c>
       <c r="O80">
-        <v>-47.06023391952003</v>
+        <v>-32.22930877152002</v>
       </c>
       <c r="P80">
-        <v>-141.6335668804801</v>
+        <v>-96.99807202848007</v>
       </c>
       <c r="Q80">
-        <v>-43.13356688048009</v>
+        <v>1.501927971519933</v>
       </c>
       <c r="R80">
         <v>3.545454545454546</v>
       </c>
       <c r="S80">
-        <v>0.1912803492849299</v>
+        <v>0.1882948468074149</v>
       </c>
       <c r="T80">
-        <v>3.357663241456692</v>
+        <v>3.290874060217435</v>
       </c>
       <c r="U80">
-        <v>0.2458</v>
+        <v>0.2008</v>
       </c>
       <c r="V80">
-        <v>0.1045185035976525</v>
+        <v>0.1279414750214293</v>
       </c>
       <c r="W80">
-        <v>0.220109351815697</v>
+        <v>0.175109351815697</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y80">
-        <v>0.4190798059248297</v>
+        <v>0.5129970931091791</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7902,13 +7902,13 @@
         <v>0.79</v>
       </c>
       <c r="B81">
-        <v>0.2157669712589282</v>
+        <v>0.179560160713875</v>
       </c>
       <c r="C81">
-        <v>-944.2114502248313</v>
+        <v>-863.7533907380338</v>
       </c>
       <c r="D81">
-        <v>298.1065497751688</v>
+        <v>378.5646092619664</v>
       </c>
       <c r="E81">
         <v>503.9180000000001</v>
@@ -7935,45 +7935,45 @@
         <v>136.125</v>
       </c>
       <c r="M81">
-        <v>328.9831444000001</v>
+        <v>268.7543344</v>
       </c>
       <c r="N81">
-        <v>-192.8581444000001</v>
+        <v>-132.6293344</v>
       </c>
       <c r="O81">
-        <v>-48.09882121336003</v>
+        <v>-33.07775599936001</v>
       </c>
       <c r="P81">
-        <v>-144.7593231866401</v>
+        <v>-99.55157840064003</v>
       </c>
       <c r="Q81">
-        <v>-46.25932318664007</v>
+        <v>-1.051578400640025</v>
       </c>
       <c r="R81">
         <v>3.761904761904763</v>
       </c>
       <c r="S81">
-        <v>0.1982079849651646</v>
+        <v>0.1950803157030061</v>
       </c>
       <c r="T81">
-        <v>3.517551967240344</v>
+        <v>3.447582348799218</v>
       </c>
       <c r="U81">
-        <v>0.2458</v>
+        <v>0.2008</v>
       </c>
       <c r="V81">
-        <v>0.1031954845647709</v>
+        <v>0.1263219626793859</v>
       </c>
       <c r="W81">
-        <v>0.2204345498939793</v>
+        <v>0.1754345498939793</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y81">
-        <v>0.4137749982548952</v>
+        <v>0.5065034590191896</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7984,13 +7984,13 @@
         <v>0.8</v>
       </c>
       <c r="B82">
-        <v>0.2177669712589283</v>
+        <v>0.181110160713875</v>
       </c>
       <c r="C82">
-        <v>-964.6204712183725</v>
+        <v>-885.0319101927466</v>
       </c>
       <c r="D82">
-        <v>294.6395287816276</v>
+        <v>374.2280898072535</v>
       </c>
       <c r="E82">
         <v>520.8600000000001</v>
@@ -8017,45 +8017,45 @@
         <v>136.125</v>
       </c>
       <c r="M82">
-        <v>333.1474880000001</v>
+        <v>272.156288</v>
       </c>
       <c r="N82">
-        <v>-197.0224880000001</v>
+        <v>-136.031288</v>
       </c>
       <c r="O82">
-        <v>-49.13740850720003</v>
+        <v>-33.92620322720001</v>
       </c>
       <c r="P82">
-        <v>-147.8850794928001</v>
+        <v>-102.1050847728</v>
       </c>
       <c r="Q82">
-        <v>-49.38507949280006</v>
+        <v>-3.605084772800041</v>
       </c>
       <c r="R82">
         <v>4.000000000000001</v>
       </c>
       <c r="S82">
-        <v>0.2058283842134229</v>
+        <v>0.2025443314881564</v>
       </c>
       <c r="T82">
-        <v>3.693429565602362</v>
+        <v>3.619961466239179</v>
       </c>
       <c r="U82">
-        <v>0.2458</v>
+        <v>0.2008</v>
       </c>
       <c r="V82">
-        <v>0.1019055410077112</v>
+        <v>0.1247429381458935</v>
       </c>
       <c r="W82">
-        <v>0.2207516180203046</v>
+        <v>0.1757516180203046</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y82">
-        <v>0.408602810776709</v>
+        <v>0.5001721657814497</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8066,13 +8066,13 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2197669712589282</v>
+        <v>0.2115259951186807</v>
       </c>
       <c r="C83">
-        <v>-984.9497754480135</v>
+        <v>-970.656313342916</v>
       </c>
       <c r="D83">
-        <v>291.2522245519867</v>
+        <v>305.5456866570842</v>
       </c>
       <c r="E83">
         <v>537.8020000000001</v>
@@ -8099,37 +8099,37 @@
         <v>136.125</v>
       </c>
       <c r="M83">
-        <v>337.3118316000001</v>
+        <v>323.5888116</v>
       </c>
       <c r="N83">
-        <v>-201.1868316000001</v>
+        <v>-187.4638116000001</v>
       </c>
       <c r="O83">
-        <v>-50.17599580104002</v>
+        <v>-46.75347461304002</v>
       </c>
       <c r="P83">
-        <v>-151.0108357989601</v>
+        <v>-140.71033698696</v>
       </c>
       <c r="Q83">
-        <v>-52.51083579896007</v>
+        <v>-42.21033698696004</v>
       </c>
       <c r="R83">
         <v>4.263157894736843</v>
       </c>
       <c r="S83">
-        <v>0.2142509307509715</v>
+        <v>0.2135089510654581</v>
       </c>
       <c r="T83">
-        <v>3.887820595370907</v>
+        <v>3.873185936846608</v>
       </c>
       <c r="U83">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.1006474479088506</v>
+        <v>0.1049157875148239</v>
       </c>
       <c r="W83">
-        <v>0.2210608573040045</v>
+        <v>0.2110608573040045</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.4035583316313176</v>
+        <v>0.4206727646945626</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8148,13 +8148,13 @@
         <v>0.8200000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2217669712589283</v>
+        <v>0.2134259951186807</v>
       </c>
       <c r="C84">
-        <v>-1005.202081040799</v>
+        <v>-991.0615995965632</v>
       </c>
       <c r="D84">
-        <v>287.9419189592007</v>
+        <v>302.082400403437</v>
       </c>
       <c r="E84">
         <v>554.7440000000001</v>
@@ -8181,37 +8181,37 @@
         <v>136.125</v>
       </c>
       <c r="M84">
-        <v>341.4761752000001</v>
+        <v>327.5837352</v>
       </c>
       <c r="N84">
-        <v>-205.3511752000001</v>
+        <v>-191.4587352000001</v>
       </c>
       <c r="O84">
-        <v>-51.21458309488003</v>
+        <v>-47.74980855888002</v>
       </c>
       <c r="P84">
-        <v>-154.1365921051201</v>
+        <v>-143.7089266411201</v>
       </c>
       <c r="Q84">
-        <v>-55.63659210512006</v>
+        <v>-45.20892664112006</v>
       </c>
       <c r="R84">
         <v>4.555555555555557</v>
       </c>
       <c r="S84">
-        <v>0.2236093157926921</v>
+        <v>0.2228261150135391</v>
       </c>
       <c r="T84">
-        <v>4.10381062844707</v>
+        <v>4.088362933338086</v>
       </c>
       <c r="U84">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.09942004000752316</v>
+        <v>0.1036363266914724</v>
       </c>
       <c r="W84">
-        <v>0.2213625541661508</v>
+        <v>0.2113625541661508</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.398636888562643</v>
+        <v>0.4155426090275558</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8230,13 +8230,13 @@
         <v>0.8300000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2237669712589282</v>
+        <v>0.2153259951186807</v>
       </c>
       <c r="C85">
-        <v>-1025.379983938088</v>
+        <v>-1011.389254760331</v>
       </c>
       <c r="D85">
-        <v>284.7060160619126</v>
+        <v>298.6967452396688</v>
       </c>
       <c r="E85">
         <v>571.6860000000001</v>
@@ -8263,37 +8263,37 @@
         <v>136.125</v>
       </c>
       <c r="M85">
-        <v>345.6405188000001</v>
+        <v>331.5786588</v>
       </c>
       <c r="N85">
-        <v>-209.5155188000001</v>
+        <v>-195.4536588000001</v>
       </c>
       <c r="O85">
-        <v>-52.25317038872002</v>
+        <v>-48.74614250472002</v>
       </c>
       <c r="P85">
-        <v>-157.2623484112801</v>
+        <v>-146.70751629528</v>
       </c>
       <c r="Q85">
-        <v>-58.76234841128007</v>
+        <v>-48.20751629528004</v>
       </c>
       <c r="R85">
         <v>4.882352941176473</v>
       </c>
       <c r="S85">
-        <v>0.2340686873099093</v>
+        <v>0.2332394158966885</v>
       </c>
       <c r="T85">
-        <v>4.345211253649839</v>
+        <v>4.328854870593268</v>
       </c>
       <c r="U85">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.09822220820020361</v>
+        <v>0.1023876962494065</v>
       </c>
       <c r="W85">
-        <v>0.22165698122439</v>
+        <v>0.21165698122439</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8301,7 +8301,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.393834034483575</v>
+        <v>0.4105360715693924</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8312,13 +8312,13 @@
         <v>0.84</v>
       </c>
       <c r="B86">
-        <v>0.2257669712589283</v>
+        <v>0.2172259951186807</v>
       </c>
       <c r="C86">
-        <v>-1045.485964684891</v>
+        <v>-1031.641860106752</v>
       </c>
       <c r="D86">
-        <v>281.5420353151089</v>
+        <v>295.3861398932482</v>
       </c>
       <c r="E86">
         <v>588.6279999999999</v>
@@ -8345,37 +8345,37 @@
         <v>136.125</v>
       </c>
       <c r="M86">
-        <v>349.8048624</v>
+        <v>335.5735824</v>
       </c>
       <c r="N86">
-        <v>-213.6798624</v>
+        <v>-199.4485824</v>
       </c>
       <c r="O86">
-        <v>-53.29175768256</v>
+        <v>-49.74247645056001</v>
       </c>
       <c r="P86">
-        <v>-160.38810471744</v>
+        <v>-149.70610594944</v>
       </c>
       <c r="Q86">
-        <v>-61.88810471744</v>
+        <v>-51.20610594944003</v>
       </c>
       <c r="R86">
         <v>5.249999999999999</v>
       </c>
       <c r="S86">
-        <v>0.2458354802667785</v>
+        <v>0.2449543793902314</v>
       </c>
       <c r="T86">
-        <v>4.616786957002951</v>
+        <v>4.599408300005345</v>
       </c>
       <c r="U86">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.09705289619782025</v>
+        <v>0.1011687951035802</v>
       </c>
       <c r="W86">
-        <v>0.2219443981145758</v>
+        <v>0.2119443981145758</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3891455340730563</v>
+        <v>0.4056487373840425</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8394,13 +8394,13 @@
         <v>0.85</v>
       </c>
       <c r="B87">
-        <v>0.2277669712589283</v>
+        <v>0.2191259951186807</v>
       </c>
       <c r="C87">
-        <v>-1065.522394771486</v>
+        <v>-1051.821883724691</v>
       </c>
       <c r="D87">
-        <v>278.4476052285138</v>
+        <v>292.1481162753086</v>
       </c>
       <c r="E87">
         <v>605.5699999999999</v>
@@ -8427,37 +8427,37 @@
         <v>136.125</v>
       </c>
       <c r="M87">
-        <v>353.969206</v>
+        <v>339.568506</v>
       </c>
       <c r="N87">
-        <v>-217.844206</v>
+        <v>-203.443506</v>
       </c>
       <c r="O87">
-        <v>-54.33034497640001</v>
+        <v>-50.73881039640001</v>
       </c>
       <c r="P87">
-        <v>-163.5138610236</v>
+        <v>-152.7046956036</v>
       </c>
       <c r="Q87">
-        <v>-65.01386102360001</v>
+        <v>-54.20469560360004</v>
       </c>
       <c r="R87">
         <v>5.666666666666666</v>
       </c>
       <c r="S87">
-        <v>0.2591711789512304</v>
+        <v>0.2582313380162468</v>
       </c>
       <c r="T87">
-        <v>4.924572754136481</v>
+        <v>4.906035520005702</v>
       </c>
       <c r="U87">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.09591109741902237</v>
+        <v>0.09997857398471456</v>
       </c>
       <c r="W87">
-        <v>0.2222250522544043</v>
+        <v>0.2122250522544043</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8465,7 +8465,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3845673513192557</v>
+        <v>0.4008763992971714</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8476,13 +8476,13 @@
         <v>0.86</v>
       </c>
       <c r="B88">
-        <v>0.2297669712589283</v>
+        <v>0.2210259951186807</v>
       </c>
       <c r="C88">
-        <v>-1085.491542561364</v>
+        <v>-1071.931686655684</v>
       </c>
       <c r="D88">
-        <v>275.4204574386357</v>
+        <v>288.9803133443158</v>
       </c>
       <c r="E88">
         <v>622.5119999999999</v>
@@ -8509,37 +8509,37 @@
         <v>136.125</v>
       </c>
       <c r="M88">
-        <v>358.1335496</v>
+        <v>343.5634296</v>
       </c>
       <c r="N88">
-        <v>-222.0085496000001</v>
+        <v>-207.4384296</v>
       </c>
       <c r="O88">
-        <v>-55.36893227024002</v>
+        <v>-51.73514434224001</v>
       </c>
       <c r="P88">
-        <v>-166.6396173297601</v>
+        <v>-155.70328525776</v>
       </c>
       <c r="Q88">
-        <v>-68.13961732976006</v>
+        <v>-57.20328525776003</v>
       </c>
       <c r="R88">
         <v>6.142857142857142</v>
       </c>
       <c r="S88">
-        <v>0.2744119774477469</v>
+        <v>0.2734050050174073</v>
       </c>
       <c r="T88">
-        <v>5.276327950860515</v>
+        <v>5.256466628577538</v>
       </c>
       <c r="U88">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.0947958521001965</v>
+        <v>0.09881603242675277</v>
       </c>
       <c r="W88">
-        <v>0.2224991795537717</v>
+        <v>0.2124991795537717</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3800956379318224</v>
+        <v>0.3962150458169718</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8558,13 +8558,13 @@
         <v>0.87</v>
       </c>
       <c r="B89">
-        <v>0.2317669712589283</v>
+        <v>0.2229259951186807</v>
       </c>
       <c r="C89">
-        <v>-1105.395578836668</v>
+        <v>-1091.973528635323</v>
       </c>
       <c r="D89">
-        <v>272.4584211633322</v>
+        <v>285.8804713646768</v>
       </c>
       <c r="E89">
         <v>639.454</v>
@@ -8591,37 +8591,37 @@
         <v>136.125</v>
       </c>
       <c r="M89">
-        <v>362.2978932</v>
+        <v>347.5583532</v>
       </c>
       <c r="N89">
-        <v>-226.1728932000001</v>
+        <v>-211.4333532</v>
       </c>
       <c r="O89">
-        <v>-56.40751956408002</v>
+        <v>-52.73147828808001</v>
       </c>
       <c r="P89">
-        <v>-169.76537363592</v>
+        <v>-158.70187491192</v>
       </c>
       <c r="Q89">
-        <v>-71.26537363592004</v>
+        <v>-60.20187491192002</v>
       </c>
       <c r="R89">
         <v>6.692307692307692</v>
       </c>
       <c r="S89">
-        <v>0.2919975141744966</v>
+        <v>0.2909130823264387</v>
       </c>
       <c r="T89">
-        <v>5.682199331695939</v>
+        <v>5.660810215391195</v>
       </c>
       <c r="U89">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.09370624460479195</v>
+        <v>0.09768021596207746</v>
       </c>
       <c r="W89">
-        <v>0.2227670050761422</v>
+        <v>0.2127670050761422</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3757267225532958</v>
+        <v>0.3916608498880411</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8640,13 +8640,13 @@
         <v>0.88</v>
       </c>
       <c r="B90">
-        <v>0.2337669712589282</v>
+        <v>0.2248259951186807</v>
       </c>
       <c r="C90">
-        <v>-1125.236581989599</v>
+        <v>-1111.949573469051</v>
       </c>
       <c r="D90">
-        <v>269.5594180104003</v>
+        <v>282.8464265309487</v>
       </c>
       <c r="E90">
         <v>656.396</v>
@@ -8673,37 +8673,37 @@
         <v>136.125</v>
       </c>
       <c r="M90">
-        <v>366.4622368</v>
+        <v>351.5532768</v>
       </c>
       <c r="N90">
-        <v>-230.3372368000001</v>
+        <v>-215.4282768</v>
       </c>
       <c r="O90">
-        <v>-57.44610685792001</v>
+        <v>-53.72781223392001</v>
       </c>
       <c r="P90">
-        <v>-172.8911299420801</v>
+        <v>-161.70046456608</v>
       </c>
       <c r="Q90">
-        <v>-74.39112994208006</v>
+        <v>-63.20046456608003</v>
       </c>
       <c r="R90">
         <v>7.333333333333334</v>
       </c>
       <c r="S90">
-        <v>0.312513973689038</v>
+        <v>0.3113391725203086</v>
       </c>
       <c r="T90">
-        <v>6.155715942670602</v>
+        <v>6.132544400007129</v>
       </c>
       <c r="U90">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.09264140091610114</v>
+        <v>0.09657021350796294</v>
       </c>
       <c r="W90">
-        <v>0.2230287436548223</v>
+        <v>0.2130287436548224</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3714571007060992</v>
+        <v>0.3872101584120407</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8722,13 +8722,13 @@
         <v>0.89</v>
       </c>
       <c r="B91">
-        <v>0.2357669712589283</v>
+        <v>0.2267259951186807</v>
       </c>
       <c r="C91">
-        <v>-1145.016542885896</v>
+        <v>-1131.86189406923</v>
       </c>
       <c r="D91">
-        <v>266.7214571141035</v>
+        <v>279.8761059307702</v>
       </c>
       <c r="E91">
         <v>673.338</v>
@@ -8755,37 +8755,37 @@
         <v>136.125</v>
       </c>
       <c r="M91">
-        <v>370.6265804</v>
+        <v>355.5482004</v>
       </c>
       <c r="N91">
-        <v>-234.5015804000001</v>
+        <v>-219.4232004</v>
       </c>
       <c r="O91">
-        <v>-58.48469415176002</v>
+        <v>-54.72414617976001</v>
       </c>
       <c r="P91">
-        <v>-176.01688624824</v>
+        <v>-164.69905422024</v>
       </c>
       <c r="Q91">
-        <v>-77.51688624824004</v>
+        <v>-66.19905422024001</v>
       </c>
       <c r="R91">
         <v>8.090909090909092</v>
       </c>
       <c r="S91">
-        <v>0.3367606985698598</v>
+        <v>0.3354790972948821</v>
       </c>
       <c r="T91">
-        <v>6.715326482913386</v>
+        <v>6.690048436371413</v>
       </c>
       <c r="U91">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.09160048629906629</v>
+        <v>0.09548515492922179</v>
       </c>
       <c r="W91">
-        <v>0.2232846004676895</v>
+        <v>0.2132846004676895</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3672834254172666</v>
+        <v>0.3828594824748267</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8804,13 +8804,13 @@
         <v>0.9</v>
       </c>
       <c r="B92">
-        <v>0.2377669712589282</v>
+        <v>0.2286259951186807</v>
       </c>
       <c r="C92">
-        <v>-1164.737369424284</v>
+        <v>-1151.712477178121</v>
       </c>
       <c r="D92">
-        <v>263.9426305757157</v>
+        <v>276.9675228218788</v>
       </c>
       <c r="E92">
         <v>690.28</v>
@@ -8837,37 +8837,37 @@
         <v>136.125</v>
       </c>
       <c r="M92">
-        <v>374.790924</v>
+        <v>359.543124</v>
       </c>
       <c r="N92">
-        <v>-238.665924</v>
+        <v>-223.4181240000001</v>
       </c>
       <c r="O92">
-        <v>-59.52328144560001</v>
+        <v>-55.72048012560002</v>
       </c>
       <c r="P92">
-        <v>-179.1426425544</v>
+        <v>-167.6976438744001</v>
       </c>
       <c r="Q92">
-        <v>-80.64264255440003</v>
+        <v>-69.19764387440006</v>
       </c>
       <c r="R92">
         <v>9.000000000000002</v>
       </c>
       <c r="S92">
-        <v>0.3658567684268457</v>
+        <v>0.3644470070243704</v>
       </c>
       <c r="T92">
-        <v>7.386859131204724</v>
+        <v>7.359053280008555</v>
       </c>
       <c r="U92">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.09058270311796555</v>
+        <v>0.09442420876334154</v>
       </c>
       <c r="W92">
-        <v>0.2235347715736041</v>
+        <v>0.2135347715736041</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3632024984681859</v>
+        <v>0.3786054882251063</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8886,13 +8886,13 @@
         <v>0.91</v>
       </c>
       <c r="B93">
-        <v>0.2397669712589282</v>
+        <v>0.2305259951186807</v>
       </c>
       <c r="C93">
-        <v>-1184.400890813855</v>
+        <v>-1171.503227799405</v>
       </c>
       <c r="D93">
-        <v>261.2211091861449</v>
+        <v>274.1187722005951</v>
       </c>
       <c r="E93">
         <v>707.2220000000002</v>
@@ -8919,37 +8919,37 @@
         <v>136.125</v>
       </c>
       <c r="M93">
-        <v>378.9552676000001</v>
+        <v>363.5380476000001</v>
       </c>
       <c r="N93">
-        <v>-242.8302676000001</v>
+        <v>-227.4130476000001</v>
       </c>
       <c r="O93">
-        <v>-60.56186873944003</v>
+        <v>-56.71681407144003</v>
       </c>
       <c r="P93">
-        <v>-182.2683988605601</v>
+        <v>-170.6962335285601</v>
       </c>
       <c r="Q93">
-        <v>-83.76839886056007</v>
+        <v>-72.19623352856007</v>
       </c>
       <c r="R93">
         <v>10.11111111111111</v>
       </c>
       <c r="S93">
-        <v>0.4014186315853842</v>
+        <v>0.3998522300270782</v>
       </c>
       <c r="T93">
-        <v>8.207621256894138</v>
+        <v>8.176725866676172</v>
       </c>
       <c r="U93">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.08958728879798791</v>
+        <v>0.09338658009561249</v>
       </c>
       <c r="W93">
-        <v>0.2237794444134546</v>
+        <v>0.2137794444134546</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3592112622212826</v>
+        <v>0.3744449883545008</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8968,13 +8968,13 @@
         <v>0.92</v>
       </c>
       <c r="B94">
-        <v>0.2417669712589282</v>
+        <v>0.2324259951186807</v>
       </c>
       <c r="C94">
-        <v>-1204.008861589522</v>
+        <v>-1191.235973358993</v>
       </c>
       <c r="D94">
-        <v>258.5551384104779</v>
+        <v>271.3280266410072</v>
       </c>
       <c r="E94">
         <v>724.1640000000002</v>
@@ -9001,37 +9001,37 @@
         <v>136.125</v>
       </c>
       <c r="M94">
-        <v>383.1196112000001</v>
+        <v>367.5329712000001</v>
       </c>
       <c r="N94">
-        <v>-246.9946112000001</v>
+        <v>-231.4079712000001</v>
       </c>
       <c r="O94">
-        <v>-61.60045603328003</v>
+        <v>-57.71314801728003</v>
       </c>
       <c r="P94">
-        <v>-185.3941551667201</v>
+        <v>-173.6948231827201</v>
       </c>
       <c r="Q94">
-        <v>-86.89415516672005</v>
+        <v>-75.19482318272009</v>
       </c>
       <c r="R94">
         <v>11.50000000000001</v>
       </c>
       <c r="S94">
-        <v>0.4458709605335573</v>
+        <v>0.4441087587804631</v>
       </c>
       <c r="T94">
-        <v>9.233573914005907</v>
+        <v>9.198816600010698</v>
       </c>
       <c r="U94">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.08861351391974891</v>
+        <v>0.09237150857283409</v>
       </c>
       <c r="W94">
-        <v>0.2240187982785257</v>
+        <v>0.2140187982785257</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.355306791979747</v>
+        <v>0.3703749341332562</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9050,13 +9050,13 @@
         <v>0.93</v>
       </c>
       <c r="B95">
-        <v>0.2437669712589282</v>
+        <v>0.2343259951186807</v>
       </c>
       <c r="C95">
-        <v>-1223.562965384072</v>
+        <v>-1210.912467614246</v>
       </c>
       <c r="D95">
-        <v>255.9430346159282</v>
+        <v>268.5935323857542</v>
       </c>
       <c r="E95">
         <v>741.1060000000002</v>
@@ -9083,37 +9083,37 @@
         <v>136.125</v>
       </c>
       <c r="M95">
-        <v>387.2839548000001</v>
+        <v>371.5278948000001</v>
       </c>
       <c r="N95">
-        <v>-251.1589548000001</v>
+        <v>-235.4028948000001</v>
       </c>
       <c r="O95">
-        <v>-62.63904332712003</v>
+        <v>-58.70948196312003</v>
       </c>
       <c r="P95">
-        <v>-188.5199114728801</v>
+        <v>-176.6934128368801</v>
       </c>
       <c r="Q95">
-        <v>-90.01991147288007</v>
+        <v>-78.19341283688007</v>
       </c>
       <c r="R95">
         <v>13.2857142857143</v>
       </c>
       <c r="S95">
-        <v>0.5030239548954941</v>
+        <v>0.501010010034815</v>
       </c>
       <c r="T95">
-        <v>10.55265590172104</v>
+        <v>10.51293325715508</v>
       </c>
       <c r="U95">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.08766068043674086</v>
+        <v>0.09137826654516921</v>
       </c>
       <c r="W95">
-        <v>0.2242530047486491</v>
+        <v>0.2142530047486491</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3514862888401799</v>
+        <v>0.3663924079597803</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9132,13 +9132,13 @@
         <v>0.9400000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2457669712589283</v>
+        <v>0.2362259951186807</v>
       </c>
       <c r="C96">
-        <v>-1243.064818473856</v>
+        <v>-1230.534394329162</v>
       </c>
       <c r="D96">
-        <v>253.3831815261446</v>
+        <v>265.9136056708386</v>
       </c>
       <c r="E96">
         <v>758.0480000000002</v>
@@ -9165,37 +9165,37 @@
         <v>136.125</v>
       </c>
       <c r="M96">
-        <v>391.4482984000001</v>
+        <v>375.5228184000001</v>
       </c>
       <c r="N96">
-        <v>-255.3232984000001</v>
+        <v>-239.3978184000001</v>
       </c>
       <c r="O96">
-        <v>-63.67763062096004</v>
+        <v>-59.70581590896003</v>
       </c>
       <c r="P96">
-        <v>-191.6456677790401</v>
+        <v>-179.6920024910401</v>
       </c>
       <c r="Q96">
-        <v>-93.14566777904011</v>
+        <v>-81.19200249104006</v>
       </c>
       <c r="R96">
         <v>15.66666666666668</v>
       </c>
       <c r="S96">
-        <v>0.5792279473780765</v>
+        <v>0.5768783450406176</v>
       </c>
       <c r="T96">
-        <v>12.31143188534121</v>
+        <v>12.26508880001427</v>
       </c>
       <c r="U96">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.08672812000656274</v>
+        <v>0.09040615732660358</v>
       </c>
       <c r="W96">
-        <v>0.2244822281023869</v>
+        <v>0.2144822281023869</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3477470730014545</v>
+        <v>0.3624946163857401</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9214,13 +9214,13 @@
         <v>0.9500000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2477669712589283</v>
+        <v>0.2381259951186807</v>
       </c>
       <c r="C97">
-        <v>-1262.515973113812</v>
+        <v>-1250.103370731716</v>
       </c>
       <c r="D97">
-        <v>250.8740268861882</v>
+        <v>263.286629268284</v>
       </c>
       <c r="E97">
         <v>774.9900000000002</v>
@@ -9247,37 +9247,37 @@
         <v>136.125</v>
       </c>
       <c r="M97">
-        <v>395.6126420000001</v>
+        <v>379.5177420000001</v>
       </c>
       <c r="N97">
-        <v>-259.4876420000002</v>
+        <v>-243.3927420000001</v>
       </c>
       <c r="O97">
-        <v>-64.71621791480004</v>
+        <v>-60.70214985480003</v>
       </c>
       <c r="P97">
-        <v>-194.7714240852001</v>
+        <v>-182.6905921452001</v>
       </c>
       <c r="Q97">
-        <v>-96.27142408520012</v>
+        <v>-84.19059214520007</v>
       </c>
       <c r="R97">
         <v>19.00000000000003</v>
       </c>
       <c r="S97">
-        <v>0.6859135368536922</v>
+        <v>0.6830940140487415</v>
       </c>
       <c r="T97">
-        <v>14.77371826240947</v>
+        <v>14.71810656001713</v>
       </c>
       <c r="U97">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.0858151924275463</v>
+        <v>0.08945451356527093</v>
       </c>
       <c r="W97">
-        <v>0.2247066257013091</v>
+        <v>0.2147066257013091</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3440865774961759</v>
+        <v>0.3586788835816797</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9296,13 +9296,13 @@
         <v>0.96</v>
       </c>
       <c r="B98">
-        <v>0.2497669712589282</v>
+        <v>0.2400259951186807</v>
       </c>
       <c r="C98">
-        <v>-1281.91792067628</v>
+        <v>-1269.620950768282</v>
       </c>
       <c r="D98">
-        <v>248.41407932372</v>
+        <v>260.7110492317186</v>
       </c>
       <c r="E98">
         <v>791.932</v>
@@ -9329,37 +9329,37 @@
         <v>136.125</v>
       </c>
       <c r="M98">
-        <v>399.7769856</v>
+        <v>383.5126656</v>
       </c>
       <c r="N98">
-        <v>-263.6519856000001</v>
+        <v>-247.3876656</v>
       </c>
       <c r="O98">
-        <v>-65.75480520864002</v>
+        <v>-61.69848380064001</v>
       </c>
       <c r="P98">
-        <v>-197.8971803913601</v>
+        <v>-185.68918179936</v>
       </c>
       <c r="Q98">
-        <v>-99.39718039136008</v>
+        <v>-87.18918179936003</v>
       </c>
       <c r="R98">
         <v>23.99999999999998</v>
       </c>
       <c r="S98">
-        <v>0.8459419210671134</v>
+        <v>0.842417517560925</v>
       </c>
       <c r="T98">
-        <v>18.46714782801179</v>
+        <v>18.39763320002137</v>
       </c>
       <c r="U98">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.08492128417309271</v>
+        <v>0.08852269571563269</v>
       </c>
       <c r="W98">
-        <v>0.2249263483502538</v>
+        <v>0.2149263483502538</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3405023423139242</v>
+        <v>0.3549426452110372</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9378,13 +9378,13 @@
         <v>0.97</v>
       </c>
       <c r="B99">
-        <v>0.2517669712589282</v>
+        <v>0.2419259951186807</v>
       </c>
       <c r="C99">
-        <v>-1301.272094606938</v>
+        <v>-1289.088628168875</v>
       </c>
       <c r="D99">
-        <v>246.0019053930619</v>
+        <v>258.1853718311245</v>
       </c>
       <c r="E99">
         <v>808.874</v>
@@ -9411,37 +9411,37 @@
         <v>136.125</v>
       </c>
       <c r="M99">
-        <v>403.9413292</v>
+        <v>387.5075892</v>
       </c>
       <c r="N99">
-        <v>-267.8163292</v>
+        <v>-251.3825892000001</v>
       </c>
       <c r="O99">
-        <v>-66.79339250248002</v>
+        <v>-62.69481774648002</v>
       </c>
       <c r="P99">
-        <v>-201.02293669752</v>
+        <v>-188.68777145352</v>
       </c>
       <c r="Q99">
-        <v>-102.52293669752</v>
+        <v>-90.18777145352004</v>
       </c>
       <c r="R99">
         <v>32.33333333333331</v>
       </c>
       <c r="S99">
-        <v>1.112655894756151</v>
+        <v>1.107956690081233</v>
       </c>
       <c r="T99">
-        <v>24.62286377068239</v>
+        <v>24.53017760002849</v>
       </c>
       <c r="U99">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.08404580701666908</v>
+        <v>0.08761009060516224</v>
       </c>
       <c r="W99">
-        <v>0.2251415406353028</v>
+        <v>0.2151415406353027</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3369920088880075</v>
+        <v>0.3512834426830884</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9460,13 +9460,13 @@
         <v>0.98</v>
       </c>
       <c r="B100">
-        <v>0.2537669712589282</v>
+        <v>0.2438259951186807</v>
       </c>
       <c r="C100">
-        <v>-1320.579873210183</v>
+        <v>-1308.50783933595</v>
       </c>
       <c r="D100">
-        <v>243.6361267898166</v>
+        <v>255.7081606640496</v>
       </c>
       <c r="E100">
         <v>825.816</v>
@@ -9493,37 +9493,37 @@
         <v>136.125</v>
       </c>
       <c r="M100">
-        <v>408.1056728</v>
+        <v>391.5025128</v>
       </c>
       <c r="N100">
-        <v>-271.9806728000001</v>
+        <v>-255.3775128000001</v>
       </c>
       <c r="O100">
-        <v>-67.83197979632003</v>
+        <v>-63.69115169232002</v>
       </c>
       <c r="P100">
-        <v>-204.1486930036801</v>
+        <v>-191.6863611076801</v>
       </c>
       <c r="Q100">
-        <v>-105.6486930036801</v>
+        <v>-93.18636110768006</v>
       </c>
       <c r="R100">
         <v>48.99999999999996</v>
       </c>
       <c r="S100">
-        <v>1.646083842134227</v>
+        <v>1.63903503512185</v>
       </c>
       <c r="T100">
-        <v>36.93429565602358</v>
+        <v>36.79526640004273</v>
       </c>
       <c r="U100">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.08318819674098878</v>
+        <v>0.08671611008878304</v>
       </c>
       <c r="W100">
-        <v>0.225352341241065</v>
+        <v>0.215352341241065</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9531,7 +9531,7 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3335533149197625</v>
+        <v>0.3476989177577507</v>
       </c>
       <c r="Z100">
         <v>0</v>
@@ -9542,13 +9542,13 @@
         <v>0.99</v>
       </c>
       <c r="B101">
-        <v>0.2557669712589283</v>
+        <v>0.2457259951186807</v>
       </c>
       <c r="C101">
-        <v>-1339.842582275319</v>
+        <v>-1327.879966068461</v>
       </c>
       <c r="D101">
-        <v>241.3154177246811</v>
+        <v>253.2780339315389</v>
       </c>
       <c r="E101">
         <v>842.758</v>
@@ -9575,37 +9575,37 @@
         <v>136.125</v>
       </c>
       <c r="M101">
-        <v>412.2700164</v>
+        <v>395.4974364</v>
       </c>
       <c r="N101">
-        <v>-276.1450164</v>
+        <v>-259.3724364000001</v>
       </c>
       <c r="O101">
-        <v>-68.87056709016001</v>
+        <v>-64.68748563816003</v>
       </c>
       <c r="P101">
-        <v>-207.27444930984</v>
+        <v>-194.6849507618401</v>
       </c>
       <c r="Q101">
-        <v>-108.77444930984</v>
+        <v>-96.18495076184007</v>
       </c>
       <c r="R101">
         <v>98.99999999999991</v>
       </c>
       <c r="S101">
-        <v>3.246367684268454</v>
+        <v>3.2322700702437</v>
       </c>
       <c r="T101">
-        <v>73.86859131204716</v>
+        <v>73.59053280008547</v>
       </c>
       <c r="U101">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V101">
-        <v>0.08234791192542323</v>
+        <v>0.08584018978485594</v>
       </c>
       <c r="W101">
-        <v>0.225558883248731</v>
+        <v>0.215558883248731</v>
       </c>
       <c r="X101" t="inlineStr">
         <is>
@@ -9613,7 +9613,7 @@
         </is>
       </c>
       <c r="Y101">
-        <v>0.3301840895165327</v>
+        <v>0.3441868074773694</v>
       </c>
       <c r="Z101">
         <v>0</v>

--- a/research/traditional_assets/database/data/luxembourg/luxembourg_environmental_waste_services.xlsx
+++ b/research/traditional_assets/database/data/luxembourg/luxembourg_environmental_waste_services.xlsx
@@ -1284,7 +1284,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1421,22 +1421,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08062411637343692</v>
+        <v>0.08045681682720156</v>
       </c>
       <c r="C2">
-        <v>1550.174596824246</v>
+        <v>1540.251880258555</v>
       </c>
       <c r="D2">
-        <v>1454.074596824246</v>
+        <v>1461.093880258555</v>
       </c>
       <c r="E2">
-        <v>-834.5</v>
+        <v>-817.558</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>16.942</v>
       </c>
       <c r="G2">
         <v>96.09999999999999</v>
@@ -1457,28 +1457,28 @@
         <v>136.125</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.8521826000000001</v>
       </c>
       <c r="N2">
-        <v>136.125</v>
+        <v>135.2728174</v>
       </c>
       <c r="O2">
-        <v>33.949575</v>
+        <v>33.73704065955999</v>
       </c>
       <c r="P2">
-        <v>102.175425</v>
+        <v>101.53577674044</v>
       </c>
       <c r="Q2">
-        <v>200.675425</v>
+        <v>200.03577674044</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08062411637343692</v>
+        <v>0.08088814649212278</v>
       </c>
       <c r="T2">
-        <v>0.8042521102410373</v>
+        <v>0.8103498035132284</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>159.7368920698451</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1503,22 +1503,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08045681682720156</v>
+        <v>0.0802895172809662</v>
       </c>
       <c r="C3">
-        <v>1540.251880258555</v>
+        <v>1530.397261075839</v>
       </c>
       <c r="D3">
-        <v>1461.093880258555</v>
+        <v>1468.181261075839</v>
       </c>
       <c r="E3">
-        <v>-817.558</v>
+        <v>-800.616</v>
       </c>
       <c r="F3">
-        <v>16.942</v>
+        <v>33.884</v>
       </c>
       <c r="G3">
         <v>96.09999999999999</v>
@@ -1539,28 +1539,28 @@
         <v>136.125</v>
       </c>
       <c r="M3">
-        <v>0.8521826000000001</v>
+        <v>1.7043652</v>
       </c>
       <c r="N3">
-        <v>135.2728174</v>
+        <v>134.4206348</v>
       </c>
       <c r="O3">
-        <v>33.73704065955999</v>
+        <v>33.52450631911999</v>
       </c>
       <c r="P3">
-        <v>101.53577674044</v>
+        <v>100.89612848088</v>
       </c>
       <c r="Q3">
-        <v>200.03577674044</v>
+        <v>199.39612848088</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08088814649212278</v>
+        <v>0.08115756498057776</v>
       </c>
       <c r="T3">
-        <v>0.8103498035132284</v>
+        <v>0.8165719395052602</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>159.7368920698451</v>
+        <v>79.86844603492253</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1585,22 +1585,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.0802895172809662</v>
+        <v>0.08012221773473084</v>
       </c>
       <c r="C4">
-        <v>1530.397261075839</v>
+        <v>1520.61173507375</v>
       </c>
       <c r="D4">
-        <v>1468.181261075839</v>
+        <v>1475.33773507375</v>
       </c>
       <c r="E4">
-        <v>-800.616</v>
+        <v>-783.674</v>
       </c>
       <c r="F4">
-        <v>33.884</v>
+        <v>50.826</v>
       </c>
       <c r="G4">
         <v>96.09999999999999</v>
@@ -1621,28 +1621,28 @@
         <v>136.125</v>
       </c>
       <c r="M4">
-        <v>1.7043652</v>
+        <v>2.5565478</v>
       </c>
       <c r="N4">
-        <v>134.4206348</v>
+        <v>133.5684522</v>
       </c>
       <c r="O4">
-        <v>33.52450631911999</v>
+        <v>33.31197197867999</v>
       </c>
       <c r="P4">
-        <v>100.89612848088</v>
+        <v>100.25648022132</v>
       </c>
       <c r="Q4">
-        <v>199.39612848088</v>
+        <v>198.75648022132</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08115756498057776</v>
+        <v>0.08143253848941324</v>
       </c>
       <c r="T4">
-        <v>0.8165719395052602</v>
+        <v>0.8229223669610451</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>79.86844603492253</v>
+        <v>53.24563068994836</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1667,22 +1667,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08012221773473084</v>
+        <v>0.0799549181884955</v>
       </c>
       <c r="C5">
-        <v>1520.61173507375</v>
+        <v>1510.896317560628</v>
       </c>
       <c r="D5">
-        <v>1475.33773507375</v>
+        <v>1482.564317560628</v>
       </c>
       <c r="E5">
-        <v>-783.674</v>
+        <v>-766.732</v>
       </c>
       <c r="F5">
-        <v>50.826</v>
+        <v>67.768</v>
       </c>
       <c r="G5">
         <v>96.09999999999999</v>
@@ -1703,28 +1703,28 @@
         <v>136.125</v>
       </c>
       <c r="M5">
-        <v>2.5565478</v>
+        <v>3.4087304</v>
       </c>
       <c r="N5">
-        <v>133.5684522</v>
+        <v>132.7162696</v>
       </c>
       <c r="O5">
-        <v>33.31197197867999</v>
+        <v>33.09943763824</v>
       </c>
       <c r="P5">
-        <v>100.25648022132</v>
+        <v>99.61683196175997</v>
       </c>
       <c r="Q5">
-        <v>198.75648022132</v>
+        <v>198.11683196176</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08143253848941324</v>
+        <v>0.08171324061301614</v>
       </c>
       <c r="T5">
-        <v>0.8229223669610451</v>
+        <v>0.8294050949888256</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>53.24563068994836</v>
+        <v>39.93422301746127</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1749,22 +1749,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.0799549181884955</v>
+        <v>0.07978761864226015</v>
       </c>
       <c r="C6">
-        <v>1510.896317560628</v>
+        <v>1501.252043835696</v>
       </c>
       <c r="D6">
-        <v>1482.564317560628</v>
+        <v>1489.862043835696</v>
       </c>
       <c r="E6">
-        <v>-766.732</v>
+        <v>-749.79</v>
       </c>
       <c r="F6">
-        <v>67.768</v>
+        <v>84.71000000000001</v>
       </c>
       <c r="G6">
         <v>96.09999999999999</v>
@@ -1785,28 +1785,28 @@
         <v>136.125</v>
       </c>
       <c r="M6">
-        <v>3.4087304</v>
+        <v>4.260913</v>
       </c>
       <c r="N6">
-        <v>132.7162696</v>
+        <v>131.864087</v>
       </c>
       <c r="O6">
-        <v>33.09943763824</v>
+        <v>32.8869032978</v>
       </c>
       <c r="P6">
-        <v>99.61683196175997</v>
+        <v>98.97718370219999</v>
       </c>
       <c r="Q6">
-        <v>198.11683196176</v>
+        <v>197.4771837022</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08171324061301614</v>
+        <v>0.08199985225501069</v>
       </c>
       <c r="T6">
-        <v>0.8294050949888256</v>
+        <v>0.8360243015014016</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>39.93422301746127</v>
+        <v>31.94737841396902</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1831,22 +1831,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.07978761864226015</v>
+        <v>0.07962031909602479</v>
       </c>
       <c r="C7">
-        <v>1501.252043835696</v>
+        <v>1491.679969683506</v>
       </c>
       <c r="D7">
-        <v>1489.862043835696</v>
+        <v>1497.231969683506</v>
       </c>
       <c r="E7">
-        <v>-749.79</v>
+        <v>-732.848</v>
       </c>
       <c r="F7">
-        <v>84.71000000000001</v>
+        <v>101.652</v>
       </c>
       <c r="G7">
         <v>96.09999999999999</v>
@@ -1867,28 +1867,28 @@
         <v>136.125</v>
       </c>
       <c r="M7">
-        <v>4.260913</v>
+        <v>5.113095600000001</v>
       </c>
       <c r="N7">
-        <v>131.864087</v>
+        <v>131.0119044</v>
       </c>
       <c r="O7">
-        <v>32.8869032978</v>
+        <v>32.67436895736</v>
       </c>
       <c r="P7">
-        <v>98.97718370219999</v>
+        <v>98.33753544263996</v>
       </c>
       <c r="Q7">
-        <v>197.4771837022</v>
+        <v>196.83753544264</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.08199985225501069</v>
+        <v>0.08229256201704765</v>
       </c>
       <c r="T7">
-        <v>0.8360243015014016</v>
+        <v>0.842784342195096</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>31.94737841396902</v>
+        <v>26.62281534497417</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1913,22 +1913,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.07962031909602479</v>
+        <v>0.07945301954978946</v>
       </c>
       <c r="C8">
-        <v>1491.679969683506</v>
+        <v>1482.181171883133</v>
       </c>
       <c r="D8">
-        <v>1497.231969683506</v>
+        <v>1504.675171883133</v>
       </c>
       <c r="E8">
-        <v>-732.848</v>
+        <v>-715.9059999999999</v>
       </c>
       <c r="F8">
-        <v>101.652</v>
+        <v>118.594</v>
       </c>
       <c r="G8">
         <v>96.09999999999999</v>
@@ -1949,28 +1949,28 @@
         <v>136.125</v>
       </c>
       <c r="M8">
-        <v>5.1130956</v>
+        <v>5.9652782</v>
       </c>
       <c r="N8">
-        <v>131.0119044</v>
+        <v>130.1597218</v>
       </c>
       <c r="O8">
-        <v>32.67436895736</v>
+        <v>32.46183461691999</v>
       </c>
       <c r="P8">
-        <v>98.33753544263996</v>
+        <v>97.69788718307998</v>
       </c>
       <c r="Q8">
-        <v>196.83753544264</v>
+        <v>196.19788718308</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.08229256201704765</v>
+        <v>0.08259156661267683</v>
       </c>
       <c r="T8">
-        <v>0.842784342195096</v>
+        <v>0.84968976010801</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>26.62281534497418</v>
+        <v>22.81955600997787</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1995,22 +1995,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.07945301954978945</v>
+        <v>0.07928572000355411</v>
       </c>
       <c r="C9">
-        <v>1482.181171883134</v>
+        <v>1472.756748732636</v>
       </c>
       <c r="D9">
-        <v>1504.675171883134</v>
+        <v>1512.192748732636</v>
       </c>
       <c r="E9">
-        <v>-715.9059999999999</v>
+        <v>-698.9639999999999</v>
       </c>
       <c r="F9">
-        <v>118.594</v>
+        <v>135.536</v>
       </c>
       <c r="G9">
         <v>96.09999999999999</v>
@@ -2031,28 +2031,28 @@
         <v>136.125</v>
       </c>
       <c r="M9">
-        <v>5.965278200000001</v>
+        <v>6.817460800000001</v>
       </c>
       <c r="N9">
-        <v>130.1597218</v>
+        <v>129.3075392</v>
       </c>
       <c r="O9">
-        <v>32.46183461691999</v>
+        <v>32.24930027648</v>
       </c>
       <c r="P9">
-        <v>97.69788718307998</v>
+        <v>97.05823892351998</v>
       </c>
       <c r="Q9">
-        <v>196.19788718308</v>
+        <v>195.55823892352</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.08259156661267683</v>
+        <v>0.08289707130821097</v>
       </c>
       <c r="T9">
-        <v>0.84968976010801</v>
+        <v>0.8567452958016393</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>22.81955600997787</v>
+        <v>19.96711150873064</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2077,22 +2077,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.07928572000355411</v>
+        <v>0.07911842045731875</v>
       </c>
       <c r="C10">
-        <v>1472.756748732636</v>
+        <v>1463.407820589312</v>
       </c>
       <c r="D10">
-        <v>1512.192748732636</v>
+        <v>1519.785820589312</v>
       </c>
       <c r="E10">
-        <v>-698.9639999999999</v>
+        <v>-682.0219999999999</v>
       </c>
       <c r="F10">
-        <v>135.536</v>
+        <v>152.478</v>
       </c>
       <c r="G10">
         <v>96.09999999999999</v>
@@ -2113,28 +2113,28 @@
         <v>136.125</v>
       </c>
       <c r="M10">
-        <v>6.817460800000001</v>
+        <v>7.669643400000001</v>
       </c>
       <c r="N10">
-        <v>129.3075392</v>
+        <v>128.4553566</v>
       </c>
       <c r="O10">
-        <v>32.24930027648</v>
+        <v>32.03676593603999</v>
       </c>
       <c r="P10">
-        <v>97.05823892351998</v>
+        <v>96.41859066395998</v>
       </c>
       <c r="Q10">
-        <v>195.55823892352</v>
+        <v>194.91859066396</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.08289707130821097</v>
+        <v>0.08320929039265795</v>
       </c>
       <c r="T10">
-        <v>0.8567452958016393</v>
+        <v>0.8639558982138099</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>19.96711150873064</v>
+        <v>17.74854356331612</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.07911842045731875</v>
+        <v>0.0789511209110834</v>
       </c>
       <c r="C11">
-        <v>1463.407820589312</v>
+        <v>1454.135530426318</v>
       </c>
       <c r="D11">
-        <v>1519.785820589312</v>
+        <v>1527.455530426318</v>
       </c>
       <c r="E11">
-        <v>-682.0219999999999</v>
+        <v>-665.08</v>
       </c>
       <c r="F11">
-        <v>152.478</v>
+        <v>169.42</v>
       </c>
       <c r="G11">
         <v>96.09999999999999</v>
@@ -2195,28 +2195,28 @@
         <v>136.125</v>
       </c>
       <c r="M11">
-        <v>7.669643400000001</v>
+        <v>8.521826000000001</v>
       </c>
       <c r="N11">
-        <v>128.4553566</v>
+        <v>127.603174</v>
       </c>
       <c r="O11">
-        <v>32.03676593603999</v>
+        <v>31.82423159559999</v>
       </c>
       <c r="P11">
-        <v>96.41859066395998</v>
+        <v>95.77894240439997</v>
       </c>
       <c r="Q11">
-        <v>194.91859066396</v>
+        <v>194.2789424044</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.08320929039265795</v>
+        <v>0.08352844767898154</v>
       </c>
       <c r="T11">
-        <v>0.8639558982138099</v>
+        <v>0.8713267362351397</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>17.74854356331612</v>
+        <v>15.97368920698451</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2241,22 +2241,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.0789511209110834</v>
+        <v>0.07878382136484804</v>
       </c>
       <c r="C12">
-        <v>1454.135530426318</v>
+        <v>1444.941044406228</v>
       </c>
       <c r="D12">
-        <v>1527.455530426318</v>
+        <v>1535.203044406228</v>
       </c>
       <c r="E12">
-        <v>-665.0799999999999</v>
+        <v>-648.138</v>
       </c>
       <c r="F12">
-        <v>169.42</v>
+        <v>186.362</v>
       </c>
       <c r="G12">
         <v>96.09999999999999</v>
@@ -2277,28 +2277,28 @@
         <v>136.125</v>
       </c>
       <c r="M12">
-        <v>8.521826000000001</v>
+        <v>9.3740086</v>
       </c>
       <c r="N12">
-        <v>127.603174</v>
+        <v>126.7509914</v>
       </c>
       <c r="O12">
-        <v>31.82423159559999</v>
+        <v>31.61169725516</v>
       </c>
       <c r="P12">
-        <v>95.77894240439997</v>
+        <v>95.13929414483998</v>
       </c>
       <c r="Q12">
-        <v>194.2789424044</v>
+        <v>193.63929414484</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.08352844767898154</v>
+        <v>0.0838547770391551</v>
       </c>
       <c r="T12">
-        <v>0.8713267362351397</v>
+        <v>0.8788632110659378</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>15.97368920698451</v>
+        <v>14.52153564271319</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2323,22 +2323,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.07878382136484804</v>
+        <v>0.07861652181861267</v>
       </c>
       <c r="C13">
-        <v>1444.941044406228</v>
+        <v>1435.825552472133</v>
       </c>
       <c r="D13">
-        <v>1535.203044406228</v>
+        <v>1543.029552472133</v>
       </c>
       <c r="E13">
-        <v>-648.138</v>
+        <v>-631.196</v>
       </c>
       <c r="F13">
-        <v>186.362</v>
+        <v>203.304</v>
       </c>
       <c r="G13">
         <v>96.09999999999999</v>
@@ -2359,28 +2359,28 @@
         <v>136.125</v>
       </c>
       <c r="M13">
-        <v>9.3740086</v>
+        <v>10.2261912</v>
       </c>
       <c r="N13">
-        <v>126.7509914</v>
+        <v>125.8988088</v>
       </c>
       <c r="O13">
-        <v>31.61169725516</v>
+        <v>31.39916291471999</v>
       </c>
       <c r="P13">
-        <v>95.13929414483998</v>
+        <v>94.49964588527997</v>
       </c>
       <c r="Q13">
-        <v>193.63929414484</v>
+        <v>192.99964588528</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.0838547770391551</v>
+        <v>0.08418852297569623</v>
       </c>
       <c r="T13">
-        <v>0.8788632110659378</v>
+        <v>0.8865709694156175</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>14.52153564271319</v>
+        <v>13.31140767248709</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2405,22 +2405,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.07861652181861267</v>
+        <v>0.07859558927237732</v>
       </c>
       <c r="C14">
-        <v>1435.825552472133</v>
+        <v>1419.868426906965</v>
       </c>
       <c r="D14">
-        <v>1543.029552472133</v>
+        <v>1544.014426906966</v>
       </c>
       <c r="E14">
-        <v>-631.196</v>
+        <v>-614.254</v>
       </c>
       <c r="F14">
-        <v>203.304</v>
+        <v>220.246</v>
       </c>
       <c r="G14">
         <v>96.09999999999999</v>
@@ -2441,45 +2441,45 @@
         <v>136.125</v>
       </c>
       <c r="M14">
-        <v>10.2261912</v>
+        <v>11.4087428</v>
       </c>
       <c r="N14">
-        <v>125.8988088</v>
+        <v>124.7162572</v>
       </c>
       <c r="O14">
-        <v>31.39916291471999</v>
+        <v>31.10423454567999</v>
       </c>
       <c r="P14">
-        <v>94.49964588527997</v>
+        <v>93.61202265431999</v>
       </c>
       <c r="Q14">
-        <v>192.99964588528</v>
+        <v>192.11202265432</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.08418852297569623</v>
+        <v>0.08452994123261762</v>
       </c>
       <c r="T14">
-        <v>0.8865709694156175</v>
+        <v>0.8944559176124165</v>
       </c>
       <c r="U14">
-        <v>0.0503</v>
+        <v>0.05180000000000001</v>
       </c>
       <c r="V14">
         <v>0.2494</v>
       </c>
       <c r="W14">
-        <v>0.03775518</v>
+        <v>0.03888108</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y14">
-        <v>13.31140767248709</v>
+        <v>11.93163895324206</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2487,22 +2487,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.07859558927237732</v>
+        <v>0.07843954872614199</v>
       </c>
       <c r="C15">
-        <v>1419.868426906965</v>
+        <v>1410.307927692754</v>
       </c>
       <c r="D15">
-        <v>1544.014426906966</v>
+        <v>1551.395927692754</v>
       </c>
       <c r="E15">
-        <v>-614.254</v>
+        <v>-597.312</v>
       </c>
       <c r="F15">
-        <v>220.246</v>
+        <v>237.188</v>
       </c>
       <c r="G15">
         <v>96.09999999999999</v>
@@ -2523,28 +2523,28 @@
         <v>136.125</v>
       </c>
       <c r="M15">
-        <v>11.4087428</v>
+        <v>12.2863384</v>
       </c>
       <c r="N15">
-        <v>124.7162572</v>
+        <v>123.8386616</v>
       </c>
       <c r="O15">
-        <v>31.10423454567999</v>
+        <v>30.88536220303999</v>
       </c>
       <c r="P15">
-        <v>93.61202265431999</v>
+        <v>92.95329939695998</v>
       </c>
       <c r="Q15">
-        <v>192.11202265432</v>
+        <v>191.45329939696</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.08452994123261762</v>
+        <v>0.08487929944900231</v>
       </c>
       <c r="T15">
-        <v>0.8944559176124165</v>
+        <v>0.9025242366975131</v>
       </c>
       <c r="U15">
         <v>0.05180000000000001</v>
@@ -2561,7 +2561,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>11.93163895324206</v>
+        <v>11.07937902801049</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2569,22 +2569,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.07843954872614199</v>
+        <v>0.07828350817990663</v>
       </c>
       <c r="C16">
-        <v>1410.307927692754</v>
+        <v>1400.818345290131</v>
       </c>
       <c r="D16">
-        <v>1551.395927692754</v>
+        <v>1558.848345290131</v>
       </c>
       <c r="E16">
-        <v>-597.312</v>
+        <v>-580.3699999999999</v>
       </c>
       <c r="F16">
-        <v>237.188</v>
+        <v>254.1300000000001</v>
       </c>
       <c r="G16">
         <v>96.09999999999999</v>
@@ -2605,28 +2605,28 @@
         <v>136.125</v>
       </c>
       <c r="M16">
-        <v>12.2863384</v>
+        <v>13.163934</v>
       </c>
       <c r="N16">
-        <v>123.8386616</v>
+        <v>122.961066</v>
       </c>
       <c r="O16">
-        <v>30.88536220303999</v>
+        <v>30.66648986039999</v>
       </c>
       <c r="P16">
-        <v>92.95329939695998</v>
+        <v>92.29457613959997</v>
       </c>
       <c r="Q16">
-        <v>191.45329939696</v>
+        <v>190.7945761396</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.08487929944900231</v>
+        <v>0.08523687785871369</v>
       </c>
       <c r="T16">
-        <v>0.9025242366975131</v>
+        <v>0.9107823985846119</v>
       </c>
       <c r="U16">
         <v>0.05180000000000001</v>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>11.07937902801049</v>
+        <v>10.34075375947645</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2651,22 +2651,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.07828350817990663</v>
+        <v>0.07833163083367127</v>
       </c>
       <c r="C17">
-        <v>1400.818345290131</v>
+        <v>1381.570407429976</v>
       </c>
       <c r="D17">
-        <v>1558.848345290131</v>
+        <v>1556.542407429976</v>
       </c>
       <c r="E17">
-        <v>-580.37</v>
+        <v>-563.428</v>
       </c>
       <c r="F17">
-        <v>254.13</v>
+        <v>271.072</v>
       </c>
       <c r="G17">
         <v>96.09999999999999</v>
@@ -2687,45 +2687,45 @@
         <v>136.125</v>
       </c>
       <c r="M17">
-        <v>13.163934</v>
+        <v>14.502352</v>
       </c>
       <c r="N17">
-        <v>122.961066</v>
+        <v>121.622648</v>
       </c>
       <c r="O17">
-        <v>30.6664898604</v>
+        <v>30.33268841119999</v>
       </c>
       <c r="P17">
-        <v>92.29457613959998</v>
+        <v>91.28995958879997</v>
       </c>
       <c r="Q17">
-        <v>190.7945761396</v>
+        <v>189.7899595888</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.08523687785871369</v>
+        <v>0.08560297004008485</v>
       </c>
       <c r="T17">
-        <v>0.9107823985846119</v>
+        <v>0.9192371833737844</v>
       </c>
       <c r="U17">
-        <v>0.05180000000000001</v>
+        <v>0.05350000000000001</v>
       </c>
       <c r="V17">
         <v>0.2494</v>
       </c>
       <c r="W17">
-        <v>0.03888108</v>
+        <v>0.0401571</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y17">
-        <v>10.34075375947646</v>
+        <v>9.38640849429113</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2733,22 +2733,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.07833163083367127</v>
+        <v>0.07818835048743593</v>
       </c>
       <c r="C18">
-        <v>1381.570407429976</v>
+        <v>1371.514276321418</v>
       </c>
       <c r="D18">
-        <v>1556.542407429976</v>
+        <v>1563.428276321418</v>
       </c>
       <c r="E18">
-        <v>-563.428</v>
+        <v>-546.486</v>
       </c>
       <c r="F18">
-        <v>271.072</v>
+        <v>288.014</v>
       </c>
       <c r="G18">
         <v>96.09999999999999</v>
@@ -2769,28 +2769,28 @@
         <v>136.125</v>
       </c>
       <c r="M18">
-        <v>14.502352</v>
+        <v>15.408749</v>
       </c>
       <c r="N18">
-        <v>121.622648</v>
+        <v>120.716251</v>
       </c>
       <c r="O18">
-        <v>30.33268841119999</v>
+        <v>30.1066329994</v>
       </c>
       <c r="P18">
-        <v>91.28995958879997</v>
+        <v>90.60961800059998</v>
       </c>
       <c r="Q18">
-        <v>189.7899595888</v>
+        <v>189.1096180006</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.08560297004008485</v>
+        <v>0.08597788371980233</v>
       </c>
       <c r="T18">
-        <v>0.9192371833737844</v>
+        <v>0.9278956979169131</v>
       </c>
       <c r="U18">
         <v>0.05350000000000001</v>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>9.38640849429113</v>
+        <v>8.834266818156358</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2815,22 +2815,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.07818835048743593</v>
+        <v>0.07804507014120057</v>
       </c>
       <c r="C19">
-        <v>1371.514276321418</v>
+        <v>1361.519339663645</v>
       </c>
       <c r="D19">
-        <v>1563.428276321418</v>
+        <v>1570.375339663645</v>
       </c>
       <c r="E19">
-        <v>-546.486</v>
+        <v>-529.544</v>
       </c>
       <c r="F19">
-        <v>288.014</v>
+        <v>304.956</v>
       </c>
       <c r="G19">
         <v>96.09999999999999</v>
@@ -2851,28 +2851,28 @@
         <v>136.125</v>
       </c>
       <c r="M19">
-        <v>15.408749</v>
+        <v>16.315146</v>
       </c>
       <c r="N19">
-        <v>120.716251</v>
+        <v>119.809854</v>
       </c>
       <c r="O19">
-        <v>30.1066329994</v>
+        <v>29.88057758759999</v>
       </c>
       <c r="P19">
-        <v>90.60961800059998</v>
+        <v>89.92927641239999</v>
       </c>
       <c r="Q19">
-        <v>189.1096180006</v>
+        <v>188.4292764124</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.08597788371980233</v>
+        <v>0.08636194163561045</v>
       </c>
       <c r="T19">
-        <v>0.9278956979169131</v>
+        <v>0.9367653957415812</v>
       </c>
       <c r="U19">
         <v>0.05350000000000001</v>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>8.834266818156358</v>
+        <v>8.343474217147671</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2897,22 +2897,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.07804507014120057</v>
+        <v>0.07790178979496522</v>
       </c>
       <c r="C20">
-        <v>1361.519339663645</v>
+        <v>1351.58641684668</v>
       </c>
       <c r="D20">
-        <v>1570.375339663645</v>
+        <v>1577.38441684668</v>
       </c>
       <c r="E20">
-        <v>-529.544</v>
+        <v>-512.602</v>
       </c>
       <c r="F20">
-        <v>304.956</v>
+        <v>321.898</v>
       </c>
       <c r="G20">
         <v>96.09999999999999</v>
@@ -2933,28 +2933,28 @@
         <v>136.125</v>
       </c>
       <c r="M20">
-        <v>16.315146</v>
+        <v>17.221543</v>
       </c>
       <c r="N20">
-        <v>119.809854</v>
+        <v>118.903457</v>
       </c>
       <c r="O20">
-        <v>29.88057758759999</v>
+        <v>29.65452217579999</v>
       </c>
       <c r="P20">
-        <v>89.92927641239999</v>
+        <v>89.24893482419998</v>
       </c>
       <c r="Q20">
-        <v>188.4292764124</v>
+        <v>187.7489348242</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.08636194163561045</v>
+        <v>0.08675548246292003</v>
       </c>
       <c r="T20">
-        <v>0.9367653957415812</v>
+        <v>0.9458540984508091</v>
       </c>
       <c r="U20">
         <v>0.05350000000000001</v>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>8.343474217147671</v>
+        <v>7.90434399519253</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2979,22 +2979,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.07790178979496522</v>
+        <v>0.07787860544872988</v>
       </c>
       <c r="C21">
-        <v>1351.58641684668</v>
+        <v>1335.784448526824</v>
       </c>
       <c r="D21">
-        <v>1577.38441684668</v>
+        <v>1578.524448526824</v>
       </c>
       <c r="E21">
-        <v>-512.602</v>
+        <v>-495.66</v>
       </c>
       <c r="F21">
-        <v>321.898</v>
+        <v>338.84</v>
       </c>
       <c r="G21">
         <v>96.09999999999999</v>
@@ -3015,45 +3015,45 @@
         <v>136.125</v>
       </c>
       <c r="M21">
-        <v>17.221543</v>
+        <v>18.39901200000001</v>
       </c>
       <c r="N21">
-        <v>118.903457</v>
+        <v>117.725988</v>
       </c>
       <c r="O21">
-        <v>29.65452217579999</v>
+        <v>29.36086140719999</v>
       </c>
       <c r="P21">
-        <v>89.24893482419998</v>
+        <v>88.36512659279998</v>
       </c>
       <c r="Q21">
-        <v>187.7489348242</v>
+        <v>186.8651265928</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.08675548246292003</v>
+        <v>0.08715886181091234</v>
       </c>
       <c r="T21">
-        <v>0.9458540984508091</v>
+        <v>0.955170018727768</v>
       </c>
       <c r="U21">
-        <v>0.05350000000000001</v>
+        <v>0.05430000000000001</v>
       </c>
       <c r="V21">
         <v>0.2494</v>
       </c>
       <c r="W21">
-        <v>0.0401571</v>
+        <v>0.04075758</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y21">
-        <v>7.90434399519253</v>
+        <v>7.398495093106082</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3061,22 +3061,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.07787860544872988</v>
+        <v>0.07774132990249452</v>
       </c>
       <c r="C22">
-        <v>1335.784448526824</v>
+        <v>1325.626536934504</v>
       </c>
       <c r="D22">
-        <v>1578.524448526824</v>
+        <v>1585.308536934504</v>
       </c>
       <c r="E22">
-        <v>-495.66</v>
+        <v>-478.718</v>
       </c>
       <c r="F22">
-        <v>338.84</v>
+        <v>355.782</v>
       </c>
       <c r="G22">
         <v>96.09999999999999</v>
@@ -3097,28 +3097,28 @@
         <v>136.125</v>
       </c>
       <c r="M22">
-        <v>18.39901200000001</v>
+        <v>19.31896260000001</v>
       </c>
       <c r="N22">
-        <v>117.725988</v>
+        <v>116.8060374</v>
       </c>
       <c r="O22">
-        <v>29.36086140719999</v>
+        <v>29.13142572755999</v>
       </c>
       <c r="P22">
-        <v>88.36512659279998</v>
+        <v>87.67461167243997</v>
       </c>
       <c r="Q22">
-        <v>186.8651265928</v>
+        <v>186.17461167244</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.08715886181091234</v>
+        <v>0.08757245329429686</v>
       </c>
       <c r="T22">
-        <v>0.955170018727768</v>
+        <v>0.9647217850876876</v>
       </c>
       <c r="U22">
         <v>0.05430000000000001</v>
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>7.398495093106082</v>
+        <v>7.046185802958174</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3143,22 +3143,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.07774132990249452</v>
+        <v>0.07760405435625918</v>
       </c>
       <c r="C23">
-        <v>1325.626536934504</v>
+        <v>1315.527189538523</v>
       </c>
       <c r="D23">
-        <v>1585.308536934504</v>
+        <v>1592.151189538523</v>
       </c>
       <c r="E23">
-        <v>-478.718</v>
+        <v>-461.776</v>
       </c>
       <c r="F23">
-        <v>355.782</v>
+        <v>372.724</v>
       </c>
       <c r="G23">
         <v>96.09999999999999</v>
@@ -3179,28 +3179,28 @@
         <v>136.125</v>
       </c>
       <c r="M23">
-        <v>19.3189626</v>
+        <v>20.2389132</v>
       </c>
       <c r="N23">
-        <v>116.8060374</v>
+        <v>115.8860868</v>
       </c>
       <c r="O23">
-        <v>29.13142572755999</v>
+        <v>28.90199004791999</v>
       </c>
       <c r="P23">
-        <v>87.67461167243997</v>
+        <v>86.98409675207998</v>
       </c>
       <c r="Q23">
-        <v>186.17461167244</v>
+        <v>185.48409675208</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.08757245329429686</v>
+        <v>0.08799664968751175</v>
       </c>
       <c r="T23">
-        <v>0.9647217850876876</v>
+        <v>0.9745184685337591</v>
       </c>
       <c r="U23">
         <v>0.05430000000000001</v>
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>7.046185802958175</v>
+        <v>6.72590463009644</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.07760405435625918</v>
+        <v>0.07746677881002381</v>
       </c>
       <c r="C24">
-        <v>1315.527189538523</v>
+        <v>1305.487167966591</v>
       </c>
       <c r="D24">
-        <v>1592.151189538523</v>
+        <v>1599.053167966591</v>
       </c>
       <c r="E24">
-        <v>-461.776</v>
+        <v>-444.8339999999999</v>
       </c>
       <c r="F24">
-        <v>372.724</v>
+        <v>389.6660000000001</v>
       </c>
       <c r="G24">
         <v>96.09999999999999</v>
@@ -3261,28 +3261,28 @@
         <v>136.125</v>
       </c>
       <c r="M24">
-        <v>20.2389132</v>
+        <v>21.15886380000001</v>
       </c>
       <c r="N24">
-        <v>115.8860868</v>
+        <v>114.9661362</v>
       </c>
       <c r="O24">
-        <v>28.90199004791999</v>
+        <v>28.67255436827999</v>
       </c>
       <c r="P24">
-        <v>86.98409675207998</v>
+        <v>86.29358183171998</v>
       </c>
       <c r="Q24">
-        <v>185.48409675208</v>
+        <v>184.79358183172</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.08799664968751175</v>
+        <v>0.0884318641688621</v>
       </c>
       <c r="T24">
-        <v>0.9745184685337591</v>
+        <v>0.9845696112901181</v>
       </c>
       <c r="U24">
         <v>0.05430000000000001</v>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>6.72590463009644</v>
+        <v>6.433473994005289</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3307,22 +3307,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.07746677881002381</v>
+        <v>0.07732950326378847</v>
       </c>
       <c r="C25">
-        <v>1305.487167966591</v>
+        <v>1295.507247110542</v>
       </c>
       <c r="D25">
-        <v>1599.053167966591</v>
+        <v>1606.015247110543</v>
       </c>
       <c r="E25">
-        <v>-444.8339999999999</v>
+        <v>-427.8919999999999</v>
       </c>
       <c r="F25">
-        <v>389.6660000000001</v>
+        <v>406.6080000000001</v>
       </c>
       <c r="G25">
         <v>96.09999999999999</v>
@@ -3343,28 +3343,28 @@
         <v>136.125</v>
       </c>
       <c r="M25">
-        <v>21.15886380000001</v>
+        <v>22.07881440000001</v>
       </c>
       <c r="N25">
-        <v>114.9661362</v>
+        <v>114.0461856</v>
       </c>
       <c r="O25">
-        <v>28.67255436827999</v>
+        <v>28.44311868863999</v>
       </c>
       <c r="P25">
-        <v>86.29358183171998</v>
+        <v>85.60306691135997</v>
       </c>
       <c r="Q25">
-        <v>184.79358183172</v>
+        <v>184.10306691136</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.0884318641688621</v>
+        <v>0.08887853166287957</v>
       </c>
       <c r="T25">
-        <v>0.9845696112901181</v>
+        <v>0.9948852578032233</v>
       </c>
       <c r="U25">
         <v>0.05430000000000001</v>
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>6.433473994005289</v>
+        <v>6.165412577588403</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3389,22 +3389,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.07732950326378847</v>
+        <v>0.07737987771755311</v>
       </c>
       <c r="C26">
-        <v>1295.507247110542</v>
+        <v>1276.003421458953</v>
       </c>
       <c r="D26">
-        <v>1606.015247110543</v>
+        <v>1603.453421458953</v>
       </c>
       <c r="E26">
-        <v>-427.892</v>
+        <v>-410.95</v>
       </c>
       <c r="F26">
-        <v>406.608</v>
+        <v>423.55</v>
       </c>
       <c r="G26">
         <v>96.09999999999999</v>
@@ -3425,45 +3425,45 @@
         <v>136.125</v>
       </c>
       <c r="M26">
-        <v>22.0788144</v>
+        <v>23.422315</v>
       </c>
       <c r="N26">
-        <v>114.0461856</v>
+        <v>112.702685</v>
       </c>
       <c r="O26">
-        <v>28.44311868863999</v>
+        <v>28.10804963899999</v>
       </c>
       <c r="P26">
-        <v>85.60306691135997</v>
+        <v>84.59463536099997</v>
       </c>
       <c r="Q26">
-        <v>184.10306691136</v>
+        <v>183.094635361</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.08887853166287957</v>
+        <v>0.08933711029007083</v>
       </c>
       <c r="T26">
-        <v>0.9948852578032233</v>
+        <v>1.005475988223345</v>
       </c>
       <c r="U26">
-        <v>0.05430000000000001</v>
+        <v>0.05530000000000001</v>
       </c>
       <c r="V26">
         <v>0.2494</v>
       </c>
       <c r="W26">
-        <v>0.04075758</v>
+        <v>0.04150818000000001</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y26">
-        <v>6.165412577588404</v>
+        <v>5.811765404060186</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3471,22 +3471,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.07737987771755311</v>
+        <v>0.07725010817131775</v>
       </c>
       <c r="C27">
-        <v>1276.003421458953</v>
+        <v>1265.677596569665</v>
       </c>
       <c r="D27">
-        <v>1603.453421458953</v>
+        <v>1610.069596569665</v>
       </c>
       <c r="E27">
-        <v>-410.95</v>
+        <v>-394.008</v>
       </c>
       <c r="F27">
-        <v>423.55</v>
+        <v>440.492</v>
       </c>
       <c r="G27">
         <v>96.09999999999999</v>
@@ -3507,28 +3507,28 @@
         <v>136.125</v>
       </c>
       <c r="M27">
-        <v>23.422315</v>
+        <v>24.3592076</v>
       </c>
       <c r="N27">
-        <v>112.702685</v>
+        <v>111.7657924</v>
       </c>
       <c r="O27">
-        <v>28.10804963899999</v>
+        <v>27.87438862455999</v>
       </c>
       <c r="P27">
-        <v>84.59463536099997</v>
+        <v>83.89140377543997</v>
       </c>
       <c r="Q27">
-        <v>183.094635361</v>
+        <v>182.39140377544</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.08933711029007083</v>
+        <v>0.08980808293421319</v>
       </c>
       <c r="T27">
-        <v>1.005475988223345</v>
+        <v>1.016352954600767</v>
       </c>
       <c r="U27">
         <v>0.05530000000000001</v>
@@ -3545,7 +3545,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>5.811765404060186</v>
+        <v>5.588235965442486</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3553,22 +3553,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.07725010817131775</v>
+        <v>0.07712033862508241</v>
       </c>
       <c r="C28">
-        <v>1265.677596569665</v>
+        <v>1255.406597271645</v>
       </c>
       <c r="D28">
-        <v>1610.069596569665</v>
+        <v>1616.740597271645</v>
       </c>
       <c r="E28">
-        <v>-394.008</v>
+        <v>-377.066</v>
       </c>
       <c r="F28">
-        <v>440.492</v>
+        <v>457.434</v>
       </c>
       <c r="G28">
         <v>96.09999999999999</v>
@@ -3589,28 +3589,28 @@
         <v>136.125</v>
       </c>
       <c r="M28">
-        <v>24.3592076</v>
+        <v>25.29610020000001</v>
       </c>
       <c r="N28">
-        <v>111.7657924</v>
+        <v>110.8288998</v>
       </c>
       <c r="O28">
-        <v>27.87438862455999</v>
+        <v>27.64072761011999</v>
       </c>
       <c r="P28">
-        <v>83.89140377543997</v>
+        <v>83.18817218987996</v>
       </c>
       <c r="Q28">
-        <v>182.39140377544</v>
+        <v>181.68817218988</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.08980808293421319</v>
+        <v>0.09029195893846906</v>
       </c>
       <c r="T28">
-        <v>1.016352954600767</v>
+        <v>1.027527920057022</v>
       </c>
       <c r="U28">
         <v>0.05530000000000001</v>
@@ -3627,7 +3627,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>5.588235965442486</v>
+        <v>5.38126426301869</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3635,22 +3635,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.07712033862508241</v>
+        <v>0.07699056907884706</v>
       </c>
       <c r="C29">
-        <v>1255.406597271645</v>
+        <v>1245.191107876752</v>
       </c>
       <c r="D29">
-        <v>1616.740597271645</v>
+        <v>1623.467107876752</v>
       </c>
       <c r="E29">
-        <v>-377.066</v>
+        <v>-360.124</v>
       </c>
       <c r="F29">
-        <v>457.434</v>
+        <v>474.376</v>
       </c>
       <c r="G29">
         <v>96.09999999999999</v>
@@ -3671,28 +3671,28 @@
         <v>136.125</v>
       </c>
       <c r="M29">
-        <v>25.29610020000001</v>
+        <v>26.23299280000001</v>
       </c>
       <c r="N29">
-        <v>110.8288998</v>
+        <v>109.8920072</v>
       </c>
       <c r="O29">
-        <v>27.64072761011999</v>
+        <v>27.40706659567999</v>
       </c>
       <c r="P29">
-        <v>83.18817218987996</v>
+        <v>82.48494060431997</v>
       </c>
       <c r="Q29">
-        <v>181.68817218988</v>
+        <v>180.98494060432</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.09029195893846906</v>
+        <v>0.09078927594284314</v>
       </c>
       <c r="T29">
-        <v>1.027527920057022</v>
+        <v>1.039013301220396</v>
       </c>
       <c r="U29">
         <v>0.05530000000000001</v>
@@ -3709,7 +3709,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>5.38126426301869</v>
+        <v>5.189076253625165</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3717,22 +3717,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.07699056907884706</v>
+        <v>0.07686079953261171</v>
       </c>
       <c r="C30">
-        <v>1245.191107876752</v>
+        <v>1235.031824132848</v>
       </c>
       <c r="D30">
-        <v>1623.467107876752</v>
+        <v>1630.249824132848</v>
       </c>
       <c r="E30">
-        <v>-360.124</v>
+        <v>-343.1819999999999</v>
       </c>
       <c r="F30">
-        <v>474.376</v>
+        <v>491.3180000000001</v>
       </c>
       <c r="G30">
         <v>96.09999999999999</v>
@@ -3753,28 +3753,28 @@
         <v>136.125</v>
       </c>
       <c r="M30">
-        <v>26.23299280000001</v>
+        <v>27.16988540000001</v>
       </c>
       <c r="N30">
-        <v>109.8920072</v>
+        <v>108.9551146</v>
       </c>
       <c r="O30">
-        <v>27.40706659567999</v>
+        <v>27.17340558123999</v>
       </c>
       <c r="P30">
-        <v>82.48494060431997</v>
+        <v>81.78170901875997</v>
       </c>
       <c r="Q30">
-        <v>180.98494060432</v>
+        <v>180.28170901876</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.09078927594284314</v>
+        <v>0.09130060187691791</v>
       </c>
       <c r="T30">
-        <v>1.039013301220396</v>
+        <v>1.050822214247527</v>
       </c>
       <c r="U30">
         <v>0.05530000000000001</v>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>5.189076253625165</v>
+        <v>5.010142589707056</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3799,22 +3799,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.07686079953261171</v>
+        <v>0.07673102998637636</v>
       </c>
       <c r="C31">
-        <v>1235.031824132848</v>
+        <v>1224.929453463691</v>
       </c>
       <c r="D31">
-        <v>1630.249824132848</v>
+        <v>1637.089453463691</v>
       </c>
       <c r="E31">
-        <v>-343.182</v>
+        <v>-326.24</v>
       </c>
       <c r="F31">
-        <v>491.318</v>
+        <v>508.26</v>
       </c>
       <c r="G31">
         <v>96.09999999999999</v>
@@ -3835,28 +3835,28 @@
         <v>136.125</v>
       </c>
       <c r="M31">
-        <v>27.1698854</v>
+        <v>28.10677800000001</v>
       </c>
       <c r="N31">
-        <v>108.9551146</v>
+        <v>108.018222</v>
       </c>
       <c r="O31">
-        <v>27.17340558123999</v>
+        <v>26.93974456679999</v>
       </c>
       <c r="P31">
-        <v>81.78170901875998</v>
+        <v>81.07847743319998</v>
       </c>
       <c r="Q31">
-        <v>180.28170901876</v>
+        <v>179.5784774332</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.09130060187691791</v>
+        <v>0.09182653712339481</v>
       </c>
       <c r="T31">
-        <v>1.050822214247527</v>
+        <v>1.062968524789718</v>
       </c>
       <c r="U31">
         <v>0.05530000000000001</v>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>5.010142589707058</v>
+        <v>4.843137836716821</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3881,22 +3881,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.07673102998637636</v>
+        <v>0.076601260440141</v>
       </c>
       <c r="C32">
-        <v>1224.929453463691</v>
+        <v>1214.884715214895</v>
       </c>
       <c r="D32">
-        <v>1637.089453463691</v>
+        <v>1643.986715214895</v>
       </c>
       <c r="E32">
-        <v>-326.24</v>
+        <v>-309.298</v>
       </c>
       <c r="F32">
-        <v>508.26</v>
+        <v>525.202</v>
       </c>
       <c r="G32">
         <v>96.09999999999999</v>
@@ -3917,28 +3917,28 @@
         <v>136.125</v>
       </c>
       <c r="M32">
-        <v>28.10677800000001</v>
+        <v>29.04367060000001</v>
       </c>
       <c r="N32">
-        <v>108.018222</v>
+        <v>107.0813294</v>
       </c>
       <c r="O32">
-        <v>26.93974456679999</v>
+        <v>26.70608355235999</v>
       </c>
       <c r="P32">
-        <v>81.07847743319998</v>
+        <v>80.37524584763997</v>
       </c>
       <c r="Q32">
-        <v>179.5784774332</v>
+        <v>178.87524584764</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.09182653712339481</v>
+        <v>0.09236771686976958</v>
       </c>
       <c r="T32">
-        <v>1.062968524789718</v>
+        <v>1.075466902304147</v>
       </c>
       <c r="U32">
         <v>0.05530000000000001</v>
@@ -3955,7 +3955,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>4.843137836716821</v>
+        <v>4.686907583919504</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3963,22 +3963,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.076601260440141</v>
+        <v>0.07647149089390566</v>
       </c>
       <c r="C33">
-        <v>1214.884715214895</v>
+        <v>1204.898340906138</v>
       </c>
       <c r="D33">
-        <v>1643.986715214895</v>
+        <v>1650.942340906138</v>
       </c>
       <c r="E33">
-        <v>-309.298</v>
+        <v>-292.356</v>
       </c>
       <c r="F33">
-        <v>525.202</v>
+        <v>542.144</v>
       </c>
       <c r="G33">
         <v>96.09999999999999</v>
@@ -3999,28 +3999,28 @@
         <v>136.125</v>
       </c>
       <c r="M33">
-        <v>29.04367060000001</v>
+        <v>29.98056320000001</v>
       </c>
       <c r="N33">
-        <v>107.0813294</v>
+        <v>106.1444368</v>
       </c>
       <c r="O33">
-        <v>26.70608355235999</v>
+        <v>26.47242253791999</v>
       </c>
       <c r="P33">
-        <v>80.37524584763997</v>
+        <v>79.67201426207997</v>
       </c>
       <c r="Q33">
-        <v>178.87524584764</v>
+        <v>178.17201426208</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.09236771686976958</v>
+        <v>0.09292481366750832</v>
       </c>
       <c r="T33">
-        <v>1.075466902304147</v>
+        <v>1.088332879157236</v>
       </c>
       <c r="U33">
         <v>0.05530000000000001</v>
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>4.686907583919504</v>
+        <v>4.54044172192202</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4045,22 +4045,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.07647149089390566</v>
+        <v>0.0769609663476703</v>
       </c>
       <c r="C34">
-        <v>1204.898340906138</v>
+        <v>1162.023391894282</v>
       </c>
       <c r="D34">
-        <v>1650.942340906138</v>
+        <v>1625.009391894282</v>
       </c>
       <c r="E34">
-        <v>-292.356</v>
+        <v>-275.414</v>
       </c>
       <c r="F34">
-        <v>542.144</v>
+        <v>559.086</v>
       </c>
       <c r="G34">
         <v>96.09999999999999</v>
@@ -4081,45 +4081,45 @@
         <v>136.125</v>
       </c>
       <c r="M34">
-        <v>29.98056320000001</v>
+        <v>32.3151708</v>
       </c>
       <c r="N34">
-        <v>106.1444368</v>
+        <v>103.8098292</v>
       </c>
       <c r="O34">
-        <v>26.47242253791999</v>
+        <v>25.89017140247999</v>
       </c>
       <c r="P34">
-        <v>79.67201426207997</v>
+        <v>77.91965779751997</v>
       </c>
       <c r="Q34">
-        <v>178.17201426208</v>
+        <v>176.41965779752</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.09292481366750832</v>
+        <v>0.09349854022040344</v>
       </c>
       <c r="T34">
-        <v>1.088332879157236</v>
+        <v>1.101582915020865</v>
       </c>
       <c r="U34">
-        <v>0.05530000000000001</v>
+        <v>0.0578</v>
       </c>
       <c r="V34">
         <v>0.2494</v>
       </c>
       <c r="W34">
-        <v>0.04150818000000001</v>
+        <v>0.04338468</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y34">
-        <v>4.54044172192202</v>
+        <v>4.212417778710919</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4127,22 +4127,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.0769609663476703</v>
+        <v>0.07684996180143494</v>
       </c>
       <c r="C35">
-        <v>1162.023391894282</v>
+        <v>1150.890849288432</v>
       </c>
       <c r="D35">
-        <v>1625.009391894282</v>
+        <v>1630.818849288432</v>
       </c>
       <c r="E35">
-        <v>-275.414</v>
+        <v>-258.472</v>
       </c>
       <c r="F35">
-        <v>559.086</v>
+        <v>576.028</v>
       </c>
       <c r="G35">
         <v>96.09999999999999</v>
@@ -4163,28 +4163,28 @@
         <v>136.125</v>
       </c>
       <c r="M35">
-        <v>32.3151708</v>
+        <v>33.2944184</v>
       </c>
       <c r="N35">
-        <v>103.8098292</v>
+        <v>102.8305816</v>
       </c>
       <c r="O35">
-        <v>25.89017140247999</v>
+        <v>25.64594705103999</v>
       </c>
       <c r="P35">
-        <v>77.91965779751997</v>
+        <v>77.18463454895996</v>
       </c>
       <c r="Q35">
-        <v>176.41965779752</v>
+        <v>175.68463454896</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.09349854022040344</v>
+        <v>0.09408965242641659</v>
       </c>
       <c r="T35">
-        <v>1.101582915020865</v>
+        <v>1.115234467122785</v>
       </c>
       <c r="U35">
         <v>0.0578</v>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>4.212417778710919</v>
+        <v>4.088523138160598</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4209,22 +4209,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.07684996180143494</v>
+        <v>0.07765844225519959</v>
       </c>
       <c r="C36">
-        <v>1150.890849288432</v>
+        <v>1092.563110691452</v>
       </c>
       <c r="D36">
-        <v>1630.818849288432</v>
+        <v>1589.433110691453</v>
       </c>
       <c r="E36">
-        <v>-258.472</v>
+        <v>-241.53</v>
       </c>
       <c r="F36">
-        <v>576.028</v>
+        <v>592.97</v>
       </c>
       <c r="G36">
         <v>96.09999999999999</v>
@@ -4245,45 +4245,45 @@
         <v>136.125</v>
       </c>
       <c r="M36">
-        <v>33.2944184</v>
+        <v>36.34906100000001</v>
       </c>
       <c r="N36">
-        <v>102.8305816</v>
+        <v>99.77593899999997</v>
       </c>
       <c r="O36">
-        <v>25.64594705103999</v>
+        <v>24.88411918659999</v>
       </c>
       <c r="P36">
-        <v>77.18463454895996</v>
+        <v>74.89181981339998</v>
       </c>
       <c r="Q36">
-        <v>175.68463454896</v>
+        <v>173.3918198134</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.09408965242641659</v>
+        <v>0.09469895270030708</v>
       </c>
       <c r="T36">
-        <v>1.115234467122785</v>
+        <v>1.129306066981688</v>
       </c>
       <c r="U36">
-        <v>0.0578</v>
+        <v>0.06130000000000001</v>
       </c>
       <c r="V36">
         <v>0.2494</v>
       </c>
       <c r="W36">
-        <v>0.04338468</v>
+        <v>0.04601178</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y36">
-        <v>4.088523138160598</v>
+        <v>3.744938555634214</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.07765844225519959</v>
+        <v>0.07757370870896424</v>
       </c>
       <c r="C37">
-        <v>1092.563110691452</v>
+        <v>1079.859781889907</v>
       </c>
       <c r="D37">
-        <v>1589.433110691453</v>
+        <v>1593.671781889907</v>
       </c>
       <c r="E37">
-        <v>-241.53</v>
+        <v>-224.588</v>
       </c>
       <c r="F37">
-        <v>592.97</v>
+        <v>609.912</v>
       </c>
       <c r="G37">
         <v>96.09999999999999</v>
@@ -4327,28 +4327,28 @@
         <v>136.125</v>
       </c>
       <c r="M37">
-        <v>36.34906100000001</v>
+        <v>37.38760560000001</v>
       </c>
       <c r="N37">
-        <v>99.77593899999997</v>
+        <v>98.73739439999997</v>
       </c>
       <c r="O37">
-        <v>24.88411918659999</v>
+        <v>24.62510616335999</v>
       </c>
       <c r="P37">
-        <v>74.89181981339998</v>
+        <v>74.11228823663998</v>
       </c>
       <c r="Q37">
-        <v>173.3918198134</v>
+        <v>172.61228823664</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.09469895270030708</v>
+        <v>0.09532729360775663</v>
       </c>
       <c r="T37">
-        <v>1.129306066981688</v>
+        <v>1.143817404336181</v>
       </c>
       <c r="U37">
         <v>0.06130000000000001</v>
@@ -4365,7 +4365,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>3.744938555634214</v>
+        <v>3.640912484644375</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4373,22 +4373,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.07757370870896424</v>
+        <v>0.0774889751627289</v>
       </c>
       <c r="C38">
-        <v>1079.859781889907</v>
+        <v>1067.179120760012</v>
       </c>
       <c r="D38">
-        <v>1593.671781889907</v>
+        <v>1597.933120760012</v>
       </c>
       <c r="E38">
-        <v>-224.588</v>
+        <v>-207.646</v>
       </c>
       <c r="F38">
-        <v>609.912</v>
+        <v>626.854</v>
       </c>
       <c r="G38">
         <v>96.09999999999999</v>
@@ -4409,28 +4409,28 @@
         <v>136.125</v>
       </c>
       <c r="M38">
-        <v>37.38760560000001</v>
+        <v>38.42615020000001</v>
       </c>
       <c r="N38">
-        <v>98.73739439999997</v>
+        <v>97.69884979999996</v>
       </c>
       <c r="O38">
-        <v>24.62510616335999</v>
+        <v>24.36609314011999</v>
       </c>
       <c r="P38">
-        <v>74.11228823663998</v>
+        <v>73.33275665987998</v>
       </c>
       <c r="Q38">
-        <v>172.61228823664</v>
+        <v>171.83275665988</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.09532729360775663</v>
+        <v>0.09597558184560143</v>
       </c>
       <c r="T38">
-        <v>1.143817404336181</v>
+        <v>1.158789419067008</v>
       </c>
       <c r="U38">
         <v>0.06130000000000001</v>
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>3.640912484644375</v>
+        <v>3.542509444518851</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4455,22 +4455,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.0774889751627289</v>
+        <v>0.07820288001649355</v>
       </c>
       <c r="C39">
-        <v>1067.179120760012</v>
+        <v>1015.031231335332</v>
       </c>
       <c r="D39">
-        <v>1597.933120760012</v>
+        <v>1562.727231335332</v>
       </c>
       <c r="E39">
-        <v>-207.646</v>
+        <v>-190.704</v>
       </c>
       <c r="F39">
-        <v>626.854</v>
+        <v>643.796</v>
       </c>
       <c r="G39">
         <v>96.09999999999999</v>
@@ -4491,45 +4491,45 @@
         <v>136.125</v>
       </c>
       <c r="M39">
-        <v>38.42615020000001</v>
+        <v>41.2673236</v>
       </c>
       <c r="N39">
-        <v>97.69884979999996</v>
+        <v>94.85767639999997</v>
       </c>
       <c r="O39">
-        <v>24.36609314011999</v>
+        <v>23.65750449415999</v>
       </c>
       <c r="P39">
-        <v>73.33275665987998</v>
+        <v>71.20017190583998</v>
       </c>
       <c r="Q39">
-        <v>171.83275665988</v>
+        <v>169.70017190584</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.09597558184560143</v>
+        <v>0.09664478260724765</v>
       </c>
       <c r="T39">
-        <v>1.158789419067008</v>
+        <v>1.174244402014957</v>
       </c>
       <c r="U39">
-        <v>0.06130000000000001</v>
+        <v>0.0641</v>
       </c>
       <c r="V39">
         <v>0.2494</v>
       </c>
       <c r="W39">
-        <v>0.04601178</v>
+        <v>0.04811346</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y39">
-        <v>3.542509444518851</v>
+        <v>3.298614693781595</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4537,22 +4537,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.07820288001649355</v>
+        <v>0.07813916327025819</v>
       </c>
       <c r="C40">
-        <v>1015.031231335332</v>
+        <v>1001.168219298067</v>
       </c>
       <c r="D40">
-        <v>1562.727231335332</v>
+        <v>1565.806219298068</v>
       </c>
       <c r="E40">
-        <v>-190.704</v>
+        <v>-173.7619999999999</v>
       </c>
       <c r="F40">
-        <v>643.796</v>
+        <v>660.7380000000001</v>
       </c>
       <c r="G40">
         <v>96.09999999999999</v>
@@ -4573,28 +4573,28 @@
         <v>136.125</v>
       </c>
       <c r="M40">
-        <v>41.2673236</v>
+        <v>42.35330580000001</v>
       </c>
       <c r="N40">
-        <v>94.85767639999997</v>
+        <v>93.77169419999996</v>
       </c>
       <c r="O40">
-        <v>23.65750449415999</v>
+        <v>23.38666053347999</v>
       </c>
       <c r="P40">
-        <v>71.20017190583998</v>
+        <v>70.38503366651997</v>
       </c>
       <c r="Q40">
-        <v>169.70017190584</v>
+        <v>168.88503366652</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.09664478260724765</v>
+        <v>0.09733592437747245</v>
       </c>
       <c r="T40">
-        <v>1.174244402014957</v>
+        <v>1.190206105715299</v>
       </c>
       <c r="U40">
         <v>0.0641</v>
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>3.298614693781595</v>
+        <v>3.214034829838476</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4619,22 +4619,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.07813916327025819</v>
+        <v>0.07807544652402285</v>
       </c>
       <c r="C41">
-        <v>1001.168219298067</v>
+        <v>987.3173640620748</v>
       </c>
       <c r="D41">
-        <v>1565.806219298068</v>
+        <v>1568.897364062075</v>
       </c>
       <c r="E41">
-        <v>-173.7619999999999</v>
+        <v>-156.8199999999999</v>
       </c>
       <c r="F41">
-        <v>660.7380000000001</v>
+        <v>677.6800000000001</v>
       </c>
       <c r="G41">
         <v>96.09999999999999</v>
@@ -4655,28 +4655,28 @@
         <v>136.125</v>
       </c>
       <c r="M41">
-        <v>42.35330580000001</v>
+        <v>43.439288</v>
       </c>
       <c r="N41">
-        <v>93.77169419999996</v>
+        <v>92.68571199999997</v>
       </c>
       <c r="O41">
-        <v>23.38666053347999</v>
+        <v>23.11581657279999</v>
       </c>
       <c r="P41">
-        <v>70.38503366651997</v>
+        <v>69.56989542719998</v>
       </c>
       <c r="Q41">
-        <v>168.88503366652</v>
+        <v>168.0698954272</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.09733592437747245</v>
+        <v>0.09805010420670474</v>
       </c>
       <c r="T41">
-        <v>1.190206105715299</v>
+        <v>1.206699866205652</v>
       </c>
       <c r="U41">
         <v>0.0641</v>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>3.214034829838476</v>
+        <v>3.133683959092514</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4701,22 +4701,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.07807544652402285</v>
+        <v>0.07801172977778748</v>
       </c>
       <c r="C42">
-        <v>987.3173640620748</v>
+        <v>973.4787377680163</v>
       </c>
       <c r="D42">
-        <v>1568.897364062075</v>
+        <v>1572.000737768017</v>
       </c>
       <c r="E42">
-        <v>-156.8199999999999</v>
+        <v>-139.8779999999999</v>
       </c>
       <c r="F42">
-        <v>677.6800000000001</v>
+        <v>694.6220000000001</v>
       </c>
       <c r="G42">
         <v>96.09999999999999</v>
@@ -4737,28 +4737,28 @@
         <v>136.125</v>
       </c>
       <c r="M42">
-        <v>43.439288</v>
+        <v>44.52527020000001</v>
       </c>
       <c r="N42">
-        <v>92.68571199999997</v>
+        <v>91.59972979999996</v>
       </c>
       <c r="O42">
-        <v>23.11581657279999</v>
+        <v>22.84497261211999</v>
       </c>
       <c r="P42">
-        <v>69.56989542719998</v>
+        <v>68.75475718787997</v>
       </c>
       <c r="Q42">
-        <v>168.0698954272</v>
+        <v>167.25475718788</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.09805010420670474</v>
+        <v>0.09878849352167371</v>
       </c>
       <c r="T42">
-        <v>1.206699866205652</v>
+        <v>1.223752737221102</v>
       </c>
       <c r="U42">
         <v>0.0641</v>
@@ -4775,7 +4775,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>3.133683959092514</v>
+        <v>3.057252643017087</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4783,22 +4783,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.07801172977778748</v>
+        <v>0.08040697863155213</v>
       </c>
       <c r="C43">
-        <v>973.4787377680163</v>
+        <v>847.7340305064504</v>
       </c>
       <c r="D43">
-        <v>1572.000737768017</v>
+        <v>1463.198030506451</v>
       </c>
       <c r="E43">
-        <v>-139.8779999999999</v>
+        <v>-122.9359999999999</v>
       </c>
       <c r="F43">
-        <v>694.6220000000001</v>
+        <v>711.5640000000001</v>
       </c>
       <c r="G43">
         <v>96.09999999999999</v>
@@ -4819,45 +4819,45 @@
         <v>136.125</v>
       </c>
       <c r="M43">
-        <v>44.52527020000001</v>
+        <v>51.16145160000001</v>
       </c>
       <c r="N43">
-        <v>91.59972979999996</v>
+        <v>84.96354839999996</v>
       </c>
       <c r="O43">
-        <v>22.84497261211999</v>
+        <v>21.18990897095999</v>
       </c>
       <c r="P43">
-        <v>68.75475718787997</v>
+        <v>63.77363942903997</v>
       </c>
       <c r="Q43">
-        <v>167.25475718788</v>
+        <v>162.27363942904</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.09878849352167371</v>
+        <v>0.09955234453715886</v>
       </c>
       <c r="T43">
-        <v>1.223752737221102</v>
+        <v>1.241393638271567</v>
       </c>
       <c r="U43">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V43">
         <v>0.2494</v>
       </c>
       <c r="W43">
-        <v>0.04811346</v>
+        <v>0.05396814</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y43">
-        <v>3.057252643017087</v>
+        <v>2.660694639086432</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4865,22 +4865,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.08040697863155215</v>
+        <v>0.08040180868531679</v>
       </c>
       <c r="C44">
-        <v>847.73403050645</v>
+        <v>831.0106507299819</v>
       </c>
       <c r="D44">
-        <v>1463.19803050645</v>
+        <v>1463.416650729982</v>
       </c>
       <c r="E44">
-        <v>-122.936</v>
+        <v>-105.994</v>
       </c>
       <c r="F44">
-        <v>711.564</v>
+        <v>728.506</v>
       </c>
       <c r="G44">
         <v>96.09999999999999</v>
@@ -4901,28 +4901,28 @@
         <v>136.125</v>
       </c>
       <c r="M44">
-        <v>51.1614516</v>
+        <v>52.3795814</v>
       </c>
       <c r="N44">
-        <v>84.96354839999998</v>
+        <v>83.74541859999997</v>
       </c>
       <c r="O44">
-        <v>21.18990897095999</v>
+        <v>20.88610739883999</v>
       </c>
       <c r="P44">
-        <v>63.77363942903999</v>
+        <v>62.85931120115997</v>
       </c>
       <c r="Q44">
-        <v>162.27363942904</v>
+        <v>161.35931120116</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.09955234453715886</v>
+        <v>0.100342997342661</v>
       </c>
       <c r="T44">
-        <v>1.241393638271567</v>
+        <v>1.259653518306259</v>
       </c>
       <c r="U44">
         <v>0.07190000000000001</v>
@@ -4939,7 +4939,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>2.660694639086432</v>
+        <v>2.598818019572794</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4947,22 +4947,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.08040180868531679</v>
+        <v>0.08039663873908143</v>
       </c>
       <c r="C45">
-        <v>831.0106507299819</v>
+        <v>814.2873362925094</v>
       </c>
       <c r="D45">
-        <v>1463.416650729982</v>
+        <v>1463.635336292509</v>
       </c>
       <c r="E45">
-        <v>-105.994</v>
+        <v>-89.05200000000002</v>
       </c>
       <c r="F45">
-        <v>728.506</v>
+        <v>745.448</v>
       </c>
       <c r="G45">
         <v>96.09999999999999</v>
@@ -4983,28 +4983,28 @@
         <v>136.125</v>
       </c>
       <c r="M45">
-        <v>52.3795814</v>
+        <v>53.5977112</v>
       </c>
       <c r="N45">
-        <v>83.74541859999997</v>
+        <v>82.52728879999998</v>
       </c>
       <c r="O45">
-        <v>20.88610739883999</v>
+        <v>20.58230582672</v>
       </c>
       <c r="P45">
-        <v>62.85931120115997</v>
+        <v>61.94498297327998</v>
       </c>
       <c r="Q45">
-        <v>161.35931120116</v>
+        <v>160.44498297328</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.100342997342661</v>
+        <v>0.1011618877483597</v>
       </c>
       <c r="T45">
-        <v>1.259653518306259</v>
+        <v>1.278565536913619</v>
       </c>
       <c r="U45">
         <v>0.07190000000000001</v>
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>2.598818019572794</v>
+        <v>2.539753973673413</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5029,22 +5029,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.08039663873908143</v>
+        <v>0.08170877179284609</v>
       </c>
       <c r="C46">
-        <v>814.2873362925094</v>
+        <v>743.8630196461357</v>
       </c>
       <c r="D46">
-        <v>1463.635336292509</v>
+        <v>1410.153019646136</v>
       </c>
       <c r="E46">
-        <v>-89.05200000000002</v>
+        <v>-72.11000000000001</v>
       </c>
       <c r="F46">
-        <v>745.448</v>
+        <v>762.39</v>
       </c>
       <c r="G46">
         <v>96.09999999999999</v>
@@ -5065,45 +5065,45 @@
         <v>136.125</v>
       </c>
       <c r="M46">
-        <v>53.5977112</v>
+        <v>57.789162</v>
       </c>
       <c r="N46">
-        <v>82.52728879999998</v>
+        <v>78.33583799999997</v>
       </c>
       <c r="O46">
-        <v>20.58230582672</v>
+        <v>19.53695799719999</v>
       </c>
       <c r="P46">
-        <v>61.94498297327998</v>
+        <v>58.79888000279998</v>
       </c>
       <c r="Q46">
-        <v>160.44498297328</v>
+        <v>157.2988800028</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1011618877483597</v>
+        <v>0.1020105559869929</v>
       </c>
       <c r="T46">
-        <v>1.278565536913619</v>
+        <v>1.298165265288519</v>
       </c>
       <c r="U46">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V46">
         <v>0.2494</v>
       </c>
       <c r="W46">
-        <v>0.05396814</v>
+        <v>0.05689548</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y46">
-        <v>2.539753973673413</v>
+        <v>2.355545491384698</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5111,22 +5111,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.08170877179284609</v>
+        <v>0.08173287524661074</v>
       </c>
       <c r="C47">
-        <v>743.8630196461357</v>
+        <v>725.9751015174902</v>
       </c>
       <c r="D47">
-        <v>1410.153019646136</v>
+        <v>1409.20710151749</v>
       </c>
       <c r="E47">
-        <v>-72.11000000000001</v>
+        <v>-55.16799999999989</v>
       </c>
       <c r="F47">
-        <v>762.39</v>
+        <v>779.3320000000001</v>
       </c>
       <c r="G47">
         <v>96.09999999999999</v>
@@ -5147,28 +5147,28 @@
         <v>136.125</v>
       </c>
       <c r="M47">
-        <v>57.789162</v>
+        <v>59.07336560000001</v>
       </c>
       <c r="N47">
-        <v>78.33583799999997</v>
+        <v>77.05163439999995</v>
       </c>
       <c r="O47">
-        <v>19.53695799719999</v>
+        <v>19.21667761935999</v>
       </c>
       <c r="P47">
-        <v>58.79888000279998</v>
+        <v>57.83495678063997</v>
       </c>
       <c r="Q47">
-        <v>157.2988800028</v>
+        <v>156.33495678064</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1020105559869929</v>
+        <v>0.1028906563826125</v>
       </c>
       <c r="T47">
-        <v>1.298165265288519</v>
+        <v>1.318490909529156</v>
       </c>
       <c r="U47">
         <v>0.07580000000000001</v>
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>2.355545491384698</v>
+        <v>2.304337980702423</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5193,22 +5193,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.08173287524661074</v>
+        <v>0.08175697870037538</v>
       </c>
       <c r="C48">
-        <v>725.9751015174902</v>
+        <v>708.088451565133</v>
       </c>
       <c r="D48">
-        <v>1409.20710151749</v>
+        <v>1408.262451565133</v>
       </c>
       <c r="E48">
-        <v>-55.16799999999989</v>
+        <v>-38.22599999999989</v>
       </c>
       <c r="F48">
-        <v>779.3320000000001</v>
+        <v>796.2740000000001</v>
       </c>
       <c r="G48">
         <v>96.09999999999999</v>
@@ -5229,28 +5229,28 @@
         <v>136.125</v>
       </c>
       <c r="M48">
-        <v>59.07336560000001</v>
+        <v>60.35756920000001</v>
       </c>
       <c r="N48">
-        <v>77.05163439999995</v>
+        <v>75.76743079999996</v>
       </c>
       <c r="O48">
-        <v>19.21667761935999</v>
+        <v>18.89639724151999</v>
       </c>
       <c r="P48">
-        <v>57.83495678063997</v>
+        <v>56.87103355847997</v>
       </c>
       <c r="Q48">
-        <v>156.33495678064</v>
+        <v>155.37103355848</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1028906563826125</v>
+        <v>0.1038039681139158</v>
       </c>
       <c r="T48">
-        <v>1.318490909529156</v>
+        <v>1.339583559212836</v>
       </c>
       <c r="U48">
         <v>0.07580000000000001</v>
@@ -5267,7 +5267,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>2.304337980702423</v>
+        <v>2.255309513027902</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5275,22 +5275,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.08175697870037538</v>
+        <v>0.08178108215414003</v>
       </c>
       <c r="C49">
-        <v>708.088451565133</v>
+        <v>690.2030672404376</v>
       </c>
       <c r="D49">
-        <v>1408.262451565133</v>
+        <v>1407.319067240438</v>
       </c>
       <c r="E49">
-        <v>-38.22599999999989</v>
+        <v>-21.28399999999988</v>
       </c>
       <c r="F49">
-        <v>796.2740000000001</v>
+        <v>813.2160000000001</v>
       </c>
       <c r="G49">
         <v>96.09999999999999</v>
@@ -5311,28 +5311,28 @@
         <v>136.125</v>
       </c>
       <c r="M49">
-        <v>60.35756920000001</v>
+        <v>61.64177280000001</v>
       </c>
       <c r="N49">
-        <v>75.76743079999996</v>
+        <v>74.48322719999996</v>
       </c>
       <c r="O49">
-        <v>18.89639724151999</v>
+        <v>18.57611686367999</v>
       </c>
       <c r="P49">
-        <v>56.87103355847997</v>
+        <v>55.90711033631997</v>
       </c>
       <c r="Q49">
-        <v>155.37103355848</v>
+        <v>154.40711033632</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1038039681139158</v>
+        <v>0.1047524072195</v>
       </c>
       <c r="T49">
-        <v>1.339583559212836</v>
+        <v>1.361487464653581</v>
       </c>
       <c r="U49">
         <v>0.07580000000000001</v>
@@ -5349,7 +5349,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>2.255309513027902</v>
+        <v>2.208323898173155</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.08178108215414003</v>
+        <v>0.08180518560790467</v>
       </c>
       <c r="C50">
-        <v>690.2030672404377</v>
+        <v>672.3189460016046</v>
       </c>
       <c r="D50">
-        <v>1407.319067240438</v>
+        <v>1406.376946001605</v>
       </c>
       <c r="E50">
-        <v>-21.28399999999999</v>
+        <v>-4.341999999999985</v>
       </c>
       <c r="F50">
-        <v>813.216</v>
+        <v>830.158</v>
       </c>
       <c r="G50">
         <v>96.09999999999999</v>
@@ -5393,28 +5393,28 @@
         <v>136.125</v>
       </c>
       <c r="M50">
-        <v>61.64177280000001</v>
+        <v>62.9259764</v>
       </c>
       <c r="N50">
-        <v>74.48322719999996</v>
+        <v>73.19902359999998</v>
       </c>
       <c r="O50">
-        <v>18.57611686367999</v>
+        <v>18.25583648584</v>
       </c>
       <c r="P50">
-        <v>55.90711033631997</v>
+        <v>54.94318711415998</v>
       </c>
       <c r="Q50">
-        <v>154.40711033632</v>
+        <v>153.44318711416</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1047524072195</v>
+        <v>0.1057380400154994</v>
       </c>
       <c r="T50">
-        <v>1.361487464653581</v>
+        <v>1.384250346778277</v>
       </c>
       <c r="U50">
         <v>0.07580000000000001</v>
@@ -5431,7 +5431,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>2.208323898173155</v>
+        <v>2.163256063516561</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5439,22 +5439,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.08180518560790467</v>
+        <v>0.08182928906166932</v>
       </c>
       <c r="C51">
-        <v>672.3189460016046</v>
+        <v>654.4360853136349</v>
       </c>
       <c r="D51">
-        <v>1406.376946001605</v>
+        <v>1405.436085313635</v>
       </c>
       <c r="E51">
-        <v>-4.341999999999985</v>
+        <v>12.60000000000002</v>
       </c>
       <c r="F51">
-        <v>830.158</v>
+        <v>847.1</v>
       </c>
       <c r="G51">
         <v>96.09999999999999</v>
@@ -5475,28 +5475,28 @@
         <v>136.125</v>
       </c>
       <c r="M51">
-        <v>62.9259764</v>
+        <v>64.21018000000001</v>
       </c>
       <c r="N51">
-        <v>73.19902359999998</v>
+        <v>71.91481999999996</v>
       </c>
       <c r="O51">
-        <v>18.25583648584</v>
+        <v>17.93555610799999</v>
       </c>
       <c r="P51">
-        <v>54.94318711415998</v>
+        <v>53.97926389199997</v>
       </c>
       <c r="Q51">
-        <v>153.44318711416</v>
+        <v>152.479263892</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1057380400154994</v>
+        <v>0.1067630981233386</v>
       </c>
       <c r="T51">
-        <v>1.384250346778277</v>
+        <v>1.40792374418796</v>
       </c>
       <c r="U51">
         <v>0.07580000000000001</v>
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>2.163256063516561</v>
+        <v>2.119990942246229</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5521,22 +5521,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.08182928906166932</v>
+        <v>0.08185339251543397</v>
       </c>
       <c r="C52">
-        <v>654.4360853136349</v>
+        <v>636.5544826483095</v>
       </c>
       <c r="D52">
-        <v>1405.436085313635</v>
+        <v>1404.49648264831</v>
       </c>
       <c r="E52">
-        <v>12.60000000000002</v>
+        <v>29.54200000000003</v>
       </c>
       <c r="F52">
-        <v>847.1</v>
+        <v>864.042</v>
       </c>
       <c r="G52">
         <v>96.09999999999999</v>
@@ -5557,28 +5557,28 @@
         <v>136.125</v>
       </c>
       <c r="M52">
-        <v>64.21018000000001</v>
+        <v>65.49438360000001</v>
       </c>
       <c r="N52">
-        <v>71.91481999999996</v>
+        <v>70.63061639999997</v>
       </c>
       <c r="O52">
-        <v>17.93555610799999</v>
+        <v>17.61527573015999</v>
       </c>
       <c r="P52">
-        <v>53.97926389199997</v>
+        <v>53.01534066983997</v>
       </c>
       <c r="Q52">
-        <v>152.479263892</v>
+        <v>151.51534066984</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1067630981233386</v>
+        <v>0.1078299953376204</v>
       </c>
       <c r="T52">
-        <v>1.40792374418796</v>
+        <v>1.432563402716406</v>
       </c>
       <c r="U52">
         <v>0.07580000000000001</v>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>2.119990942246229</v>
+        <v>2.078422492398263</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5603,22 +5603,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.08185339251543397</v>
+        <v>0.08187749596919862</v>
       </c>
       <c r="C53">
-        <v>636.5544826483095</v>
+        <v>618.674135484165</v>
       </c>
       <c r="D53">
-        <v>1404.49648264831</v>
+        <v>1403.558135484165</v>
       </c>
       <c r="E53">
-        <v>29.54200000000003</v>
+        <v>46.48400000000004</v>
       </c>
       <c r="F53">
-        <v>864.042</v>
+        <v>880.984</v>
       </c>
       <c r="G53">
         <v>96.09999999999999</v>
@@ -5639,28 +5639,28 @@
         <v>136.125</v>
       </c>
       <c r="M53">
-        <v>65.49438360000001</v>
+        <v>66.7785872</v>
       </c>
       <c r="N53">
-        <v>70.63061639999997</v>
+        <v>69.34641279999997</v>
       </c>
       <c r="O53">
-        <v>17.61527573015999</v>
+        <v>17.29499535231999</v>
       </c>
       <c r="P53">
-        <v>53.01534066983997</v>
+        <v>52.05141744767997</v>
       </c>
       <c r="Q53">
-        <v>151.51534066984</v>
+        <v>150.55141744768</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1078299953376204</v>
+        <v>0.1089413466024971</v>
       </c>
       <c r="T53">
-        <v>1.432563402716406</v>
+        <v>1.458229713683537</v>
       </c>
       <c r="U53">
         <v>0.07580000000000001</v>
@@ -5677,7 +5677,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>2.078422492398263</v>
+        <v>2.038452829082912</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5685,22 +5685,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.08187749596919862</v>
+        <v>0.08755061502296327</v>
       </c>
       <c r="C54">
-        <v>618.674135484165</v>
+        <v>411.0151269538209</v>
       </c>
       <c r="D54">
-        <v>1403.558135484165</v>
+        <v>1212.841126953821</v>
       </c>
       <c r="E54">
-        <v>46.48400000000004</v>
+        <v>63.42600000000004</v>
       </c>
       <c r="F54">
-        <v>880.984</v>
+        <v>897.926</v>
       </c>
       <c r="G54">
         <v>96.09999999999999</v>
@@ -5721,45 +5721,45 @@
         <v>136.125</v>
       </c>
       <c r="M54">
-        <v>66.7785872</v>
+        <v>80.81334000000001</v>
       </c>
       <c r="N54">
-        <v>69.34641279999997</v>
+        <v>55.31165999999996</v>
       </c>
       <c r="O54">
-        <v>17.29499535231999</v>
+        <v>13.79472800399999</v>
       </c>
       <c r="P54">
-        <v>52.05141744767997</v>
+        <v>41.51693199599997</v>
       </c>
       <c r="Q54">
-        <v>150.55141744768</v>
+        <v>140.016931996</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1089413466024971</v>
+        <v>0.1100999894105602</v>
       </c>
       <c r="T54">
-        <v>1.458229713683537</v>
+        <v>1.484988208096078</v>
       </c>
       <c r="U54">
-        <v>0.07580000000000001</v>
+        <v>0.09000000000000001</v>
       </c>
       <c r="V54">
         <v>0.2494</v>
       </c>
       <c r="W54">
-        <v>0.05689548</v>
+        <v>0.067554</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y54">
-        <v>2.038452829082912</v>
+        <v>1.684437247612832</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5767,22 +5767,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.08755061502296327</v>
+        <v>0.08768130367672791</v>
       </c>
       <c r="C55">
-        <v>411.0151269538209</v>
+        <v>390.2885128134529</v>
       </c>
       <c r="D55">
-        <v>1212.841126953821</v>
+        <v>1209.056512813453</v>
       </c>
       <c r="E55">
-        <v>63.42600000000004</v>
+        <v>80.36800000000005</v>
       </c>
       <c r="F55">
-        <v>897.926</v>
+        <v>914.8680000000001</v>
       </c>
       <c r="G55">
         <v>96.09999999999999</v>
@@ -5803,28 +5803,28 @@
         <v>136.125</v>
       </c>
       <c r="M55">
-        <v>80.81334000000001</v>
+        <v>82.33812000000002</v>
       </c>
       <c r="N55">
-        <v>55.31165999999996</v>
+        <v>53.78687999999995</v>
       </c>
       <c r="O55">
-        <v>13.79472800399999</v>
+        <v>13.41444787199999</v>
       </c>
       <c r="P55">
-        <v>41.51693199599997</v>
+        <v>40.37243212799996</v>
       </c>
       <c r="Q55">
-        <v>140.016931996</v>
+        <v>138.872432128</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1100999894105602</v>
+        <v>0.1113090079928868</v>
       </c>
       <c r="T55">
-        <v>1.484988208096078</v>
+        <v>1.512910115309164</v>
       </c>
       <c r="U55">
         <v>0.09000000000000001</v>
@@ -5841,7 +5841,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>1.684437247612832</v>
+        <v>1.653243965249631</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5849,22 +5849,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.08768130367672791</v>
+        <v>0.08781199233049257</v>
       </c>
       <c r="C56">
-        <v>390.2885128134529</v>
+        <v>369.5854446226855</v>
       </c>
       <c r="D56">
-        <v>1209.056512813453</v>
+        <v>1205.295444622686</v>
       </c>
       <c r="E56">
-        <v>80.36800000000005</v>
+        <v>97.31000000000006</v>
       </c>
       <c r="F56">
-        <v>914.8680000000001</v>
+        <v>931.8100000000001</v>
       </c>
       <c r="G56">
         <v>96.09999999999999</v>
@@ -5885,28 +5885,28 @@
         <v>136.125</v>
       </c>
       <c r="M56">
-        <v>82.33812000000002</v>
+        <v>83.86290000000001</v>
       </c>
       <c r="N56">
-        <v>53.78687999999995</v>
+        <v>52.26209999999996</v>
       </c>
       <c r="O56">
-        <v>13.41444787199999</v>
+        <v>13.03416773999999</v>
       </c>
       <c r="P56">
-        <v>40.37243212799996</v>
+        <v>39.22793225999997</v>
       </c>
       <c r="Q56">
-        <v>138.872432128</v>
+        <v>137.72793226</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1113090079928868</v>
+        <v>0.1125717607344279</v>
       </c>
       <c r="T56">
-        <v>1.512910115309164</v>
+        <v>1.542072996176165</v>
       </c>
       <c r="U56">
         <v>0.09000000000000001</v>
@@ -5923,7 +5923,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>1.653243965249631</v>
+        <v>1.623184984063274</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5931,22 +5931,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.08781199233049257</v>
+        <v>0.08794268098425723</v>
       </c>
       <c r="C57">
-        <v>369.5854446226855</v>
+        <v>348.90570332651</v>
       </c>
       <c r="D57">
-        <v>1205.295444622686</v>
+        <v>1201.55770332651</v>
       </c>
       <c r="E57">
-        <v>97.31000000000006</v>
+        <v>114.2520000000001</v>
       </c>
       <c r="F57">
-        <v>931.8100000000001</v>
+        <v>948.7520000000001</v>
       </c>
       <c r="G57">
         <v>96.09999999999999</v>
@@ -5967,28 +5967,28 @@
         <v>136.125</v>
       </c>
       <c r="M57">
-        <v>83.86290000000001</v>
+        <v>85.38768000000002</v>
       </c>
       <c r="N57">
-        <v>52.26209999999996</v>
+        <v>50.73731999999995</v>
       </c>
       <c r="O57">
-        <v>13.03416773999999</v>
+        <v>12.65388760799999</v>
       </c>
       <c r="P57">
-        <v>39.22793225999997</v>
+        <v>38.08343239199996</v>
       </c>
       <c r="Q57">
-        <v>137.72793226</v>
+        <v>136.583432392</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1125717607344279</v>
+        <v>0.1138919113278573</v>
       </c>
       <c r="T57">
-        <v>1.542072996176165</v>
+        <v>1.572561462537121</v>
       </c>
       <c r="U57">
         <v>0.09000000000000001</v>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>1.623184984063274</v>
+        <v>1.594199537919287</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6013,22 +6013,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.08794268098425723</v>
+        <v>0.08807336963802187</v>
       </c>
       <c r="C58">
-        <v>348.90570332651</v>
+        <v>328.2490725787627</v>
       </c>
       <c r="D58">
-        <v>1201.55770332651</v>
+        <v>1197.843072578763</v>
       </c>
       <c r="E58">
-        <v>114.2520000000001</v>
+        <v>131.1940000000002</v>
       </c>
       <c r="F58">
-        <v>948.7520000000001</v>
+        <v>965.6940000000002</v>
       </c>
       <c r="G58">
         <v>96.09999999999999</v>
@@ -6049,28 +6049,28 @@
         <v>136.125</v>
       </c>
       <c r="M58">
-        <v>85.38768000000002</v>
+        <v>86.91246000000002</v>
       </c>
       <c r="N58">
-        <v>50.73731999999995</v>
+        <v>49.21253999999995</v>
       </c>
       <c r="O58">
-        <v>12.65388760799999</v>
+        <v>12.27360747599999</v>
       </c>
       <c r="P58">
-        <v>38.08343239199996</v>
+        <v>36.93893252399996</v>
       </c>
       <c r="Q58">
-        <v>136.583432392</v>
+        <v>135.438932524</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1138919113278573</v>
+        <v>0.1152734642744695</v>
       </c>
       <c r="T58">
-        <v>1.572561462537121</v>
+        <v>1.604467997100911</v>
       </c>
       <c r="U58">
         <v>0.09000000000000001</v>
@@ -6087,7 +6087,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>1.594199537919287</v>
+        <v>1.566231124973334</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6095,22 +6095,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.08807336963802187</v>
+        <v>0.08820405829178651</v>
       </c>
       <c r="C59">
-        <v>328.2490725787627</v>
+        <v>307.6153387003817</v>
       </c>
       <c r="D59">
-        <v>1197.843072578763</v>
+        <v>1194.151338700382</v>
       </c>
       <c r="E59">
-        <v>131.1940000000002</v>
+        <v>148.1360000000002</v>
       </c>
       <c r="F59">
-        <v>965.6940000000002</v>
+        <v>982.6360000000002</v>
       </c>
       <c r="G59">
         <v>96.09999999999999</v>
@@ -6131,28 +6131,28 @@
         <v>136.125</v>
       </c>
       <c r="M59">
-        <v>86.91246000000002</v>
+        <v>88.43724000000003</v>
       </c>
       <c r="N59">
-        <v>49.21253999999995</v>
+        <v>47.68775999999994</v>
       </c>
       <c r="O59">
-        <v>12.27360747599999</v>
+        <v>11.89332734399999</v>
       </c>
       <c r="P59">
-        <v>36.93893252399996</v>
+        <v>35.79443265599996</v>
       </c>
       <c r="Q59">
-        <v>135.438932524</v>
+        <v>134.294432656</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1152734642744695</v>
+        <v>0.1167208054566345</v>
       </c>
       <c r="T59">
-        <v>1.604467997100911</v>
+        <v>1.637893890453454</v>
       </c>
       <c r="U59">
         <v>0.09000000000000001</v>
@@ -6169,7 +6169,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>1.566231124973334</v>
+        <v>1.539227140060001</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6177,22 +6177,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.08820405829178651</v>
+        <v>0.08833474694555116</v>
       </c>
       <c r="C60">
-        <v>307.6153387003819</v>
+        <v>287.0042906384347</v>
       </c>
       <c r="D60">
-        <v>1194.151338700382</v>
+        <v>1190.482290638435</v>
       </c>
       <c r="E60">
-        <v>148.136</v>
+        <v>165.078</v>
       </c>
       <c r="F60">
-        <v>982.636</v>
+        <v>999.578</v>
       </c>
       <c r="G60">
         <v>96.09999999999999</v>
@@ -6213,28 +6213,28 @@
         <v>136.125</v>
       </c>
       <c r="M60">
-        <v>88.43724</v>
+        <v>89.96202000000001</v>
       </c>
       <c r="N60">
-        <v>47.68775999999997</v>
+        <v>46.16297999999996</v>
       </c>
       <c r="O60">
-        <v>11.89332734399999</v>
+        <v>11.51304721199999</v>
       </c>
       <c r="P60">
-        <v>35.79443265599998</v>
+        <v>34.64993278799997</v>
       </c>
       <c r="Q60">
-        <v>134.294432656</v>
+        <v>133.149932788</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1167208054566345</v>
+        <v>0.1182387486476857</v>
       </c>
       <c r="T60">
-        <v>1.637893890453454</v>
+        <v>1.672950315189048</v>
       </c>
       <c r="U60">
         <v>0.09000000000000001</v>
@@ -6251,7 +6251,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>1.539227140060001</v>
+        <v>1.513138544465764</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6259,22 +6259,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.08833474694555116</v>
+        <v>0.1164317989693688</v>
       </c>
       <c r="C61">
-        <v>287.0042906384347</v>
+        <v>-203.5068855906414</v>
       </c>
       <c r="D61">
-        <v>1190.482290638435</v>
+        <v>716.9131144093585</v>
       </c>
       <c r="E61">
-        <v>165.078</v>
+        <v>182.02</v>
       </c>
       <c r="F61">
-        <v>999.578</v>
+        <v>1016.52</v>
       </c>
       <c r="G61">
         <v>96.09999999999999</v>
@@ -6295,45 +6295,45 @@
         <v>136.125</v>
       </c>
       <c r="M61">
-        <v>89.96202000000001</v>
+        <v>149.225136</v>
       </c>
       <c r="N61">
-        <v>46.16297999999996</v>
+        <v>-13.10013600000005</v>
       </c>
       <c r="O61">
-        <v>11.51304721199999</v>
+        <v>-3.267173918400012</v>
       </c>
       <c r="P61">
-        <v>34.64993278799997</v>
+        <v>-9.832962081600037</v>
       </c>
       <c r="Q61">
-        <v>133.149932788</v>
+        <v>88.66703791839996</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1182387486476857</v>
+        <v>0.1209762613828128</v>
       </c>
       <c r="T61">
-        <v>1.672950315189048</v>
+        <v>1.736172318309764</v>
       </c>
       <c r="U61">
-        <v>0.09000000000000001</v>
+        <v>0.1468</v>
       </c>
       <c r="V61">
-        <v>0.2494</v>
+        <v>0.2275057400517295</v>
       </c>
       <c r="W61">
-        <v>0.067554</v>
+        <v>0.1134021573604061</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y61">
-        <v>1.513138544465764</v>
+        <v>0.912212269654088</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6341,22 +6341,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1164317989693688</v>
+        <v>0.1174417989693688</v>
       </c>
       <c r="C62">
-        <v>-203.5068855906414</v>
+        <v>-230.5558658168507</v>
       </c>
       <c r="D62">
-        <v>716.9131144093585</v>
+        <v>706.8061341831493</v>
       </c>
       <c r="E62">
-        <v>182.02</v>
+        <v>198.962</v>
       </c>
       <c r="F62">
-        <v>1016.52</v>
+        <v>1033.462</v>
       </c>
       <c r="G62">
         <v>96.09999999999999</v>
@@ -6377,37 +6377,37 @@
         <v>136.125</v>
       </c>
       <c r="M62">
-        <v>149.225136</v>
+        <v>151.7122216</v>
       </c>
       <c r="N62">
-        <v>-13.10013600000005</v>
+        <v>-15.58722160000005</v>
       </c>
       <c r="O62">
-        <v>-3.267173918400012</v>
+        <v>-3.887453067040012</v>
       </c>
       <c r="P62">
-        <v>-9.832962081600037</v>
+        <v>-11.69976853296004</v>
       </c>
       <c r="Q62">
-        <v>88.66703791839996</v>
+        <v>86.80023146703996</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1209762613828128</v>
+        <v>0.1229038578285259</v>
       </c>
       <c r="T62">
-        <v>1.736172318309764</v>
+        <v>1.780689557240784</v>
       </c>
       <c r="U62">
         <v>0.1468</v>
       </c>
       <c r="V62">
-        <v>0.2275057400517295</v>
+        <v>0.2237761377557995</v>
       </c>
       <c r="W62">
-        <v>0.1134021573604061</v>
+        <v>0.1139496629774486</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.912212269654088</v>
+        <v>0.8972579701515619</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1174417989693688</v>
+        <v>0.1184517989693688</v>
       </c>
       <c r="C63">
-        <v>-230.5558658168507</v>
+        <v>-257.3238330420523</v>
       </c>
       <c r="D63">
-        <v>706.8061341831493</v>
+        <v>696.9801669579476</v>
       </c>
       <c r="E63">
-        <v>198.962</v>
+        <v>215.904</v>
       </c>
       <c r="F63">
-        <v>1033.462</v>
+        <v>1050.404</v>
       </c>
       <c r="G63">
         <v>96.09999999999999</v>
@@ -6459,37 +6459,37 @@
         <v>136.125</v>
       </c>
       <c r="M63">
-        <v>151.7122216</v>
+        <v>154.1993072</v>
       </c>
       <c r="N63">
-        <v>-15.58722160000005</v>
+        <v>-18.07430720000005</v>
       </c>
       <c r="O63">
-        <v>-3.887453067040012</v>
+        <v>-4.507732215680012</v>
       </c>
       <c r="P63">
-        <v>-11.69976853296004</v>
+        <v>-13.56657498432004</v>
       </c>
       <c r="Q63">
-        <v>86.80023146703996</v>
+        <v>84.93342501567996</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1229038578285259</v>
+        <v>0.1249329067187503</v>
       </c>
       <c r="T63">
-        <v>1.780689557240784</v>
+        <v>1.827549808747121</v>
       </c>
       <c r="U63">
         <v>0.1468</v>
       </c>
       <c r="V63">
-        <v>0.2237761377557995</v>
+        <v>0.2201668452113512</v>
       </c>
       <c r="W63">
-        <v>0.1139496629774486</v>
+        <v>0.1144795071229737</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6497,7 +6497,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.8972579701515619</v>
+        <v>0.8827860674071819</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6505,22 +6505,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1184517989693688</v>
+        <v>0.1194617989693688</v>
       </c>
       <c r="C64">
-        <v>-257.3238330420523</v>
+        <v>-283.8223464380972</v>
       </c>
       <c r="D64">
-        <v>696.9801669579476</v>
+        <v>687.4236535619028</v>
       </c>
       <c r="E64">
-        <v>215.904</v>
+        <v>232.846</v>
       </c>
       <c r="F64">
-        <v>1050.404</v>
+        <v>1067.346</v>
       </c>
       <c r="G64">
         <v>96.09999999999999</v>
@@ -6541,37 +6541,37 @@
         <v>136.125</v>
       </c>
       <c r="M64">
-        <v>154.1993072</v>
+        <v>156.6863928</v>
       </c>
       <c r="N64">
-        <v>-18.07430720000005</v>
+        <v>-20.56139280000005</v>
       </c>
       <c r="O64">
-        <v>-4.507732215680012</v>
+        <v>-5.128011364320012</v>
       </c>
       <c r="P64">
-        <v>-13.56657498432004</v>
+        <v>-15.43338143568004</v>
       </c>
       <c r="Q64">
-        <v>84.93342501567996</v>
+        <v>83.06661856431997</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1249329067187503</v>
+        <v>0.1270716339273652</v>
       </c>
       <c r="T64">
-        <v>1.827549808747121</v>
+        <v>1.876943046821367</v>
       </c>
       <c r="U64">
         <v>0.1468</v>
       </c>
       <c r="V64">
-        <v>0.2201668452113512</v>
+        <v>0.2166721333825996</v>
       </c>
       <c r="W64">
-        <v>0.1144795071229737</v>
+        <v>0.1149925308194344</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6579,7 +6579,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.8827860674071819</v>
+        <v>0.8687735901467505</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6587,22 +6587,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1194617989693688</v>
+        <v>0.1204717989693688</v>
       </c>
       <c r="C65">
-        <v>-283.8223464380972</v>
+        <v>-310.0623397860589</v>
       </c>
       <c r="D65">
-        <v>687.4236535619028</v>
+        <v>678.125660213941</v>
       </c>
       <c r="E65">
-        <v>232.846</v>
+        <v>249.788</v>
       </c>
       <c r="F65">
-        <v>1067.346</v>
+        <v>1084.288</v>
       </c>
       <c r="G65">
         <v>96.09999999999999</v>
@@ -6623,37 +6623,37 @@
         <v>136.125</v>
       </c>
       <c r="M65">
-        <v>156.6863928</v>
+        <v>159.1734784</v>
       </c>
       <c r="N65">
-        <v>-20.56139280000005</v>
+        <v>-23.04847840000005</v>
       </c>
       <c r="O65">
-        <v>-5.128011364320012</v>
+        <v>-5.748290512960013</v>
       </c>
       <c r="P65">
-        <v>-15.43338143568004</v>
+        <v>-17.30018788704004</v>
       </c>
       <c r="Q65">
-        <v>83.06661856431997</v>
+        <v>81.19981211295996</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1270716339273652</v>
+        <v>0.1293291793142365</v>
       </c>
       <c r="T65">
-        <v>1.876943046821367</v>
+        <v>1.929080353677517</v>
       </c>
       <c r="U65">
         <v>0.1468</v>
       </c>
       <c r="V65">
-        <v>0.2166721333825996</v>
+        <v>0.2132866312984965</v>
       </c>
       <c r="W65">
-        <v>0.1149925308194344</v>
+        <v>0.1154895225253807</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6661,7 +6661,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.8687735901467505</v>
+        <v>0.8551990028007075</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6669,22 +6669,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1204717989693688</v>
+        <v>0.1214817989693688</v>
       </c>
       <c r="C66">
-        <v>-310.0623397860589</v>
+        <v>-336.0541632065259</v>
       </c>
       <c r="D66">
-        <v>678.125660213941</v>
+        <v>669.0758367934741</v>
       </c>
       <c r="E66">
-        <v>249.788</v>
+        <v>266.73</v>
       </c>
       <c r="F66">
-        <v>1084.288</v>
+        <v>1101.23</v>
       </c>
       <c r="G66">
         <v>96.09999999999999</v>
@@ -6705,37 +6705,37 @@
         <v>136.125</v>
       </c>
       <c r="M66">
-        <v>159.1734784</v>
+        <v>161.660564</v>
       </c>
       <c r="N66">
-        <v>-23.04847840000005</v>
+        <v>-25.53556400000005</v>
       </c>
       <c r="O66">
-        <v>-5.748290512960013</v>
+        <v>-6.368569661600013</v>
       </c>
       <c r="P66">
-        <v>-17.30018788704004</v>
+        <v>-19.16699433840004</v>
       </c>
       <c r="Q66">
-        <v>81.19981211295996</v>
+        <v>79.33300566159997</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1293291793142365</v>
+        <v>0.1317157272946432</v>
       </c>
       <c r="T66">
-        <v>1.929080353677517</v>
+        <v>1.98419693521116</v>
       </c>
       <c r="U66">
         <v>0.1468</v>
       </c>
       <c r="V66">
-        <v>0.2132866312984965</v>
+        <v>0.2100052985092888</v>
       </c>
       <c r="W66">
-        <v>0.1154895225253807</v>
+        <v>0.1159712221788364</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.8551990028007075</v>
+        <v>0.842042095065312</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6751,22 +6751,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1214817989693688</v>
+        <v>0.1224917989693688</v>
       </c>
       <c r="C67">
-        <v>-336.0541632065259</v>
+        <v>-361.8076215924654</v>
       </c>
       <c r="D67">
-        <v>669.0758367934741</v>
+        <v>660.2643784075347</v>
       </c>
       <c r="E67">
-        <v>266.73</v>
+        <v>283.672</v>
       </c>
       <c r="F67">
-        <v>1101.23</v>
+        <v>1118.172</v>
       </c>
       <c r="G67">
         <v>96.09999999999999</v>
@@ -6787,37 +6787,37 @@
         <v>136.125</v>
       </c>
       <c r="M67">
-        <v>161.660564</v>
+        <v>164.1476496</v>
       </c>
       <c r="N67">
-        <v>-25.53556400000005</v>
+        <v>-28.02264960000005</v>
       </c>
       <c r="O67">
-        <v>-6.368569661600013</v>
+        <v>-6.988848810240013</v>
       </c>
       <c r="P67">
-        <v>-19.16699433840004</v>
+        <v>-21.03380078976004</v>
       </c>
       <c r="Q67">
-        <v>79.33300566159997</v>
+        <v>77.46619921023996</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1317157272946432</v>
+        <v>0.134242660450368</v>
       </c>
       <c r="T67">
-        <v>1.98419693521116</v>
+        <v>2.042555668599723</v>
       </c>
       <c r="U67">
         <v>0.1468</v>
       </c>
       <c r="V67">
-        <v>0.2100052985092888</v>
+        <v>0.2068234000470269</v>
       </c>
       <c r="W67">
-        <v>0.1159712221788364</v>
+        <v>0.1164383248730965</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.842042095065312</v>
+        <v>0.8292838815037163</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6833,22 +6833,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1224917989693688</v>
+        <v>0.1235017989693688</v>
       </c>
       <c r="C68">
-        <v>-361.8076215924654</v>
+        <v>-387.3320100446874</v>
       </c>
       <c r="D68">
-        <v>660.2643784075347</v>
+        <v>651.6819899553126</v>
       </c>
       <c r="E68">
-        <v>283.672</v>
+        <v>300.614</v>
       </c>
       <c r="F68">
-        <v>1118.172</v>
+        <v>1135.114</v>
       </c>
       <c r="G68">
         <v>96.09999999999999</v>
@@ -6869,37 +6869,37 @@
         <v>136.125</v>
       </c>
       <c r="M68">
-        <v>164.1476496</v>
+        <v>166.6347352</v>
       </c>
       <c r="N68">
-        <v>-28.02264960000005</v>
+        <v>-30.50973520000005</v>
       </c>
       <c r="O68">
-        <v>-6.988848810240013</v>
+        <v>-7.609127958880013</v>
       </c>
       <c r="P68">
-        <v>-21.03380078976004</v>
+        <v>-22.90060724112004</v>
       </c>
       <c r="Q68">
-        <v>77.46619921023996</v>
+        <v>75.59939275887996</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.134242660450368</v>
+        <v>0.1369227410700761</v>
       </c>
       <c r="T68">
-        <v>2.042555668599723</v>
+        <v>2.104451294920927</v>
       </c>
       <c r="U68">
         <v>0.1468</v>
       </c>
       <c r="V68">
-        <v>0.2068234000470269</v>
+        <v>0.2037364836284145</v>
       </c>
       <c r="W68">
-        <v>0.1164383248730965</v>
+        <v>0.1168914842033488</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.8292838815037163</v>
+        <v>0.8169065101379892</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6915,22 +6915,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1235017989693688</v>
+        <v>0.1245117989693688</v>
       </c>
       <c r="C69">
-        <v>-387.3320100446874</v>
+        <v>-412.6361465791481</v>
       </c>
       <c r="D69">
-        <v>651.6819899553126</v>
+        <v>643.3198534208519</v>
       </c>
       <c r="E69">
-        <v>300.614</v>
+        <v>317.556</v>
       </c>
       <c r="F69">
-        <v>1135.114</v>
+        <v>1152.056</v>
       </c>
       <c r="G69">
         <v>96.09999999999999</v>
@@ -6951,37 +6951,37 @@
         <v>136.125</v>
       </c>
       <c r="M69">
-        <v>166.6347352</v>
+        <v>169.1218208</v>
       </c>
       <c r="N69">
-        <v>-30.50973520000005</v>
+        <v>-32.99682080000005</v>
       </c>
       <c r="O69">
-        <v>-7.609127958880013</v>
+        <v>-8.229407107520013</v>
       </c>
       <c r="P69">
-        <v>-22.90060724112004</v>
+        <v>-24.76741369248004</v>
       </c>
       <c r="Q69">
-        <v>75.59939275887996</v>
+        <v>73.73258630751997</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1369227410700761</v>
+        <v>0.139770326728516</v>
       </c>
       <c r="T69">
-        <v>2.104451294920927</v>
+        <v>2.170215397887206</v>
       </c>
       <c r="U69">
         <v>0.1468</v>
       </c>
       <c r="V69">
-        <v>0.2037364836284145</v>
+        <v>0.2007403588691731</v>
       </c>
       <c r="W69">
-        <v>0.1168914842033488</v>
+        <v>0.1173313153180054</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.8169065101379892</v>
+        <v>0.8048931791065482</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6997,22 +6997,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1245117989693688</v>
+        <v>0.164060160713875</v>
       </c>
       <c r="C70">
-        <v>-412.6361465791481</v>
+        <v>-644.7160774506179</v>
       </c>
       <c r="D70">
-        <v>643.3198534208519</v>
+        <v>428.1819225493821</v>
       </c>
       <c r="E70">
-        <v>317.556</v>
+        <v>334.498</v>
       </c>
       <c r="F70">
-        <v>1152.056</v>
+        <v>1168.998</v>
       </c>
       <c r="G70">
         <v>96.09999999999999</v>
@@ -7033,45 +7033,45 @@
         <v>136.125</v>
       </c>
       <c r="M70">
-        <v>169.1218208</v>
+        <v>234.7347984</v>
       </c>
       <c r="N70">
-        <v>-32.99682080000005</v>
+        <v>-98.60979840000005</v>
       </c>
       <c r="O70">
-        <v>-8.229407107520013</v>
+        <v>-24.59328372096001</v>
       </c>
       <c r="P70">
-        <v>-24.76741369248004</v>
+        <v>-74.01651467904003</v>
       </c>
       <c r="Q70">
-        <v>73.73258630751997</v>
+        <v>24.48348532095997</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.139770326728516</v>
+        <v>0.1469253751536493</v>
       </c>
       <c r="T70">
-        <v>2.170215397887206</v>
+        <v>2.33545901047689</v>
       </c>
       <c r="U70">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V70">
-        <v>0.2007403588691731</v>
+        <v>0.1446294935024853</v>
       </c>
       <c r="W70">
-        <v>0.1173313153180054</v>
+        <v>0.171758397704701</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y70">
-        <v>0.8048931791065482</v>
+        <v>0.5799097574277677</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7079,22 +7079,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.164060160713875</v>
+        <v>0.165610160713875</v>
       </c>
       <c r="C71">
-        <v>-644.7160774506179</v>
+        <v>-667.1975239883495</v>
       </c>
       <c r="D71">
-        <v>428.1819225493821</v>
+        <v>422.6424760116506</v>
       </c>
       <c r="E71">
-        <v>334.498</v>
+        <v>351.4400000000001</v>
       </c>
       <c r="F71">
-        <v>1168.998</v>
+        <v>1185.94</v>
       </c>
       <c r="G71">
         <v>96.09999999999999</v>
@@ -7115,37 +7115,37 @@
         <v>136.125</v>
       </c>
       <c r="M71">
-        <v>234.7347984</v>
+        <v>238.136752</v>
       </c>
       <c r="N71">
-        <v>-98.60979840000005</v>
+        <v>-102.0117520000001</v>
       </c>
       <c r="O71">
-        <v>-24.59328372096001</v>
+        <v>-25.44173094880001</v>
       </c>
       <c r="P71">
-        <v>-74.01651467904003</v>
+        <v>-76.57002105120004</v>
       </c>
       <c r="Q71">
-        <v>24.48348532095997</v>
+        <v>21.92997894879996</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1469253751536493</v>
+        <v>0.1502962209921043</v>
       </c>
       <c r="T71">
-        <v>2.33545901047689</v>
+        <v>2.413307644159453</v>
       </c>
       <c r="U71">
         <v>0.2008</v>
       </c>
       <c r="V71">
-        <v>0.1446294935024853</v>
+        <v>0.1425633578810212</v>
       </c>
       <c r="W71">
-        <v>0.171758397704701</v>
+        <v>0.172173277737491</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.5799097574277677</v>
+        <v>0.5716253323216567</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7161,22 +7161,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.165610160713875</v>
+        <v>0.167160160713875</v>
       </c>
       <c r="C72">
-        <v>-667.1975239883495</v>
+        <v>-689.5374719966959</v>
       </c>
       <c r="D72">
-        <v>422.6424760116506</v>
+        <v>417.2445280033041</v>
       </c>
       <c r="E72">
-        <v>351.4400000000001</v>
+        <v>368.3820000000001</v>
       </c>
       <c r="F72">
-        <v>1185.94</v>
+        <v>1202.882</v>
       </c>
       <c r="G72">
         <v>96.09999999999999</v>
@@ -7197,37 +7197,37 @@
         <v>136.125</v>
       </c>
       <c r="M72">
-        <v>238.136752</v>
+        <v>241.5387056</v>
       </c>
       <c r="N72">
-        <v>-102.0117520000001</v>
+        <v>-105.4137056</v>
       </c>
       <c r="O72">
-        <v>-25.44173094880001</v>
+        <v>-26.29017817664001</v>
       </c>
       <c r="P72">
-        <v>-76.57002105120004</v>
+        <v>-79.12352742336003</v>
       </c>
       <c r="Q72">
-        <v>21.92997894879996</v>
+        <v>19.37647257663997</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1502962209921043</v>
+        <v>0.1538995389573493</v>
       </c>
       <c r="T72">
-        <v>2.413307644159453</v>
+        <v>2.496525149130468</v>
       </c>
       <c r="U72">
         <v>0.2008</v>
       </c>
       <c r="V72">
-        <v>0.1425633578810212</v>
+        <v>0.1405554232629787</v>
       </c>
       <c r="W72">
-        <v>0.172173277737491</v>
+        <v>0.1725764710087939</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7235,7 +7235,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.5716253323216567</v>
+        <v>0.5635742713030418</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7243,22 +7243,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1671601607138749</v>
+        <v>0.1687101607138749</v>
       </c>
       <c r="C73">
-        <v>-689.5374719966958</v>
+        <v>-711.7412747203181</v>
       </c>
       <c r="D73">
-        <v>417.2445280033043</v>
+        <v>411.982725279682</v>
       </c>
       <c r="E73">
-        <v>368.3820000000001</v>
+        <v>385.3240000000001</v>
       </c>
       <c r="F73">
-        <v>1202.882</v>
+        <v>1219.824</v>
       </c>
       <c r="G73">
         <v>96.09999999999999</v>
@@ -7279,37 +7279,37 @@
         <v>136.125</v>
       </c>
       <c r="M73">
-        <v>241.5387056</v>
+        <v>244.9406592</v>
       </c>
       <c r="N73">
-        <v>-105.4137056</v>
+        <v>-108.8156592000001</v>
       </c>
       <c r="O73">
-        <v>-26.29017817664001</v>
+        <v>-27.13862540448002</v>
       </c>
       <c r="P73">
-        <v>-79.12352742336003</v>
+        <v>-81.67703379552003</v>
       </c>
       <c r="Q73">
-        <v>19.37647257663997</v>
+        <v>16.82296620447997</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1538995389573492</v>
+        <v>0.1577602367772546</v>
       </c>
       <c r="T73">
-        <v>2.496525149130468</v>
+        <v>2.585686761599413</v>
       </c>
       <c r="U73">
         <v>0.2008</v>
       </c>
       <c r="V73">
-        <v>0.1405554232629787</v>
+        <v>0.1386032646065484</v>
       </c>
       <c r="W73">
-        <v>0.1725764710087939</v>
+        <v>0.1729684644670051</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.5635742713030418</v>
+        <v>0.5557468508682775</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7325,22 +7325,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1687101607138749</v>
+        <v>0.1702601607138749</v>
       </c>
       <c r="C74">
-        <v>-711.7412747203181</v>
+        <v>-733.8140187312594</v>
       </c>
       <c r="D74">
-        <v>411.982725279682</v>
+        <v>406.8519812687407</v>
       </c>
       <c r="E74">
-        <v>385.3240000000001</v>
+        <v>402.2660000000001</v>
       </c>
       <c r="F74">
-        <v>1219.824</v>
+        <v>1236.766</v>
       </c>
       <c r="G74">
         <v>96.09999999999999</v>
@@ -7361,37 +7361,37 @@
         <v>136.125</v>
       </c>
       <c r="M74">
-        <v>244.9406592</v>
+        <v>248.3426128</v>
       </c>
       <c r="N74">
-        <v>-108.8156592000001</v>
+        <v>-112.2176128</v>
       </c>
       <c r="O74">
-        <v>-27.13862540448002</v>
+        <v>-27.98707263232001</v>
       </c>
       <c r="P74">
-        <v>-81.67703379552003</v>
+        <v>-84.23054016768003</v>
       </c>
       <c r="Q74">
-        <v>16.82296620447997</v>
+        <v>14.26945983231997</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1577602367772546</v>
+        <v>0.1619069122134492</v>
       </c>
       <c r="T74">
-        <v>2.585686761599413</v>
+        <v>2.681452937954946</v>
       </c>
       <c r="U74">
         <v>0.2008</v>
       </c>
       <c r="V74">
-        <v>0.1386032646065484</v>
+        <v>0.1367045897489244</v>
       </c>
       <c r="W74">
-        <v>0.1729684644670051</v>
+        <v>0.173349718378416</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.5557468508682775</v>
+        <v>0.548133880308438</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7407,22 +7407,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1702601607138749</v>
+        <v>0.1718101607138749</v>
       </c>
       <c r="C75">
-        <v>-733.8140187312594</v>
+        <v>-755.7605403301047</v>
       </c>
       <c r="D75">
-        <v>406.8519812687407</v>
+        <v>401.8474596698953</v>
       </c>
       <c r="E75">
-        <v>402.2660000000001</v>
+        <v>419.2080000000001</v>
       </c>
       <c r="F75">
-        <v>1236.766</v>
+        <v>1253.708</v>
       </c>
       <c r="G75">
         <v>96.09999999999999</v>
@@ -7443,37 +7443,37 @@
         <v>136.125</v>
       </c>
       <c r="M75">
-        <v>248.3426128</v>
+        <v>251.7445664</v>
       </c>
       <c r="N75">
-        <v>-112.2176128</v>
+        <v>-115.6195664000001</v>
       </c>
       <c r="O75">
-        <v>-27.98707263232001</v>
+        <v>-28.83551986016002</v>
       </c>
       <c r="P75">
-        <v>-84.23054016768003</v>
+        <v>-86.78404653984003</v>
       </c>
       <c r="Q75">
-        <v>14.26945983231997</v>
+        <v>11.71595346015997</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1619069122134492</v>
+        <v>0.1663725626831972</v>
       </c>
       <c r="T75">
-        <v>2.681452937954946</v>
+        <v>2.784585743260906</v>
       </c>
       <c r="U75">
         <v>0.2008</v>
       </c>
       <c r="V75">
-        <v>0.1367045897489244</v>
+        <v>0.134857230427993</v>
       </c>
       <c r="W75">
-        <v>0.173349718378416</v>
+        <v>0.173720668130059</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.548133880308438</v>
+        <v>0.5407266657096753</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7489,22 +7489,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1718101607138749</v>
+        <v>0.1733601607138749</v>
       </c>
       <c r="C76">
-        <v>-755.7605403301047</v>
+        <v>-777.5854407513848</v>
       </c>
       <c r="D76">
-        <v>401.8474596698953</v>
+        <v>396.9645592486153</v>
       </c>
       <c r="E76">
-        <v>419.2080000000001</v>
+        <v>436.1500000000001</v>
       </c>
       <c r="F76">
-        <v>1253.708</v>
+        <v>1270.65</v>
       </c>
       <c r="G76">
         <v>96.09999999999999</v>
@@ -7525,37 +7525,37 @@
         <v>136.125</v>
       </c>
       <c r="M76">
-        <v>251.7445664</v>
+        <v>255.14652</v>
       </c>
       <c r="N76">
-        <v>-115.6195664000001</v>
+        <v>-119.0215200000001</v>
       </c>
       <c r="O76">
-        <v>-28.83551986016002</v>
+        <v>-29.68396708800002</v>
       </c>
       <c r="P76">
-        <v>-86.78404653984003</v>
+        <v>-89.33755291200005</v>
       </c>
       <c r="Q76">
-        <v>11.71595346015997</v>
+        <v>9.162447087999951</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1663725626831972</v>
+        <v>0.1711954651905251</v>
       </c>
       <c r="T76">
-        <v>2.784585743260906</v>
+        <v>2.895969172991343</v>
       </c>
       <c r="U76">
         <v>0.2008</v>
       </c>
       <c r="V76">
-        <v>0.134857230427993</v>
+        <v>0.1330591340222864</v>
       </c>
       <c r="W76">
-        <v>0.173720668130059</v>
+        <v>0.1740817258883249</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.5407266657096753</v>
+        <v>0.5335169768335463</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7571,22 +7571,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1733601607138749</v>
+        <v>0.1749101607138749</v>
       </c>
       <c r="C77">
-        <v>-777.5854407513848</v>
+        <v>-799.2931002737126</v>
       </c>
       <c r="D77">
-        <v>396.9645592486153</v>
+        <v>392.1988997262874</v>
       </c>
       <c r="E77">
-        <v>436.1500000000001</v>
+        <v>453.0920000000001</v>
       </c>
       <c r="F77">
-        <v>1270.65</v>
+        <v>1287.592</v>
       </c>
       <c r="G77">
         <v>96.09999999999999</v>
@@ -7607,37 +7607,37 @@
         <v>136.125</v>
       </c>
       <c r="M77">
-        <v>255.14652</v>
+        <v>258.5484736</v>
       </c>
       <c r="N77">
-        <v>-119.0215200000001</v>
+        <v>-122.4234736000001</v>
       </c>
       <c r="O77">
-        <v>-29.68396708800002</v>
+        <v>-30.53241431584001</v>
       </c>
       <c r="P77">
-        <v>-89.33755291200005</v>
+        <v>-91.89105928416004</v>
       </c>
       <c r="Q77">
-        <v>9.162447087999951</v>
+        <v>6.608940715839964</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1711954651905251</v>
+        <v>0.1764202762401303</v>
       </c>
       <c r="T77">
-        <v>2.895969172991343</v>
+        <v>3.016634555199315</v>
       </c>
       <c r="U77">
         <v>0.2008</v>
       </c>
       <c r="V77">
-        <v>0.1330591340222864</v>
+        <v>0.1313083559430459</v>
       </c>
       <c r="W77">
-        <v>0.1740817258883249</v>
+        <v>0.1744332821266364</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.5335169768335463</v>
+        <v>0.5264970166120523</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7653,22 +7653,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1749101607138749</v>
+        <v>0.1764601607138749</v>
       </c>
       <c r="C78">
-        <v>-799.2931002737126</v>
+        <v>-820.8876913256015</v>
       </c>
       <c r="D78">
-        <v>392.1988997262874</v>
+        <v>387.5463086743986</v>
       </c>
       <c r="E78">
-        <v>453.0920000000001</v>
+        <v>470.0340000000001</v>
       </c>
       <c r="F78">
-        <v>1287.592</v>
+        <v>1304.534</v>
       </c>
       <c r="G78">
         <v>96.09999999999999</v>
@@ -7689,37 +7689,37 @@
         <v>136.125</v>
       </c>
       <c r="M78">
-        <v>258.5484736</v>
+        <v>261.9504272</v>
       </c>
       <c r="N78">
-        <v>-122.4234736000001</v>
+        <v>-125.8254272000001</v>
       </c>
       <c r="O78">
-        <v>-30.53241431584001</v>
+        <v>-31.38086154368002</v>
       </c>
       <c r="P78">
-        <v>-91.89105928416004</v>
+        <v>-94.44456565632005</v>
       </c>
       <c r="Q78">
-        <v>6.608940715839964</v>
+        <v>4.055434343679948</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1764202762401303</v>
+        <v>0.1820994186853534</v>
       </c>
       <c r="T78">
-        <v>3.016634555199315</v>
+        <v>3.147792579338416</v>
       </c>
       <c r="U78">
         <v>0.2008</v>
       </c>
       <c r="V78">
-        <v>0.1313083559430459</v>
+        <v>0.1296030526191102</v>
       </c>
       <c r="W78">
-        <v>0.1744332821266364</v>
+        <v>0.1747757070340827</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.5264970166120523</v>
+        <v>0.519659393019688</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7735,22 +7735,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1764601607138749</v>
+        <v>0.178010160713875</v>
       </c>
       <c r="C79">
-        <v>-820.8876913256015</v>
+        <v>-842.3731906693876</v>
       </c>
       <c r="D79">
-        <v>387.5463086743986</v>
+        <v>383.0028093306125</v>
       </c>
       <c r="E79">
-        <v>470.0340000000001</v>
+        <v>486.9760000000001</v>
       </c>
       <c r="F79">
-        <v>1304.534</v>
+        <v>1321.476</v>
       </c>
       <c r="G79">
         <v>96.09999999999999</v>
@@ -7771,37 +7771,37 @@
         <v>136.125</v>
       </c>
       <c r="M79">
-        <v>261.9504272</v>
+        <v>265.3523808</v>
       </c>
       <c r="N79">
-        <v>-125.8254272000001</v>
+        <v>-129.2273808000001</v>
       </c>
       <c r="O79">
-        <v>-31.38086154368002</v>
+        <v>-32.22930877152002</v>
       </c>
       <c r="P79">
-        <v>-94.44456565632005</v>
+        <v>-96.99807202848007</v>
       </c>
       <c r="Q79">
-        <v>4.055434343679948</v>
+        <v>1.501927971519933</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1820994186853534</v>
+        <v>0.1882948468074149</v>
       </c>
       <c r="T79">
-        <v>3.147792579338416</v>
+        <v>3.290874060217435</v>
       </c>
       <c r="U79">
         <v>0.2008</v>
       </c>
       <c r="V79">
-        <v>0.1296030526191102</v>
+        <v>0.1279414750214293</v>
       </c>
       <c r="W79">
-        <v>0.1747757070340827</v>
+        <v>0.175109351815697</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.519659393019688</v>
+        <v>0.5129970931091791</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7817,22 +7817,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.178010160713875</v>
+        <v>0.179560160713875</v>
       </c>
       <c r="C80">
-        <v>-842.3731906693876</v>
+        <v>-863.7533907380338</v>
       </c>
       <c r="D80">
-        <v>383.0028093306125</v>
+        <v>378.5646092619664</v>
       </c>
       <c r="E80">
-        <v>486.9760000000001</v>
+        <v>503.9180000000001</v>
       </c>
       <c r="F80">
-        <v>1321.476</v>
+        <v>1338.418</v>
       </c>
       <c r="G80">
         <v>96.09999999999999</v>
@@ -7853,37 +7853,37 @@
         <v>136.125</v>
       </c>
       <c r="M80">
-        <v>265.3523808</v>
+        <v>268.7543344</v>
       </c>
       <c r="N80">
-        <v>-129.2273808000001</v>
+        <v>-132.6293344</v>
       </c>
       <c r="O80">
-        <v>-32.22930877152002</v>
+        <v>-33.07775599936001</v>
       </c>
       <c r="P80">
-        <v>-96.99807202848007</v>
+        <v>-99.55157840064003</v>
       </c>
       <c r="Q80">
-        <v>1.501927971519933</v>
+        <v>-1.051578400640025</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1882948468074149</v>
+        <v>0.1950803157030061</v>
       </c>
       <c r="T80">
-        <v>3.290874060217435</v>
+        <v>3.447582348799218</v>
       </c>
       <c r="U80">
         <v>0.2008</v>
       </c>
       <c r="V80">
-        <v>0.1279414750214293</v>
+        <v>0.1263219626793859</v>
       </c>
       <c r="W80">
-        <v>0.175109351815697</v>
+        <v>0.1754345498939793</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.5129970931091791</v>
+        <v>0.5065034590191896</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7899,22 +7899,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.179560160713875</v>
+        <v>0.181110160713875</v>
       </c>
       <c r="C81">
-        <v>-863.7533907380338</v>
+        <v>-885.0319101927466</v>
       </c>
       <c r="D81">
-        <v>378.5646092619664</v>
+        <v>374.2280898072535</v>
       </c>
       <c r="E81">
-        <v>503.9180000000001</v>
+        <v>520.8600000000001</v>
       </c>
       <c r="F81">
-        <v>1338.418</v>
+        <v>1355.36</v>
       </c>
       <c r="G81">
         <v>96.09999999999999</v>
@@ -7935,37 +7935,37 @@
         <v>136.125</v>
       </c>
       <c r="M81">
-        <v>268.7543344</v>
+        <v>272.156288</v>
       </c>
       <c r="N81">
-        <v>-132.6293344</v>
+        <v>-136.031288</v>
       </c>
       <c r="O81">
-        <v>-33.07775599936001</v>
+        <v>-33.92620322720001</v>
       </c>
       <c r="P81">
-        <v>-99.55157840064003</v>
+        <v>-102.1050847728</v>
       </c>
       <c r="Q81">
-        <v>-1.051578400640025</v>
+        <v>-3.605084772800041</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1950803157030061</v>
+        <v>0.2025443314881564</v>
       </c>
       <c r="T81">
-        <v>3.447582348799218</v>
+        <v>3.619961466239179</v>
       </c>
       <c r="U81">
         <v>0.2008</v>
       </c>
       <c r="V81">
-        <v>0.1263219626793859</v>
+        <v>0.1247429381458935</v>
       </c>
       <c r="W81">
-        <v>0.1754345498939793</v>
+        <v>0.1757516180203046</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.5065034590191896</v>
+        <v>0.5001721657814497</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7981,22 +7981,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.181110160713875</v>
+        <v>0.2115259951186807</v>
       </c>
       <c r="C82">
-        <v>-885.0319101927466</v>
+        <v>-970.656313342916</v>
       </c>
       <c r="D82">
-        <v>374.2280898072535</v>
+        <v>305.5456866570842</v>
       </c>
       <c r="E82">
-        <v>520.8600000000001</v>
+        <v>537.8020000000001</v>
       </c>
       <c r="F82">
-        <v>1355.36</v>
+        <v>1372.302</v>
       </c>
       <c r="G82">
         <v>96.09999999999999</v>
@@ -8017,45 +8017,45 @@
         <v>136.125</v>
       </c>
       <c r="M82">
-        <v>272.156288</v>
+        <v>323.5888116</v>
       </c>
       <c r="N82">
-        <v>-136.031288</v>
+        <v>-187.4638116000001</v>
       </c>
       <c r="O82">
-        <v>-33.92620322720001</v>
+        <v>-46.75347461304002</v>
       </c>
       <c r="P82">
-        <v>-102.1050847728</v>
+        <v>-140.71033698696</v>
       </c>
       <c r="Q82">
-        <v>-3.605084772800041</v>
+        <v>-42.21033698696004</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2025443314881564</v>
+        <v>0.2135089510654581</v>
       </c>
       <c r="T82">
-        <v>3.619961466239179</v>
+        <v>3.873185936846608</v>
       </c>
       <c r="U82">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.1247429381458935</v>
+        <v>0.1049157875148239</v>
       </c>
       <c r="W82">
-        <v>0.1757516180203046</v>
+        <v>0.2110608573040045</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y82">
-        <v>0.5001721657814497</v>
+        <v>0.4206727646945626</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8063,22 +8063,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2115259951186807</v>
+        <v>0.2134259951186807</v>
       </c>
       <c r="C83">
-        <v>-970.656313342916</v>
+        <v>-991.0615995965632</v>
       </c>
       <c r="D83">
-        <v>305.5456866570842</v>
+        <v>302.082400403437</v>
       </c>
       <c r="E83">
-        <v>537.8020000000001</v>
+        <v>554.7440000000001</v>
       </c>
       <c r="F83">
-        <v>1372.302</v>
+        <v>1389.244</v>
       </c>
       <c r="G83">
         <v>96.09999999999999</v>
@@ -8099,37 +8099,37 @@
         <v>136.125</v>
       </c>
       <c r="M83">
-        <v>323.5888116</v>
+        <v>327.5837352</v>
       </c>
       <c r="N83">
-        <v>-187.4638116000001</v>
+        <v>-191.4587352000001</v>
       </c>
       <c r="O83">
-        <v>-46.75347461304002</v>
+        <v>-47.74980855888002</v>
       </c>
       <c r="P83">
-        <v>-140.71033698696</v>
+        <v>-143.7089266411201</v>
       </c>
       <c r="Q83">
-        <v>-42.21033698696004</v>
+        <v>-45.20892664112006</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2135089510654581</v>
+        <v>0.2228261150135391</v>
       </c>
       <c r="T83">
-        <v>3.873185936846608</v>
+        <v>4.088362933338086</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.1049157875148239</v>
+        <v>0.1036363266914724</v>
       </c>
       <c r="W83">
-        <v>0.2110608573040045</v>
+        <v>0.2113625541661508</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.4206727646945626</v>
+        <v>0.4155426090275558</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8145,22 +8145,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2134259951186807</v>
+        <v>0.2153259951186807</v>
       </c>
       <c r="C84">
-        <v>-991.0615995965632</v>
+        <v>-1011.389254760331</v>
       </c>
       <c r="D84">
-        <v>302.082400403437</v>
+        <v>298.6967452396688</v>
       </c>
       <c r="E84">
-        <v>554.7440000000001</v>
+        <v>571.6860000000001</v>
       </c>
       <c r="F84">
-        <v>1389.244</v>
+        <v>1406.186</v>
       </c>
       <c r="G84">
         <v>96.09999999999999</v>
@@ -8181,37 +8181,37 @@
         <v>136.125</v>
       </c>
       <c r="M84">
-        <v>327.5837352</v>
+        <v>331.5786588</v>
       </c>
       <c r="N84">
-        <v>-191.4587352000001</v>
+        <v>-195.4536588000001</v>
       </c>
       <c r="O84">
-        <v>-47.74980855888002</v>
+        <v>-48.74614250472002</v>
       </c>
       <c r="P84">
-        <v>-143.7089266411201</v>
+        <v>-146.70751629528</v>
       </c>
       <c r="Q84">
-        <v>-45.20892664112006</v>
+        <v>-48.20751629528004</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2228261150135391</v>
+        <v>0.2332394158966885</v>
       </c>
       <c r="T84">
-        <v>4.088362933338086</v>
+        <v>4.328854870593268</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.1036363266914724</v>
+        <v>0.1023876962494065</v>
       </c>
       <c r="W84">
-        <v>0.2113625541661508</v>
+        <v>0.21165698122439</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.4155426090275558</v>
+        <v>0.4105360715693924</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8227,22 +8227,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2153259951186807</v>
+        <v>0.2172259951186807</v>
       </c>
       <c r="C85">
-        <v>-1011.389254760331</v>
+        <v>-1031.641860106752</v>
       </c>
       <c r="D85">
-        <v>298.6967452396688</v>
+        <v>295.3861398932481</v>
       </c>
       <c r="E85">
-        <v>571.6860000000001</v>
+        <v>588.6280000000002</v>
       </c>
       <c r="F85">
-        <v>1406.186</v>
+        <v>1423.128</v>
       </c>
       <c r="G85">
         <v>96.09999999999999</v>
@@ -8263,37 +8263,37 @@
         <v>136.125</v>
       </c>
       <c r="M85">
-        <v>331.5786588</v>
+        <v>335.5735824000001</v>
       </c>
       <c r="N85">
-        <v>-195.4536588000001</v>
+        <v>-199.4485824000001</v>
       </c>
       <c r="O85">
-        <v>-48.74614250472002</v>
+        <v>-49.74247645056003</v>
       </c>
       <c r="P85">
-        <v>-146.70751629528</v>
+        <v>-149.7061059494401</v>
       </c>
       <c r="Q85">
-        <v>-48.20751629528004</v>
+        <v>-51.20610594944009</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2332394158966885</v>
+        <v>0.2449543793902316</v>
       </c>
       <c r="T85">
-        <v>4.328854870593268</v>
+        <v>4.599408300005349</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.1023876962494065</v>
+        <v>0.1011687951035802</v>
       </c>
       <c r="W85">
-        <v>0.21165698122439</v>
+        <v>0.2119443981145758</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8301,7 +8301,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.4105360715693924</v>
+        <v>0.4056487373840425</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8309,22 +8309,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2172259951186807</v>
+        <v>0.2191259951186807</v>
       </c>
       <c r="C86">
-        <v>-1031.641860106752</v>
+        <v>-1051.821883724691</v>
       </c>
       <c r="D86">
-        <v>295.3861398932482</v>
+        <v>292.1481162753086</v>
       </c>
       <c r="E86">
-        <v>588.6279999999999</v>
+        <v>605.5699999999999</v>
       </c>
       <c r="F86">
-        <v>1423.128</v>
+        <v>1440.07</v>
       </c>
       <c r="G86">
         <v>96.09999999999999</v>
@@ -8345,37 +8345,37 @@
         <v>136.125</v>
       </c>
       <c r="M86">
-        <v>335.5735824</v>
+        <v>339.568506</v>
       </c>
       <c r="N86">
-        <v>-199.4485824</v>
+        <v>-203.443506</v>
       </c>
       <c r="O86">
-        <v>-49.74247645056001</v>
+        <v>-50.73881039640001</v>
       </c>
       <c r="P86">
-        <v>-149.70610594944</v>
+        <v>-152.7046956036</v>
       </c>
       <c r="Q86">
-        <v>-51.20610594944003</v>
+        <v>-54.20469560360004</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2449543793902314</v>
+        <v>0.2582313380162468</v>
       </c>
       <c r="T86">
-        <v>4.599408300005345</v>
+        <v>4.906035520005702</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.1011687951035802</v>
+        <v>0.09997857398471456</v>
       </c>
       <c r="W86">
-        <v>0.2119443981145758</v>
+        <v>0.2122250522544043</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.4056487373840425</v>
+        <v>0.4008763992971714</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8391,22 +8391,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2191259951186807</v>
+        <v>0.2210259951186807</v>
       </c>
       <c r="C87">
-        <v>-1051.821883724691</v>
+        <v>-1071.931686655684</v>
       </c>
       <c r="D87">
-        <v>292.1481162753086</v>
+        <v>288.9803133443158</v>
       </c>
       <c r="E87">
-        <v>605.5699999999999</v>
+        <v>622.5119999999999</v>
       </c>
       <c r="F87">
-        <v>1440.07</v>
+        <v>1457.012</v>
       </c>
       <c r="G87">
         <v>96.09999999999999</v>
@@ -8427,37 +8427,37 @@
         <v>136.125</v>
       </c>
       <c r="M87">
-        <v>339.568506</v>
+        <v>343.5634296</v>
       </c>
       <c r="N87">
-        <v>-203.443506</v>
+        <v>-207.4384296</v>
       </c>
       <c r="O87">
-        <v>-50.73881039640001</v>
+        <v>-51.73514434224001</v>
       </c>
       <c r="P87">
-        <v>-152.7046956036</v>
+        <v>-155.70328525776</v>
       </c>
       <c r="Q87">
-        <v>-54.20469560360004</v>
+        <v>-57.20328525776003</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2582313380162468</v>
+        <v>0.2734050050174073</v>
       </c>
       <c r="T87">
-        <v>4.906035520005702</v>
+        <v>5.256466628577538</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.09997857398471456</v>
+        <v>0.09881603242675277</v>
       </c>
       <c r="W87">
-        <v>0.2122250522544043</v>
+        <v>0.2124991795537717</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8465,7 +8465,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.4008763992971714</v>
+        <v>0.3962150458169718</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8473,22 +8473,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2210259951186807</v>
+        <v>0.2229259951186807</v>
       </c>
       <c r="C88">
-        <v>-1071.931686655684</v>
+        <v>-1091.973528635323</v>
       </c>
       <c r="D88">
-        <v>288.9803133443158</v>
+        <v>285.8804713646768</v>
       </c>
       <c r="E88">
-        <v>622.5119999999999</v>
+        <v>639.454</v>
       </c>
       <c r="F88">
-        <v>1457.012</v>
+        <v>1473.954</v>
       </c>
       <c r="G88">
         <v>96.09999999999999</v>
@@ -8509,37 +8509,37 @@
         <v>136.125</v>
       </c>
       <c r="M88">
-        <v>343.5634296</v>
+        <v>347.5583532</v>
       </c>
       <c r="N88">
-        <v>-207.4384296</v>
+        <v>-211.4333532</v>
       </c>
       <c r="O88">
-        <v>-51.73514434224001</v>
+        <v>-52.73147828808001</v>
       </c>
       <c r="P88">
-        <v>-155.70328525776</v>
+        <v>-158.70187491192</v>
       </c>
       <c r="Q88">
-        <v>-57.20328525776003</v>
+        <v>-60.20187491192002</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2734050050174073</v>
+        <v>0.2909130823264387</v>
       </c>
       <c r="T88">
-        <v>5.256466628577538</v>
+        <v>5.660810215391195</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.09881603242675277</v>
+        <v>0.09768021596207746</v>
       </c>
       <c r="W88">
-        <v>0.2124991795537717</v>
+        <v>0.2127670050761422</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3962150458169718</v>
+        <v>0.3916608498880411</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8555,22 +8555,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2229259951186807</v>
+        <v>0.2248259951186807</v>
       </c>
       <c r="C89">
-        <v>-1091.973528635323</v>
+        <v>-1111.949573469051</v>
       </c>
       <c r="D89">
-        <v>285.8804713646768</v>
+        <v>282.8464265309487</v>
       </c>
       <c r="E89">
-        <v>639.454</v>
+        <v>656.396</v>
       </c>
       <c r="F89">
-        <v>1473.954</v>
+        <v>1490.896</v>
       </c>
       <c r="G89">
         <v>96.09999999999999</v>
@@ -8591,37 +8591,37 @@
         <v>136.125</v>
       </c>
       <c r="M89">
-        <v>347.5583532</v>
+        <v>351.5532768</v>
       </c>
       <c r="N89">
-        <v>-211.4333532</v>
+        <v>-215.4282768</v>
       </c>
       <c r="O89">
-        <v>-52.73147828808001</v>
+        <v>-53.72781223392001</v>
       </c>
       <c r="P89">
-        <v>-158.70187491192</v>
+        <v>-161.70046456608</v>
       </c>
       <c r="Q89">
-        <v>-60.20187491192002</v>
+        <v>-63.20046456608003</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2909130823264387</v>
+        <v>0.3113391725203086</v>
       </c>
       <c r="T89">
-        <v>5.660810215391195</v>
+        <v>6.132544400007129</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.09768021596207746</v>
+        <v>0.09657021350796294</v>
       </c>
       <c r="W89">
-        <v>0.2127670050761422</v>
+        <v>0.2130287436548224</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3916608498880411</v>
+        <v>0.3872101584120407</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8637,22 +8637,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2248259951186807</v>
+        <v>0.2267259951186807</v>
       </c>
       <c r="C90">
-        <v>-1111.949573469051</v>
+        <v>-1131.86189406923</v>
       </c>
       <c r="D90">
-        <v>282.8464265309487</v>
+        <v>279.8761059307702</v>
       </c>
       <c r="E90">
-        <v>656.396</v>
+        <v>673.338</v>
       </c>
       <c r="F90">
-        <v>1490.896</v>
+        <v>1507.838</v>
       </c>
       <c r="G90">
         <v>96.09999999999999</v>
@@ -8673,37 +8673,37 @@
         <v>136.125</v>
       </c>
       <c r="M90">
-        <v>351.5532768</v>
+        <v>355.5482004</v>
       </c>
       <c r="N90">
-        <v>-215.4282768</v>
+        <v>-219.4232004</v>
       </c>
       <c r="O90">
-        <v>-53.72781223392001</v>
+        <v>-54.72414617976001</v>
       </c>
       <c r="P90">
-        <v>-161.70046456608</v>
+        <v>-164.69905422024</v>
       </c>
       <c r="Q90">
-        <v>-63.20046456608003</v>
+        <v>-66.19905422024001</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3113391725203086</v>
+        <v>0.3354790972948821</v>
       </c>
       <c r="T90">
-        <v>6.132544400007129</v>
+        <v>6.690048436371413</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.09657021350796294</v>
+        <v>0.09548515492922179</v>
       </c>
       <c r="W90">
-        <v>0.2130287436548224</v>
+        <v>0.2132846004676895</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3872101584120407</v>
+        <v>0.3828594824748267</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8719,22 +8719,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2267259951186807</v>
+        <v>0.2286259951186807</v>
       </c>
       <c r="C91">
-        <v>-1131.86189406923</v>
+        <v>-1151.712477178121</v>
       </c>
       <c r="D91">
-        <v>279.8761059307702</v>
+        <v>276.9675228218788</v>
       </c>
       <c r="E91">
-        <v>673.338</v>
+        <v>690.28</v>
       </c>
       <c r="F91">
-        <v>1507.838</v>
+        <v>1524.78</v>
       </c>
       <c r="G91">
         <v>96.09999999999999</v>
@@ -8755,37 +8755,37 @@
         <v>136.125</v>
       </c>
       <c r="M91">
-        <v>355.5482004</v>
+        <v>359.543124</v>
       </c>
       <c r="N91">
-        <v>-219.4232004</v>
+        <v>-223.4181240000001</v>
       </c>
       <c r="O91">
-        <v>-54.72414617976001</v>
+        <v>-55.72048012560002</v>
       </c>
       <c r="P91">
-        <v>-164.69905422024</v>
+        <v>-167.6976438744001</v>
       </c>
       <c r="Q91">
-        <v>-66.19905422024001</v>
+        <v>-69.19764387440006</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3354790972948821</v>
+        <v>0.3644470070243704</v>
       </c>
       <c r="T91">
-        <v>6.690048436371413</v>
+        <v>7.359053280008555</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.09548515492922179</v>
+        <v>0.09442420876334154</v>
       </c>
       <c r="W91">
-        <v>0.2132846004676895</v>
+        <v>0.2135347715736041</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3828594824748267</v>
+        <v>0.3786054882251063</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8801,22 +8801,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2286259951186807</v>
+        <v>0.2305259951186807</v>
       </c>
       <c r="C92">
-        <v>-1151.712477178121</v>
+        <v>-1171.503227799405</v>
       </c>
       <c r="D92">
-        <v>276.9675228218788</v>
+        <v>274.1187722005951</v>
       </c>
       <c r="E92">
-        <v>690.28</v>
+        <v>707.2220000000002</v>
       </c>
       <c r="F92">
-        <v>1524.78</v>
+        <v>1541.722</v>
       </c>
       <c r="G92">
         <v>96.09999999999999</v>
@@ -8837,37 +8837,37 @@
         <v>136.125</v>
       </c>
       <c r="M92">
-        <v>359.543124</v>
+        <v>363.5380476000001</v>
       </c>
       <c r="N92">
-        <v>-223.4181240000001</v>
+        <v>-227.4130476000001</v>
       </c>
       <c r="O92">
-        <v>-55.72048012560002</v>
+        <v>-56.71681407144003</v>
       </c>
       <c r="P92">
-        <v>-167.6976438744001</v>
+        <v>-170.6962335285601</v>
       </c>
       <c r="Q92">
-        <v>-69.19764387440006</v>
+        <v>-72.19623352856007</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.3644470070243704</v>
+        <v>0.3998522300270782</v>
       </c>
       <c r="T92">
-        <v>7.359053280008555</v>
+        <v>8.176725866676172</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.09442420876334154</v>
+        <v>0.09338658009561249</v>
       </c>
       <c r="W92">
-        <v>0.2135347715736041</v>
+        <v>0.2137794444134546</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3786054882251063</v>
+        <v>0.3744449883545008</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8883,22 +8883,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2305259951186807</v>
+        <v>0.2324259951186807</v>
       </c>
       <c r="C93">
-        <v>-1171.503227799405</v>
+        <v>-1191.235973358993</v>
       </c>
       <c r="D93">
-        <v>274.1187722005951</v>
+        <v>271.3280266410072</v>
       </c>
       <c r="E93">
-        <v>707.2220000000002</v>
+        <v>724.1640000000002</v>
       </c>
       <c r="F93">
-        <v>1541.722</v>
+        <v>1558.664</v>
       </c>
       <c r="G93">
         <v>96.09999999999999</v>
@@ -8919,37 +8919,37 @@
         <v>136.125</v>
       </c>
       <c r="M93">
-        <v>363.5380476000001</v>
+        <v>367.5329712000001</v>
       </c>
       <c r="N93">
-        <v>-227.4130476000001</v>
+        <v>-231.4079712000001</v>
       </c>
       <c r="O93">
-        <v>-56.71681407144003</v>
+        <v>-57.71314801728003</v>
       </c>
       <c r="P93">
-        <v>-170.6962335285601</v>
+        <v>-173.6948231827201</v>
       </c>
       <c r="Q93">
-        <v>-72.19623352856007</v>
+        <v>-75.19482318272009</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.3998522300270782</v>
+        <v>0.4441087587804631</v>
       </c>
       <c r="T93">
-        <v>8.176725866676172</v>
+        <v>9.198816600010698</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.09338658009561249</v>
+        <v>0.09237150857283409</v>
       </c>
       <c r="W93">
-        <v>0.2137794444134546</v>
+        <v>0.2140187982785257</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3744449883545008</v>
+        <v>0.3703749341332562</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8965,22 +8965,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2324259951186807</v>
+        <v>0.2343259951186807</v>
       </c>
       <c r="C94">
-        <v>-1191.235973358993</v>
+        <v>-1210.912467614246</v>
       </c>
       <c r="D94">
-        <v>271.3280266410072</v>
+        <v>268.5935323857542</v>
       </c>
       <c r="E94">
-        <v>724.1640000000002</v>
+        <v>741.1060000000002</v>
       </c>
       <c r="F94">
-        <v>1558.664</v>
+        <v>1575.606</v>
       </c>
       <c r="G94">
         <v>96.09999999999999</v>
@@ -9001,37 +9001,37 @@
         <v>136.125</v>
       </c>
       <c r="M94">
-        <v>367.5329712000001</v>
+        <v>371.5278948000001</v>
       </c>
       <c r="N94">
-        <v>-231.4079712000001</v>
+        <v>-235.4028948000001</v>
       </c>
       <c r="O94">
-        <v>-57.71314801728003</v>
+        <v>-58.70948196312003</v>
       </c>
       <c r="P94">
-        <v>-173.6948231827201</v>
+        <v>-176.6934128368801</v>
       </c>
       <c r="Q94">
-        <v>-75.19482318272009</v>
+        <v>-78.19341283688007</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.4441087587804631</v>
+        <v>0.501010010034815</v>
       </c>
       <c r="T94">
-        <v>9.198816600010698</v>
+        <v>10.51293325715508</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.09237150857283409</v>
+        <v>0.09137826654516921</v>
       </c>
       <c r="W94">
-        <v>0.2140187982785257</v>
+        <v>0.2142530047486491</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3703749341332562</v>
+        <v>0.3663924079597803</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9047,22 +9047,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2343259951186807</v>
+        <v>0.2362259951186807</v>
       </c>
       <c r="C95">
-        <v>-1210.912467614246</v>
+        <v>-1230.534394329162</v>
       </c>
       <c r="D95">
-        <v>268.5935323857542</v>
+        <v>265.9136056708386</v>
       </c>
       <c r="E95">
-        <v>741.1060000000002</v>
+        <v>758.0480000000002</v>
       </c>
       <c r="F95">
-        <v>1575.606</v>
+        <v>1592.548</v>
       </c>
       <c r="G95">
         <v>96.09999999999999</v>
@@ -9083,37 +9083,37 @@
         <v>136.125</v>
       </c>
       <c r="M95">
-        <v>371.5278948000001</v>
+        <v>375.5228184000001</v>
       </c>
       <c r="N95">
-        <v>-235.4028948000001</v>
+        <v>-239.3978184000001</v>
       </c>
       <c r="O95">
-        <v>-58.70948196312003</v>
+        <v>-59.70581590896003</v>
       </c>
       <c r="P95">
-        <v>-176.6934128368801</v>
+        <v>-179.6920024910401</v>
       </c>
       <c r="Q95">
-        <v>-78.19341283688007</v>
+        <v>-81.19200249104006</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.501010010034815</v>
+        <v>0.5768783450406176</v>
       </c>
       <c r="T95">
-        <v>10.51293325715508</v>
+        <v>12.26508880001427</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.09137826654516921</v>
+        <v>0.09040615732660358</v>
       </c>
       <c r="W95">
-        <v>0.2142530047486491</v>
+        <v>0.2144822281023869</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3663924079597803</v>
+        <v>0.3624946163857401</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9129,22 +9129,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2362259951186807</v>
+        <v>0.2381259951186807</v>
       </c>
       <c r="C96">
-        <v>-1230.534394329162</v>
+        <v>-1250.103370731716</v>
       </c>
       <c r="D96">
-        <v>265.9136056708386</v>
+        <v>263.286629268284</v>
       </c>
       <c r="E96">
-        <v>758.0480000000002</v>
+        <v>774.9900000000002</v>
       </c>
       <c r="F96">
-        <v>1592.548</v>
+        <v>1609.49</v>
       </c>
       <c r="G96">
         <v>96.09999999999999</v>
@@ -9165,37 +9165,37 @@
         <v>136.125</v>
       </c>
       <c r="M96">
-        <v>375.5228184000001</v>
+        <v>379.5177420000001</v>
       </c>
       <c r="N96">
-        <v>-239.3978184000001</v>
+        <v>-243.3927420000001</v>
       </c>
       <c r="O96">
-        <v>-59.70581590896003</v>
+        <v>-60.70214985480003</v>
       </c>
       <c r="P96">
-        <v>-179.6920024910401</v>
+        <v>-182.6905921452001</v>
       </c>
       <c r="Q96">
-        <v>-81.19200249104006</v>
+        <v>-84.19059214520007</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.5768783450406176</v>
+        <v>0.6830940140487415</v>
       </c>
       <c r="T96">
-        <v>12.26508880001427</v>
+        <v>14.71810656001713</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.09040615732660358</v>
+        <v>0.08945451356527093</v>
       </c>
       <c r="W96">
-        <v>0.2144822281023869</v>
+        <v>0.2147066257013091</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3624946163857401</v>
+        <v>0.3586788835816797</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9211,22 +9211,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2381259951186807</v>
+        <v>0.2400259951186807</v>
       </c>
       <c r="C97">
-        <v>-1250.103370731716</v>
+        <v>-1269.620950768282</v>
       </c>
       <c r="D97">
-        <v>263.286629268284</v>
+        <v>260.7110492317186</v>
       </c>
       <c r="E97">
-        <v>774.9900000000002</v>
+        <v>791.9320000000002</v>
       </c>
       <c r="F97">
-        <v>1609.49</v>
+        <v>1626.432</v>
       </c>
       <c r="G97">
         <v>96.09999999999999</v>
@@ -9247,37 +9247,37 @@
         <v>136.125</v>
       </c>
       <c r="M97">
-        <v>379.5177420000001</v>
+        <v>383.5126656</v>
       </c>
       <c r="N97">
-        <v>-243.3927420000001</v>
+        <v>-247.3876656000001</v>
       </c>
       <c r="O97">
-        <v>-60.70214985480003</v>
+        <v>-61.69848380064002</v>
       </c>
       <c r="P97">
-        <v>-182.6905921452001</v>
+        <v>-185.6891817993601</v>
       </c>
       <c r="Q97">
-        <v>-84.19059214520007</v>
+        <v>-87.18918179936006</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.6830940140487415</v>
+        <v>0.8424175175609272</v>
       </c>
       <c r="T97">
-        <v>14.71810656001713</v>
+        <v>18.39763320002142</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.08945451356527093</v>
+        <v>0.08852269571563268</v>
       </c>
       <c r="W97">
-        <v>0.2147066257013091</v>
+        <v>0.2149263483502538</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3586788835816797</v>
+        <v>0.3549426452110372</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9293,22 +9293,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2400259951186807</v>
+        <v>0.2419259951186807</v>
       </c>
       <c r="C98">
-        <v>-1269.620950768282</v>
+        <v>-1289.088628168875</v>
       </c>
       <c r="D98">
-        <v>260.7110492317186</v>
+        <v>258.1853718311245</v>
       </c>
       <c r="E98">
-        <v>791.932</v>
+        <v>808.874</v>
       </c>
       <c r="F98">
-        <v>1626.432</v>
+        <v>1643.374</v>
       </c>
       <c r="G98">
         <v>96.09999999999999</v>
@@ -9329,37 +9329,37 @@
         <v>136.125</v>
       </c>
       <c r="M98">
-        <v>383.5126656</v>
+        <v>387.5075892</v>
       </c>
       <c r="N98">
-        <v>-247.3876656</v>
+        <v>-251.3825892000001</v>
       </c>
       <c r="O98">
-        <v>-61.69848380064001</v>
+        <v>-62.69481774648002</v>
       </c>
       <c r="P98">
-        <v>-185.68918179936</v>
+        <v>-188.68777145352</v>
       </c>
       <c r="Q98">
-        <v>-87.18918179936003</v>
+        <v>-90.18777145352004</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.842417517560925</v>
+        <v>1.107956690081233</v>
       </c>
       <c r="T98">
-        <v>18.39763320002137</v>
+        <v>24.53017760002849</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.08852269571563269</v>
+        <v>0.08761009060516224</v>
       </c>
       <c r="W98">
-        <v>0.2149263483502538</v>
+        <v>0.2151415406353027</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3549426452110372</v>
+        <v>0.3512834426830884</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9375,22 +9375,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2419259951186807</v>
+        <v>0.2438259951186807</v>
       </c>
       <c r="C99">
-        <v>-1289.088628168875</v>
+        <v>-1308.50783933595</v>
       </c>
       <c r="D99">
-        <v>258.1853718311245</v>
+        <v>255.7081606640496</v>
       </c>
       <c r="E99">
-        <v>808.874</v>
+        <v>825.816</v>
       </c>
       <c r="F99">
-        <v>1643.374</v>
+        <v>1660.316</v>
       </c>
       <c r="G99">
         <v>96.09999999999999</v>
@@ -9411,37 +9411,37 @@
         <v>136.125</v>
       </c>
       <c r="M99">
-        <v>387.5075892</v>
+        <v>391.5025128</v>
       </c>
       <c r="N99">
-        <v>-251.3825892000001</v>
+        <v>-255.3775128000001</v>
       </c>
       <c r="O99">
-        <v>-62.69481774648002</v>
+        <v>-63.69115169232002</v>
       </c>
       <c r="P99">
-        <v>-188.68777145352</v>
+        <v>-191.6863611076801</v>
       </c>
       <c r="Q99">
-        <v>-90.18777145352004</v>
+        <v>-93.18636110768006</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.107956690081233</v>
+        <v>1.63903503512185</v>
       </c>
       <c r="T99">
-        <v>24.53017760002849</v>
+        <v>36.79526640004273</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.08761009060516224</v>
+        <v>0.08671611008878304</v>
       </c>
       <c r="W99">
-        <v>0.2151415406353027</v>
+        <v>0.215352341241065</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3512834426830884</v>
+        <v>0.3476989177577507</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9457,22 +9457,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2438259951186807</v>
+        <v>0.2457259951186807</v>
       </c>
       <c r="C100">
-        <v>-1308.50783933595</v>
+        <v>-1327.879966068461</v>
       </c>
       <c r="D100">
-        <v>255.7081606640496</v>
+        <v>253.2780339315389</v>
       </c>
       <c r="E100">
-        <v>825.816</v>
+        <v>842.758</v>
       </c>
       <c r="F100">
-        <v>1660.316</v>
+        <v>1677.258</v>
       </c>
       <c r="G100">
         <v>96.09999999999999</v>
@@ -9493,37 +9493,37 @@
         <v>136.125</v>
       </c>
       <c r="M100">
-        <v>391.5025128</v>
+        <v>395.4974364</v>
       </c>
       <c r="N100">
-        <v>-255.3775128000001</v>
+        <v>-259.3724364000001</v>
       </c>
       <c r="O100">
-        <v>-63.69115169232002</v>
+        <v>-64.68748563816003</v>
       </c>
       <c r="P100">
-        <v>-191.6863611076801</v>
+        <v>-194.6849507618401</v>
       </c>
       <c r="Q100">
-        <v>-93.18636110768006</v>
+        <v>-96.18495076184007</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.63903503512185</v>
+        <v>3.2322700702437</v>
       </c>
       <c r="T100">
-        <v>36.79526640004273</v>
+        <v>73.59053280008547</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.08671611008878304</v>
+        <v>0.08584018978485594</v>
       </c>
       <c r="W100">
-        <v>0.215352341241065</v>
+        <v>0.215558883248731</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9531,91 +9531,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3476989177577507</v>
+        <v>0.3441868074773694</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2457259951186807</v>
-      </c>
-      <c r="C101">
-        <v>-1327.879966068461</v>
-      </c>
-      <c r="D101">
-        <v>253.2780339315389</v>
-      </c>
-      <c r="E101">
-        <v>842.758</v>
-      </c>
-      <c r="F101">
-        <v>1677.258</v>
-      </c>
-      <c r="G101">
-        <v>96.09999999999999</v>
-      </c>
-      <c r="H101">
-        <v>859.7</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>234.625</v>
-      </c>
-      <c r="K101">
-        <v>98.5</v>
-      </c>
-      <c r="L101">
-        <v>136.125</v>
-      </c>
-      <c r="M101">
-        <v>395.4974364</v>
-      </c>
-      <c r="N101">
-        <v>-259.3724364000001</v>
-      </c>
-      <c r="O101">
-        <v>-64.68748563816003</v>
-      </c>
-      <c r="P101">
-        <v>-194.6849507618401</v>
-      </c>
-      <c r="Q101">
-        <v>-96.18495076184007</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.2322700702437</v>
-      </c>
-      <c r="T101">
-        <v>73.59053280008547</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.08584018978485594</v>
-      </c>
-      <c r="W101">
-        <v>0.215558883248731</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.3441868074773694</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
